--- a/input/ES/reg_retirement.xlsx
+++ b/input/ES/reg_retirement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/SimPathsEU_AUG/input/ES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666AB7B5-956A-4D4D-8B0C-C78449CC9924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E7A8BD-DD46-6B4B-94CA-7EADC2818758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>Probit regression estimates of the probability of retiring, partnered individuals aged 50+ not yet retired</t>
   </si>
   <si>
-    <t>Regions: ES1 = Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =Centro , ES5 = Este , ES5 = Sur , ES5 = Canarias.</t>
+    <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES6=  Sur , ES7 = ,  Canarias.</t>
   </si>
   <si>
     <t>Goodnessoffit</t>
@@ -130,7 +130,7 @@
     <t>Reached_Retirement_Age</t>
   </si>
   <si>
-    <t>Les_c3_NotEmployed_L1</t>
+    <t>Les_c2_NotEmployed_L1</t>
   </si>
   <si>
     <t>Ydses_c5_Q2_L1</t>
@@ -178,16 +178,16 @@
     <t>COEFFICIENT</t>
   </si>
   <si>
-    <t>Reached_Retirement_Age_Les_c3_NotEmployed_L1</t>
-  </si>
-  <si>
-    <t>Reached_Retirement_Age_Sp</t>
-  </si>
-  <si>
-    <t>Elig_pen_Sp</t>
-  </si>
-  <si>
-    <t>Elig_pen_L1_Sp</t>
+    <t>Reached_Retirement_Age_Les_c2_NotEmployed_L1</t>
+  </si>
+  <si>
+    <t>Reached_Retirement_Age_Sp_L1</t>
+  </si>
+  <si>
+    <t>Elig_pen_Sp_L1</t>
+  </si>
+  <si>
+    <t>Elig_pen_L1_Sp_L1</t>
   </si>
   <si>
     <t>Lessp_c3_NotEmployed_L1</t>
@@ -673,13 +673,13 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.32015012213424909</v>
+        <v>0.32016434260509796</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
       </c>
       <c r="F5">
-        <v>1686.3999754828105</v>
+        <v>1686.3826534733244</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -687,13 +687,13 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>21275</v>
+        <v>21276</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
       <c r="F6">
-        <v>-4802772.8732007602</v>
+        <v>-4802802.9741875418</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -706,13 +706,13 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>0.32463500320489191</v>
+        <v>0.32501950235748978</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
       </c>
       <c r="F11">
-        <v>3430.1690579460264</v>
+        <v>3443.7101888757511</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -726,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="F12">
-        <v>-10768081.384756271</v>
+        <v>-10761951.526744192</v>
       </c>
     </row>
   </sheetData>
@@ -821,76 +821,76 @@
         <v>27</v>
       </c>
       <c r="B2">
-        <v>0.28886228311706291</v>
+        <v>0.2887942671573514</v>
       </c>
       <c r="C2">
-        <v>3.2774275453376781E-3</v>
+        <v>3.2772000983176466E-3</v>
       </c>
       <c r="D2">
-        <v>4.241711089230714E-4</v>
+        <v>4.2483191885534346E-4</v>
       </c>
       <c r="E2">
-        <v>-2.5273815145836423E-6</v>
+        <v>-2.5317882363579935E-6</v>
       </c>
       <c r="F2">
-        <v>1.2276989436466675E-4</v>
+        <v>1.2284936470375972E-4</v>
       </c>
       <c r="G2">
-        <v>6.1150522078228355E-4</v>
+        <v>6.1169123473884548E-4</v>
       </c>
       <c r="H2">
-        <v>3.1958539627207933E-4</v>
+        <v>3.1967730147480588E-4</v>
       </c>
       <c r="I2">
-        <v>9.2277019913184584E-5</v>
+        <v>9.202019046648082E-5</v>
       </c>
       <c r="J2">
-        <v>-7.2875167281320871E-5</v>
+        <v>-7.331760072023586E-5</v>
       </c>
       <c r="K2">
-        <v>1.1367285074757817E-4</v>
+        <v>1.1337716315218516E-4</v>
       </c>
       <c r="L2">
-        <v>-1.9337528582403249E-4</v>
+        <v>-1.9397742251601774E-4</v>
       </c>
       <c r="M2">
-        <v>-5.7941091450655506E-5</v>
+        <v>-5.7890159434744083E-5</v>
       </c>
       <c r="N2">
-        <v>-4.4511384326082338E-4</v>
+        <v>-4.4495405509703144E-4</v>
       </c>
       <c r="O2">
-        <v>-7.4793070381997924E-4</v>
+        <v>-7.4780033940842635E-4</v>
       </c>
       <c r="P2">
-        <v>-1.5540246346103083E-3</v>
+        <v>-1.553361962015571E-3</v>
       </c>
       <c r="Q2">
-        <v>3.7473684200277379E-4</v>
+        <v>3.7471880904776087E-4</v>
       </c>
       <c r="R2">
-        <v>4.4966432280574709E-4</v>
+        <v>4.4969172702185364E-4</v>
       </c>
       <c r="S2">
-        <v>8.3209192765267437E-4</v>
+        <v>8.309067437706273E-4</v>
       </c>
       <c r="T2">
-        <v>5.1636486182710995E-4</v>
+        <v>5.1643597614740725E-4</v>
       </c>
       <c r="U2">
-        <v>1.7084223439435857E-4</v>
+        <v>1.7082526894713007E-4</v>
       </c>
       <c r="V2">
-        <v>7.3688752101665222E-4</v>
+        <v>7.3700127852097672E-4</v>
       </c>
       <c r="W2">
-        <v>-7.9075494791071407E-5</v>
+        <v>-7.9151029552920537E-5</v>
       </c>
       <c r="X2">
-        <v>1.7967249437391601E-4</v>
+        <v>1.8073783339145636E-4</v>
       </c>
       <c r="Y2">
-        <v>-1.6786004743844087E-2</v>
+        <v>-1.6808861133236104E-2</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
@@ -898,76 +898,76 @@
         <v>28</v>
       </c>
       <c r="B3">
-        <v>-0.19449677421958297</v>
+        <v>-0.19443227834433768</v>
       </c>
       <c r="C3">
-        <v>4.241711089230714E-4</v>
+        <v>4.2483191885534346E-4</v>
       </c>
       <c r="D3">
-        <v>8.3819818405408142E-3</v>
+        <v>8.3841316967444013E-3</v>
       </c>
       <c r="E3">
-        <v>-6.7406988300632627E-5</v>
+        <v>-6.7423446384728058E-5</v>
       </c>
       <c r="F3">
-        <v>-6.2665409153839086E-3</v>
+        <v>-6.2672334140308275E-3</v>
       </c>
       <c r="G3">
-        <v>-5.7445743684857702E-3</v>
+        <v>-5.7452281984461551E-3</v>
       </c>
       <c r="H3">
-        <v>3.2547362057806783E-4</v>
+        <v>3.2557029444143723E-4</v>
       </c>
       <c r="I3">
-        <v>7.1316978225839092E-4</v>
+        <v>7.1360480317597588E-4</v>
       </c>
       <c r="J3">
-        <v>5.8492891862881313E-3</v>
+        <v>5.8494260028782857E-3</v>
       </c>
       <c r="K3">
-        <v>-1.1695211600249583E-4</v>
+        <v>-1.1665190321906438E-4</v>
       </c>
       <c r="L3">
-        <v>5.0319387980053698E-4</v>
+        <v>5.0380571806615815E-4</v>
       </c>
       <c r="M3">
-        <v>2.9895339810032118E-4</v>
+        <v>2.9900318018807794E-4</v>
       </c>
       <c r="N3">
-        <v>3.7288580278485584E-4</v>
+        <v>3.7284900316576081E-4</v>
       </c>
       <c r="O3">
-        <v>6.0563612340472361E-4</v>
+        <v>6.0577660682216081E-4</v>
       </c>
       <c r="P3">
-        <v>-5.0893754970762761E-4</v>
+        <v>-5.0972634126932037E-4</v>
       </c>
       <c r="Q3">
-        <v>8.1544929062930815E-4</v>
+        <v>8.158134524309385E-4</v>
       </c>
       <c r="R3">
-        <v>1.4438308230710073E-3</v>
+        <v>1.4442747913062243E-3</v>
       </c>
       <c r="S3">
-        <v>1.4061250129435076E-3</v>
+        <v>1.407541414986945E-3</v>
       </c>
       <c r="T3">
-        <v>1.2629612017679426E-3</v>
+        <v>1.263294423463554E-3</v>
       </c>
       <c r="U3">
-        <v>1.5359531350203626E-3</v>
+        <v>1.5363959200552016E-3</v>
       </c>
       <c r="V3">
-        <v>1.311178040704606E-3</v>
+        <v>1.3115773147099365E-3</v>
       </c>
       <c r="W3">
-        <v>-6.0076720498855943E-5</v>
+        <v>-6.0050833899493589E-5</v>
       </c>
       <c r="X3">
-        <v>2.0807677731464469E-4</v>
+        <v>2.0734956898646462E-4</v>
       </c>
       <c r="Y3">
-        <v>-0.2606092566568865</v>
+        <v>-0.26068014295401309</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.2">
@@ -975,76 +975,76 @@
         <v>29</v>
       </c>
       <c r="B4">
-        <v>2.9490041894145156E-3</v>
+        <v>2.9485875606328096E-3</v>
       </c>
       <c r="C4">
-        <v>-2.5273815145836423E-6</v>
+        <v>-2.5317882363579935E-6</v>
       </c>
       <c r="D4">
-        <v>-6.7406988300632627E-5</v>
+        <v>-6.7423446384728058E-5</v>
       </c>
       <c r="E4">
-        <v>5.4612082400913683E-7</v>
+        <v>5.4624661410713258E-7</v>
       </c>
       <c r="F4">
-        <v>5.3963462650899116E-5</v>
+        <v>5.3968788625929638E-5</v>
       </c>
       <c r="G4">
-        <v>4.9415472377848751E-5</v>
+        <v>4.9420569782659637E-5</v>
       </c>
       <c r="H4">
-        <v>-2.2156233001565425E-6</v>
+        <v>-2.2163410276575095E-6</v>
       </c>
       <c r="I4">
-        <v>-5.4258089138335806E-6</v>
+        <v>-5.4288528804621259E-6</v>
       </c>
       <c r="J4">
-        <v>-5.3022978022562901E-5</v>
+        <v>-5.3024057438836605E-5</v>
       </c>
       <c r="K4">
-        <v>1.1189365428499978E-6</v>
+        <v>1.1169784064416068E-6</v>
       </c>
       <c r="L4">
-        <v>-4.1832564008674944E-6</v>
+        <v>-4.1874440949755346E-6</v>
       </c>
       <c r="M4">
-        <v>-2.2549450359362003E-6</v>
+        <v>-2.2553300544623354E-6</v>
       </c>
       <c r="N4">
-        <v>-2.578212703962233E-6</v>
+        <v>-2.5780367690972491E-6</v>
       </c>
       <c r="O4">
-        <v>-3.8693355835524149E-6</v>
+        <v>-3.8704749348174414E-6</v>
       </c>
       <c r="P4">
-        <v>4.2255046483836902E-6</v>
+        <v>4.2309286353634087E-6</v>
       </c>
       <c r="Q4">
-        <v>-6.0028054226119202E-6</v>
+        <v>-6.0054923637039605E-6</v>
       </c>
       <c r="R4">
-        <v>-1.0773862347420956E-5</v>
+        <v>-1.077712555550578E-5</v>
       </c>
       <c r="S4">
-        <v>-1.0675723241624991E-5</v>
+        <v>-1.0685400757698298E-5</v>
       </c>
       <c r="T4">
-        <v>-9.5137999705481938E-6</v>
+        <v>-9.5162780795942856E-6</v>
       </c>
       <c r="U4">
-        <v>-1.1756102432024641E-5</v>
+        <v>-1.1759368423350442E-5</v>
       </c>
       <c r="V4">
-        <v>-9.5504226583854651E-6</v>
+        <v>-9.5534058688779026E-6</v>
       </c>
       <c r="W4">
-        <v>3.8261469408698318E-7</v>
+        <v>3.8245581064729384E-7</v>
       </c>
       <c r="X4">
-        <v>-1.0672267744552206E-6</v>
+        <v>-1.0624288981172418E-6</v>
       </c>
       <c r="Y4">
-        <v>2.0807988194184255E-3</v>
+        <v>2.0813413306304922E-3</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
@@ -1052,76 +1052,76 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>1.567215284086199</v>
+        <v>1.567226700422804</v>
       </c>
       <c r="C5">
-        <v>1.2276989436466675E-4</v>
+        <v>1.2284936470375972E-4</v>
       </c>
       <c r="D5">
-        <v>-6.2665409153839086E-3</v>
+        <v>-6.2672334140308275E-3</v>
       </c>
       <c r="E5">
-        <v>5.3963462650899116E-5</v>
+        <v>5.3968788625929638E-5</v>
       </c>
       <c r="F5">
-        <v>1.4396478317066745E-2</v>
+        <v>1.4396716369991434E-2</v>
       </c>
       <c r="G5">
-        <v>8.6965691269616733E-3</v>
+        <v>8.6969395515247797E-3</v>
       </c>
       <c r="H5">
-        <v>8.9683230638598621E-5</v>
+        <v>8.9646471711207071E-5</v>
       </c>
       <c r="I5">
-        <v>-1.2653729951742228E-4</v>
+        <v>-1.265523761466718E-4</v>
       </c>
       <c r="J5">
-        <v>-1.1854942445491623E-2</v>
+        <v>-1.1855212437201654E-2</v>
       </c>
       <c r="K5">
-        <v>1.7889662486112743E-3</v>
+        <v>1.7891674068608154E-3</v>
       </c>
       <c r="L5">
-        <v>-2.6379697373673378E-4</v>
+        <v>-2.6378356889011217E-4</v>
       </c>
       <c r="M5">
-        <v>1.8873691483347818E-4</v>
+        <v>1.8874269157246291E-4</v>
       </c>
       <c r="N5">
-        <v>6.3675129607465575E-4</v>
+        <v>6.368582083605169E-4</v>
       </c>
       <c r="O5">
-        <v>1.3453403113298928E-3</v>
+        <v>1.3453521981434576E-3</v>
       </c>
       <c r="P5">
-        <v>9.1703187757349869E-5</v>
+        <v>9.1680635442258074E-5</v>
       </c>
       <c r="Q5">
-        <v>-2.7253493038349036E-4</v>
+        <v>-2.7265044014394141E-4</v>
       </c>
       <c r="R5">
-        <v>-3.8707854340498671E-4</v>
+        <v>-3.8716513852304207E-4</v>
       </c>
       <c r="S5">
-        <v>-6.1029048194654071E-4</v>
+        <v>-6.1038663719111853E-4</v>
       </c>
       <c r="T5">
-        <v>-5.5778335818701397E-4</v>
+        <v>-5.5785807744340721E-4</v>
       </c>
       <c r="U5">
-        <v>-4.5355422815356386E-4</v>
+        <v>-4.5367507191610562E-4</v>
       </c>
       <c r="V5">
-        <v>-3.0286210280648825E-4</v>
+        <v>-3.0297118443714348E-4</v>
       </c>
       <c r="W5">
-        <v>-6.8679618888095595E-5</v>
+        <v>-6.8673621271978305E-5</v>
       </c>
       <c r="X5">
-        <v>5.8318881328912886E-4</v>
+        <v>5.8315810217423464E-4</v>
       </c>
       <c r="Y5">
-        <v>0.18104754929897471</v>
+        <v>0.18106981320598359</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.2">
@@ -1129,76 +1129,76 @@
         <v>31</v>
       </c>
       <c r="B6">
-        <v>1.3400184234619177</v>
+        <v>1.3400300852774567</v>
       </c>
       <c r="C6">
-        <v>6.1150522078228355E-4</v>
+        <v>6.1169123473884548E-4</v>
       </c>
       <c r="D6">
-        <v>-5.7445743684857702E-3</v>
+        <v>-5.7452281984461551E-3</v>
       </c>
       <c r="E6">
-        <v>4.9415472377848751E-5</v>
+        <v>4.9420569782659637E-5</v>
       </c>
       <c r="F6">
-        <v>8.6965691269616733E-3</v>
+        <v>8.6969395515247797E-3</v>
       </c>
       <c r="G6">
-        <v>1.6882581663273818E-2</v>
+        <v>1.6883113258583576E-2</v>
       </c>
       <c r="H6">
-        <v>2.2540557178631418E-4</v>
+        <v>2.2543583567750936E-4</v>
       </c>
       <c r="I6">
-        <v>4.3624020772464224E-4</v>
+        <v>4.3622779977941454E-4</v>
       </c>
       <c r="J6">
-        <v>-1.0471634473984352E-2</v>
+        <v>-1.0471894121715189E-2</v>
       </c>
       <c r="K6">
-        <v>1.9015271266200305E-4</v>
+        <v>1.9013702091490343E-4</v>
       </c>
       <c r="L6">
-        <v>-1.9007480181538333E-4</v>
+        <v>-1.9010366840431503E-4</v>
       </c>
       <c r="M6">
-        <v>2.2282598577271374E-4</v>
+        <v>2.227411949269377E-4</v>
       </c>
       <c r="N6">
-        <v>-8.4400786173235987E-5</v>
+        <v>-8.4553526749065605E-5</v>
       </c>
       <c r="O6">
-        <v>2.6693663249364487E-4</v>
+        <v>2.6676730403549578E-4</v>
       </c>
       <c r="P6">
-        <v>1.7720029612834642E-4</v>
+        <v>1.7724556950660109E-4</v>
       </c>
       <c r="Q6">
-        <v>-2.6313424909580468E-4</v>
+        <v>-2.6326142874530389E-4</v>
       </c>
       <c r="R6">
-        <v>-2.3366268862189121E-4</v>
+        <v>-2.3376743133066147E-4</v>
       </c>
       <c r="S6">
-        <v>1.4051762578142467E-4</v>
+        <v>1.4054516612603844E-4</v>
       </c>
       <c r="T6">
-        <v>-5.519837187028323E-4</v>
+        <v>-5.5210331818639907E-4</v>
       </c>
       <c r="U6">
-        <v>-3.9664521688407423E-4</v>
+        <v>-3.9680319285552434E-4</v>
       </c>
       <c r="V6">
-        <v>-1.3583423428414898E-7</v>
+        <v>-2.9916415842864974E-7</v>
       </c>
       <c r="W6">
-        <v>-7.7953170142740572E-5</v>
+        <v>-7.7964990227346112E-5</v>
       </c>
       <c r="X6">
-        <v>8.560236571222013E-4</v>
+        <v>8.561282207184967E-4</v>
       </c>
       <c r="Y6">
-        <v>0.16648058498717488</v>
+        <v>0.16650170403807674</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.2">
@@ -1206,76 +1206,76 @@
         <v>32</v>
       </c>
       <c r="B7">
-        <v>4.9600750971164877E-2</v>
+        <v>4.960623478266897E-2</v>
       </c>
       <c r="C7">
-        <v>3.1958539627207933E-4</v>
+        <v>3.1967730147480588E-4</v>
       </c>
       <c r="D7">
-        <v>3.2547362057806783E-4</v>
+        <v>3.2557029444143723E-4</v>
       </c>
       <c r="E7">
-        <v>-2.2156233001565425E-6</v>
+        <v>-2.2163410276575095E-6</v>
       </c>
       <c r="F7">
-        <v>8.9683230638598621E-5</v>
+        <v>8.9646471711207071E-5</v>
       </c>
       <c r="G7">
-        <v>2.2540557178631418E-4</v>
+        <v>2.2543583567750936E-4</v>
       </c>
       <c r="H7">
-        <v>5.080153272627873E-3</v>
+        <v>5.0805537555463787E-3</v>
       </c>
       <c r="I7">
-        <v>2.8961818460152369E-3</v>
+        <v>2.8965022173864036E-3</v>
       </c>
       <c r="J7">
-        <v>-2.2401512627251105E-4</v>
+        <v>-2.2404361070656404E-4</v>
       </c>
       <c r="K7">
-        <v>1.9015686889376372E-4</v>
+        <v>1.9018961101571421E-4</v>
       </c>
       <c r="L7">
-        <v>-7.6137042227071659E-5</v>
+        <v>-7.6114521662576156E-5</v>
       </c>
       <c r="M7">
-        <v>2.5630047841888881E-4</v>
+        <v>2.5633121703558395E-4</v>
       </c>
       <c r="N7">
-        <v>2.0210291150559183E-4</v>
+        <v>2.0213369778930752E-4</v>
       </c>
       <c r="O7">
-        <v>1.3911341897826204E-3</v>
+        <v>1.3913193622218099E-3</v>
       </c>
       <c r="P7">
-        <v>-4.0106203400793253E-4</v>
+        <v>-4.0115391401050445E-4</v>
       </c>
       <c r="Q7">
-        <v>7.1607032831221256E-4</v>
+        <v>7.1624881933539408E-4</v>
       </c>
       <c r="R7">
-        <v>3.8397096198027015E-4</v>
+        <v>3.8410221112102072E-4</v>
       </c>
       <c r="S7">
-        <v>6.2107566485741653E-4</v>
+        <v>6.2129832502369193E-4</v>
       </c>
       <c r="T7">
-        <v>5.1625243358947555E-4</v>
+        <v>5.1637967594370593E-4</v>
       </c>
       <c r="U7">
-        <v>3.9982679822226882E-4</v>
+        <v>3.9994738844769274E-4</v>
       </c>
       <c r="V7">
-        <v>7.2269423195278496E-4</v>
+        <v>7.2283373151140634E-4</v>
       </c>
       <c r="W7">
-        <v>-5.7591349200144994E-5</v>
+        <v>-5.7591344688285846E-5</v>
       </c>
       <c r="X7">
-        <v>3.7094442234440294E-4</v>
+        <v>3.7086542311981865E-4</v>
       </c>
       <c r="Y7">
-        <v>-1.4598934105944851E-2</v>
+        <v>-1.4602595817448792E-2</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.2">
@@ -1283,76 +1283,76 @@
         <v>33</v>
       </c>
       <c r="B8">
-        <v>2.190821118229162E-2</v>
+        <v>2.1854364301091622E-2</v>
       </c>
       <c r="C8">
-        <v>9.2277019913184584E-5</v>
+        <v>9.202019046648082E-5</v>
       </c>
       <c r="D8">
-        <v>7.1316978225839092E-4</v>
+        <v>7.1360480317597588E-4</v>
       </c>
       <c r="E8">
-        <v>-5.4258089138335806E-6</v>
+        <v>-5.4288528804621259E-6</v>
       </c>
       <c r="F8">
-        <v>-1.2653729951742228E-4</v>
+        <v>-1.265523761466718E-4</v>
       </c>
       <c r="G8">
-        <v>4.3624020772464224E-4</v>
+        <v>4.3622779977941454E-4</v>
       </c>
       <c r="H8">
-        <v>2.8961818460152369E-3</v>
+        <v>2.8965022173864036E-3</v>
       </c>
       <c r="I8">
-        <v>4.2936496148311427E-3</v>
+        <v>4.2939896559333387E-3</v>
       </c>
       <c r="J8">
-        <v>-2.2714115484632059E-4</v>
+        <v>-2.2725836142650931E-4</v>
       </c>
       <c r="K8">
-        <v>8.8253648770389133E-6</v>
+        <v>8.6165921000539098E-6</v>
       </c>
       <c r="L8">
-        <v>8.2962698213205578E-5</v>
+        <v>8.2616196208383074E-5</v>
       </c>
       <c r="M8">
-        <v>5.8715040816659453E-4</v>
+        <v>5.8723759636325663E-4</v>
       </c>
       <c r="N8">
-        <v>9.189425703166901E-4</v>
+        <v>9.1916946422159515E-4</v>
       </c>
       <c r="O8">
-        <v>2.1141789148999566E-3</v>
+        <v>2.1145539484863007E-3</v>
       </c>
       <c r="P8">
-        <v>1.476503768315404E-4</v>
+        <v>1.4804630244966144E-4</v>
       </c>
       <c r="Q8">
-        <v>9.215915984279201E-4</v>
+        <v>9.2164970538139682E-4</v>
       </c>
       <c r="R8">
-        <v>9.3785476767055962E-4</v>
+        <v>9.3795861874180087E-4</v>
       </c>
       <c r="S8">
-        <v>1.1607549993109239E-3</v>
+        <v>1.1602133432301888E-3</v>
       </c>
       <c r="T8">
-        <v>7.4951123555981212E-4</v>
+        <v>7.4961405640390174E-4</v>
       </c>
       <c r="U8">
-        <v>1.1488763990644686E-3</v>
+        <v>1.1489110652464554E-3</v>
       </c>
       <c r="V8">
-        <v>8.6127751849141021E-4</v>
+        <v>8.6136483622944961E-4</v>
       </c>
       <c r="W8">
-        <v>2.6254312530237228E-5</v>
+        <v>2.6233599425287853E-5</v>
       </c>
       <c r="X8">
-        <v>6.8865382215900191E-5</v>
+        <v>6.9311461262675693E-5</v>
       </c>
       <c r="Y8">
-        <v>-2.8443720688763968E-2</v>
+        <v>-2.8459061067412694E-2</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.2">
@@ -1360,153 +1360,153 @@
         <v>34</v>
       </c>
       <c r="B9">
-        <v>-1.0337325884982158</v>
+        <v>-1.033770163177413</v>
       </c>
       <c r="C9">
-        <v>-7.2875167281320871E-5</v>
+        <v>-7.331760072023586E-5</v>
       </c>
       <c r="D9">
-        <v>5.8492891862881313E-3</v>
+        <v>5.8494260028782857E-3</v>
       </c>
       <c r="E9">
-        <v>-5.3022978022562901E-5</v>
+        <v>-5.3024057438836605E-5</v>
       </c>
       <c r="F9">
-        <v>-1.1854942445491623E-2</v>
+        <v>-1.1855212437201654E-2</v>
       </c>
       <c r="G9">
-        <v>-1.0471634473984352E-2</v>
+        <v>-1.0471894121715189E-2</v>
       </c>
       <c r="H9">
-        <v>-2.2401512627251105E-4</v>
+        <v>-2.2404361070656404E-4</v>
       </c>
       <c r="I9">
-        <v>-2.2714115484632059E-4</v>
+        <v>-2.2725836142650931E-4</v>
       </c>
       <c r="J9">
-        <v>1.6580473118586042E-2</v>
+        <v>1.6580795905178934E-2</v>
       </c>
       <c r="K9">
-        <v>-2.3750698024248796E-3</v>
+        <v>-2.3754534627535113E-3</v>
       </c>
       <c r="L9">
-        <v>8.3319313859200883E-5</v>
+        <v>8.3148213434212914E-5</v>
       </c>
       <c r="M9">
-        <v>-3.6269770216627601E-4</v>
+        <v>-3.6269492924667548E-4</v>
       </c>
       <c r="N9">
-        <v>-9.4745685326783763E-4</v>
+        <v>-9.4747241147031744E-4</v>
       </c>
       <c r="O9">
-        <v>-2.0133703378150056E-3</v>
+        <v>-2.0133480897541241E-3</v>
       </c>
       <c r="P9">
-        <v>-8.1927256903799317E-5</v>
+        <v>-8.1519956650927261E-5</v>
       </c>
       <c r="Q9">
-        <v>-3.2505081919300544E-4</v>
+        <v>-3.2502564908160753E-4</v>
       </c>
       <c r="R9">
-        <v>-2.158657726506405E-4</v>
+        <v>-2.1588199243713357E-4</v>
       </c>
       <c r="S9">
-        <v>1.0708941484083951E-4</v>
+        <v>1.0665282318286394E-4</v>
       </c>
       <c r="T9">
-        <v>5.8503358031640473E-5</v>
+        <v>5.8516892856338987E-5</v>
       </c>
       <c r="U9">
-        <v>-1.2000629166868809E-4</v>
+        <v>-1.1998153827468688E-4</v>
       </c>
       <c r="V9">
-        <v>-5.4107941612495207E-4</v>
+        <v>-5.4105670192655664E-4</v>
       </c>
       <c r="W9">
-        <v>1.2991590171457755E-4</v>
+        <v>1.2991010158539505E-4</v>
       </c>
       <c r="X9">
-        <v>-7.6411163723786452E-4</v>
+        <v>-7.638186510975295E-4</v>
       </c>
       <c r="Y9">
-        <v>-0.15992006007432602</v>
+        <v>-0.15992406178289431</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B10">
-        <v>0.13809849870756685</v>
+        <v>0.13804408599137261</v>
       </c>
       <c r="C10">
-        <v>1.1367285074757817E-4</v>
+        <v>1.1337716315218516E-4</v>
       </c>
       <c r="D10">
-        <v>-1.1695211600249583E-4</v>
+        <v>-1.1665190321906438E-4</v>
       </c>
       <c r="E10">
-        <v>1.1189365428499978E-6</v>
+        <v>1.1169784064416068E-6</v>
       </c>
       <c r="F10">
-        <v>1.7889662486112743E-3</v>
+        <v>1.7891674068608154E-3</v>
       </c>
       <c r="G10">
-        <v>1.9015271266200305E-4</v>
+        <v>1.9013702091490343E-4</v>
       </c>
       <c r="H10">
-        <v>1.9015686889376372E-4</v>
+        <v>1.9018961101571421E-4</v>
       </c>
       <c r="I10">
-        <v>8.8253648770389133E-6</v>
+        <v>8.6165921000539098E-6</v>
       </c>
       <c r="J10">
-        <v>-2.3750698024248796E-3</v>
+        <v>-2.3754534627535113E-3</v>
       </c>
       <c r="K10">
-        <v>1.0046432457173174E-2</v>
+        <v>1.0047054685614894E-2</v>
       </c>
       <c r="L10">
-        <v>2.2958968391110623E-4</v>
+        <v>2.2925265625620313E-4</v>
       </c>
       <c r="M10">
-        <v>3.6180455895945636E-3</v>
+        <v>3.6183057026887584E-3</v>
       </c>
       <c r="N10">
-        <v>8.6812526808428443E-3</v>
+        <v>8.6820930050419548E-3</v>
       </c>
       <c r="O10">
-        <v>8.6939372898196202E-3</v>
+        <v>8.6946667889408625E-3</v>
       </c>
       <c r="P10">
-        <v>-1.4813617118364878E-3</v>
+        <v>-1.4810764956219033E-3</v>
       </c>
       <c r="Q10">
-        <v>-1.5779242744860811E-4</v>
+        <v>-1.5793164134294754E-4</v>
       </c>
       <c r="R10">
-        <v>-6.6401838513888492E-4</v>
+        <v>-6.6416689999699782E-4</v>
       </c>
       <c r="S10">
-        <v>-9.2745899511592026E-4</v>
+        <v>-9.2843268530518248E-4</v>
       </c>
       <c r="T10">
-        <v>-4.9752945056342687E-4</v>
+        <v>-4.9762042177596381E-4</v>
       </c>
       <c r="U10">
-        <v>-2.9326280586914211E-4</v>
+        <v>-2.9336562375335655E-4</v>
       </c>
       <c r="V10">
-        <v>-3.665445947828895E-4</v>
+        <v>-3.6664292016380662E-4</v>
       </c>
       <c r="W10">
-        <v>4.1880366462488609E-5</v>
+        <v>4.1844362811155984E-5</v>
       </c>
       <c r="X10">
-        <v>-1.8097421900054901E-4</v>
+        <v>-1.8034555545380811E-4</v>
       </c>
       <c r="Y10">
-        <v>-6.0027937355755789E-3</v>
+        <v>-6.0137935834939371E-3</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
@@ -1514,76 +1514,76 @@
         <v>36</v>
       </c>
       <c r="B11">
-        <v>0.16195831250086345</v>
+        <v>0.16187379552959719</v>
       </c>
       <c r="C11">
-        <v>-1.9337528582403249E-4</v>
+        <v>-1.9397742251601774E-4</v>
       </c>
       <c r="D11">
-        <v>5.0319387980053698E-4</v>
+        <v>5.0380571806615815E-4</v>
       </c>
       <c r="E11">
-        <v>-4.1832564008674944E-6</v>
+        <v>-4.1874440949755346E-6</v>
       </c>
       <c r="F11">
-        <v>-2.6379697373673378E-4</v>
+        <v>-2.6378356889011217E-4</v>
       </c>
       <c r="G11">
-        <v>-1.9007480181538333E-4</v>
+        <v>-1.9010366840431503E-4</v>
       </c>
       <c r="H11">
-        <v>-7.6137042227071659E-5</v>
+        <v>-7.6114521662576156E-5</v>
       </c>
       <c r="I11">
-        <v>8.2962698213205578E-5</v>
+        <v>8.2616196208383074E-5</v>
       </c>
       <c r="J11">
-        <v>8.3319313859200883E-5</v>
+        <v>8.3148213434212914E-5</v>
       </c>
       <c r="K11">
-        <v>2.2958968391110623E-4</v>
+        <v>2.2925265625620313E-4</v>
       </c>
       <c r="L11">
-        <v>3.7259722287291473E-3</v>
+        <v>3.7257057413935513E-3</v>
       </c>
       <c r="M11">
-        <v>1.5812283537065348E-3</v>
+        <v>1.581350863737784E-3</v>
       </c>
       <c r="N11">
-        <v>1.6901321808523938E-3</v>
+        <v>1.6904372280317792E-3</v>
       </c>
       <c r="O11">
-        <v>1.6526272983173967E-3</v>
+        <v>1.6528887520674488E-3</v>
       </c>
       <c r="P11">
-        <v>5.1746781389917502E-4</v>
+        <v>5.1824689684483254E-4</v>
       </c>
       <c r="Q11">
-        <v>1.8064402922648558E-4</v>
+        <v>1.8061883562657446E-4</v>
       </c>
       <c r="R11">
-        <v>2.457055645072538E-4</v>
+        <v>2.4575039570695059E-4</v>
       </c>
       <c r="S11">
-        <v>2.8312943050623761E-4</v>
+        <v>2.8181945827751109E-4</v>
       </c>
       <c r="T11">
-        <v>9.400923045754404E-5</v>
+        <v>9.4085157568694899E-5</v>
       </c>
       <c r="U11">
-        <v>6.6740216175676281E-4</v>
+        <v>6.6737962189110682E-4</v>
       </c>
       <c r="V11">
-        <v>2.2231884965593772E-4</v>
+        <v>2.2238624859621223E-4</v>
       </c>
       <c r="W11">
-        <v>-2.6329307756217495E-5</v>
+        <v>-2.6400060074644198E-5</v>
       </c>
       <c r="X11">
-        <v>4.0170218584037703E-4</v>
+        <v>4.0281613969062177E-4</v>
       </c>
       <c r="Y11">
-        <v>-1.6766972410609253E-2</v>
+        <v>-1.6787752027816405E-2</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
@@ -1591,76 +1591,76 @@
         <v>37</v>
       </c>
       <c r="B12">
-        <v>3.1295741376551979E-2</v>
+        <v>3.1297148679227234E-2</v>
       </c>
       <c r="C12">
-        <v>-5.7941091450655506E-5</v>
+        <v>-5.7890159434744083E-5</v>
       </c>
       <c r="D12">
-        <v>2.9895339810032118E-4</v>
+        <v>2.9900318018807794E-4</v>
       </c>
       <c r="E12">
-        <v>-2.2549450359362003E-6</v>
+        <v>-2.2553300544623354E-6</v>
       </c>
       <c r="F12">
-        <v>1.8873691483347818E-4</v>
+        <v>1.8874269157246291E-4</v>
       </c>
       <c r="G12">
-        <v>2.2282598577271374E-4</v>
+        <v>2.227411949269377E-4</v>
       </c>
       <c r="H12">
-        <v>2.5630047841888881E-4</v>
+        <v>2.5633121703558395E-4</v>
       </c>
       <c r="I12">
-        <v>5.8715040816659453E-4</v>
+        <v>5.8723759636325663E-4</v>
       </c>
       <c r="J12">
-        <v>-3.6269770216627601E-4</v>
+        <v>-3.6269492924667548E-4</v>
       </c>
       <c r="K12">
-        <v>3.6180455895945636E-3</v>
+        <v>3.6183057026887584E-3</v>
       </c>
       <c r="L12">
-        <v>1.5812283537065348E-3</v>
+        <v>1.581350863737784E-3</v>
       </c>
       <c r="M12">
-        <v>5.7121303464280062E-3</v>
+        <v>5.7124422353091514E-3</v>
       </c>
       <c r="N12">
-        <v>5.1154805745930914E-3</v>
+        <v>5.1158356225267333E-3</v>
       </c>
       <c r="O12">
-        <v>5.2507375929707837E-3</v>
+        <v>5.2510710657778722E-3</v>
       </c>
       <c r="P12">
-        <v>5.0147579781648641E-4</v>
+        <v>5.0150019614737112E-4</v>
       </c>
       <c r="Q12">
-        <v>-3.1756108121901508E-4</v>
+        <v>-3.175935004988209E-4</v>
       </c>
       <c r="R12">
-        <v>-4.1960833954922741E-4</v>
+        <v>-4.1962949842579231E-4</v>
       </c>
       <c r="S12">
-        <v>-3.2537621366163835E-4</v>
+        <v>-3.2529913164938159E-4</v>
       </c>
       <c r="T12">
-        <v>-2.7766656221246255E-4</v>
+        <v>-2.7769854888019547E-4</v>
       </c>
       <c r="U12">
-        <v>-2.0694007130019456E-4</v>
+        <v>-2.0693714069744689E-4</v>
       </c>
       <c r="V12">
-        <v>-3.0318246631905557E-4</v>
+        <v>-3.0323731948758768E-4</v>
       </c>
       <c r="W12">
-        <v>2.2234038349129201E-5</v>
+        <v>2.2241903466405089E-5</v>
       </c>
       <c r="X12">
-        <v>1.6975790142951044E-4</v>
+        <v>1.6971353593052494E-4</v>
       </c>
       <c r="Y12">
-        <v>-1.5544252096871589E-2</v>
+        <v>-1.5546372834418024E-2</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.2">
@@ -1668,76 +1668,76 @@
         <v>38</v>
       </c>
       <c r="B13">
-        <v>-1.1064354113368192E-2</v>
+        <v>-1.1056684234813732E-2</v>
       </c>
       <c r="C13">
-        <v>-4.4511384326082338E-4</v>
+        <v>-4.4495405509703144E-4</v>
       </c>
       <c r="D13">
-        <v>3.7288580278485584E-4</v>
+        <v>3.7284900316576081E-4</v>
       </c>
       <c r="E13">
-        <v>-2.578212703962233E-6</v>
+        <v>-2.5780367690972491E-6</v>
       </c>
       <c r="F13">
-        <v>6.3675129607465575E-4</v>
+        <v>6.368582083605169E-4</v>
       </c>
       <c r="G13">
-        <v>-8.4400786173235987E-5</v>
+        <v>-8.4553526749065605E-5</v>
       </c>
       <c r="H13">
-        <v>2.0210291150559183E-4</v>
+        <v>2.0213369778930752E-4</v>
       </c>
       <c r="I13">
-        <v>9.189425703166901E-4</v>
+        <v>9.1916946422159515E-4</v>
       </c>
       <c r="J13">
-        <v>-9.4745685326783763E-4</v>
+        <v>-9.4747241147031744E-4</v>
       </c>
       <c r="K13">
-        <v>8.6812526808428443E-3</v>
+        <v>8.6820930050419548E-3</v>
       </c>
       <c r="L13">
-        <v>1.6901321808523938E-3</v>
+        <v>1.6904372280317792E-3</v>
       </c>
       <c r="M13">
-        <v>5.1154805745930914E-3</v>
+        <v>5.1158356225267333E-3</v>
       </c>
       <c r="N13">
-        <v>1.3645364278491339E-2</v>
+        <v>1.3646372490531199E-2</v>
       </c>
       <c r="O13">
-        <v>1.0588068513824191E-2</v>
+        <v>1.0588892432423249E-2</v>
       </c>
       <c r="P13">
-        <v>5.9303654177134905E-4</v>
+        <v>5.9286625073840058E-4</v>
       </c>
       <c r="Q13">
-        <v>-4.6905901832576796E-4</v>
+        <v>-4.6912881963381402E-4</v>
       </c>
       <c r="R13">
-        <v>-7.1658041887770734E-4</v>
+        <v>-7.1667185048940579E-4</v>
       </c>
       <c r="S13">
-        <v>-1.4947499067584993E-3</v>
+        <v>-1.4945102424165509E-3</v>
       </c>
       <c r="T13">
-        <v>-5.7221584141210844E-4</v>
+        <v>-5.7233937837377919E-4</v>
       </c>
       <c r="U13">
-        <v>-6.0552285209864668E-4</v>
+        <v>-6.0557999574334734E-4</v>
       </c>
       <c r="V13">
-        <v>-4.9098548314260252E-4</v>
+        <v>-4.9110413306726599E-4</v>
       </c>
       <c r="W13">
-        <v>6.5166316608058637E-5</v>
+        <v>6.5200146862335402E-5</v>
       </c>
       <c r="X13">
-        <v>-7.823868714326894E-5</v>
+        <v>-7.8600624646599053E-5</v>
       </c>
       <c r="Y13">
-        <v>-2.4154787573449715E-2</v>
+        <v>-2.4154563808679808E-2</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.2">
@@ -1745,76 +1745,76 @@
         <v>39</v>
       </c>
       <c r="B14">
-        <v>0.26834061865294839</v>
+        <v>0.26833953350676221</v>
       </c>
       <c r="C14">
-        <v>-7.4793070381997924E-4</v>
+        <v>-7.4780033940842635E-4</v>
       </c>
       <c r="D14">
-        <v>6.0563612340472361E-4</v>
+        <v>6.0577660682216081E-4</v>
       </c>
       <c r="E14">
-        <v>-3.8693355835524149E-6</v>
+        <v>-3.8704749348174414E-6</v>
       </c>
       <c r="F14">
-        <v>1.3453403113298928E-3</v>
+        <v>1.3453521981434576E-3</v>
       </c>
       <c r="G14">
-        <v>2.6693663249364487E-4</v>
+        <v>2.6676730403549578E-4</v>
       </c>
       <c r="H14">
-        <v>1.3911341897826204E-3</v>
+        <v>1.3913193622218099E-3</v>
       </c>
       <c r="I14">
-        <v>2.1141789148999566E-3</v>
+        <v>2.1145539484863007E-3</v>
       </c>
       <c r="J14">
-        <v>-2.0133703378150056E-3</v>
+        <v>-2.0133480897541241E-3</v>
       </c>
       <c r="K14">
-        <v>8.6939372898196202E-3</v>
+        <v>8.6946667889408625E-3</v>
       </c>
       <c r="L14">
-        <v>1.6526272983173967E-3</v>
+        <v>1.6528887520674488E-3</v>
       </c>
       <c r="M14">
-        <v>5.2507375929707837E-3</v>
+        <v>5.2510710657778722E-3</v>
       </c>
       <c r="N14">
-        <v>1.0588068513824191E-2</v>
+        <v>1.0588892432423249E-2</v>
       </c>
       <c r="O14">
-        <v>1.3409844178573806E-2</v>
+        <v>1.3410811607106271E-2</v>
       </c>
       <c r="P14">
-        <v>7.1305383428605165E-4</v>
+        <v>7.1294352084205759E-4</v>
       </c>
       <c r="Q14">
-        <v>3.2182124432197055E-4</v>
+        <v>3.2185812934484859E-4</v>
       </c>
       <c r="R14">
-        <v>-2.7623885150632188E-4</v>
+        <v>-2.7619838523818517E-4</v>
       </c>
       <c r="S14">
-        <v>-5.0806908763307798E-4</v>
+        <v>-5.0768375328096396E-4</v>
       </c>
       <c r="T14">
-        <v>-1.5760250379026619E-5</v>
+        <v>-1.5741621053791399E-5</v>
       </c>
       <c r="U14">
-        <v>2.1922550568397123E-4</v>
+        <v>2.1926810676775339E-4</v>
       </c>
       <c r="V14">
-        <v>1.4198655100670964E-4</v>
+        <v>1.4195395439349588E-4</v>
       </c>
       <c r="W14">
-        <v>5.4496578314349765E-5</v>
+        <v>5.4530800481503681E-5</v>
       </c>
       <c r="X14">
-        <v>-5.4112602704414411E-5</v>
+        <v>-5.4496344426982826E-5</v>
       </c>
       <c r="Y14">
-        <v>-3.4910163465996208E-2</v>
+        <v>-3.4916024665207573E-2</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
@@ -1822,76 +1822,76 @@
         <v>40</v>
       </c>
       <c r="B15">
-        <v>0.46795453514104168</v>
+        <v>0.46805363414889128</v>
       </c>
       <c r="C15">
-        <v>-1.5540246346103083E-3</v>
+        <v>-1.553361962015571E-3</v>
       </c>
       <c r="D15">
-        <v>-5.0893754970762761E-4</v>
+        <v>-5.0972634126932037E-4</v>
       </c>
       <c r="E15">
-        <v>4.2255046483836902E-6</v>
+        <v>4.2309286353634087E-6</v>
       </c>
       <c r="F15">
-        <v>9.1703187757349869E-5</v>
+        <v>9.1680635442258074E-5</v>
       </c>
       <c r="G15">
-        <v>1.7720029612834642E-4</v>
+        <v>1.7724556950660109E-4</v>
       </c>
       <c r="H15">
-        <v>-4.0106203400793253E-4</v>
+        <v>-4.0115391401050445E-4</v>
       </c>
       <c r="I15">
-        <v>1.476503768315404E-4</v>
+        <v>1.4804630244966144E-4</v>
       </c>
       <c r="J15">
-        <v>-8.1927256903799317E-5</v>
+        <v>-8.1519956650927261E-5</v>
       </c>
       <c r="K15">
-        <v>-1.4813617118364878E-3</v>
+        <v>-1.4810764956219033E-3</v>
       </c>
       <c r="L15">
-        <v>5.1746781389917502E-4</v>
+        <v>5.1824689684483254E-4</v>
       </c>
       <c r="M15">
-        <v>5.0147579781648641E-4</v>
+        <v>5.0150019614737112E-4</v>
       </c>
       <c r="N15">
-        <v>5.9303654177134905E-4</v>
+        <v>5.9286625073840058E-4</v>
       </c>
       <c r="O15">
-        <v>7.1305383428605165E-4</v>
+        <v>7.1294352084205759E-4</v>
       </c>
       <c r="P15">
-        <v>6.1687200247080021E-3</v>
+        <v>6.168178004862801E-3</v>
       </c>
       <c r="Q15">
-        <v>-7.0860473292364435E-4</v>
+        <v>-7.0848439702978503E-4</v>
       </c>
       <c r="R15">
-        <v>-2.3266518961132876E-4</v>
+        <v>-2.325408938903858E-4</v>
       </c>
       <c r="S15">
-        <v>-4.6128882818035016E-4</v>
+        <v>-4.5953681704153369E-4</v>
       </c>
       <c r="T15">
-        <v>-4.1505052783768017E-4</v>
+        <v>-4.150214162990573E-4</v>
       </c>
       <c r="U15">
-        <v>-1.5095874068804765E-4</v>
+        <v>-1.5085902177469494E-4</v>
       </c>
       <c r="V15">
-        <v>-5.1687455332126843E-4</v>
+        <v>-5.1684723191767741E-4</v>
       </c>
       <c r="W15">
-        <v>5.0756281960641033E-5</v>
+        <v>5.0843511466612946E-5</v>
       </c>
       <c r="X15">
-        <v>1.3244538250348713E-4</v>
+        <v>1.3112722604240071E-4</v>
       </c>
       <c r="Y15">
-        <v>1.484495010740073E-2</v>
+        <v>1.4871309672353936E-2</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
@@ -1899,76 +1899,76 @@
         <v>41</v>
       </c>
       <c r="B16">
-        <v>-2.5913316858195281E-2</v>
+        <v>-2.5917432865169447E-2</v>
       </c>
       <c r="C16">
-        <v>3.7473684200277379E-4</v>
+        <v>3.7471880904776087E-4</v>
       </c>
       <c r="D16">
-        <v>8.1544929062930815E-4</v>
+        <v>8.158134524309385E-4</v>
       </c>
       <c r="E16">
-        <v>-6.0028054226119202E-6</v>
+        <v>-6.0054923637039605E-6</v>
       </c>
       <c r="F16">
-        <v>-2.7253493038349036E-4</v>
+        <v>-2.7265044014394141E-4</v>
       </c>
       <c r="G16">
-        <v>-2.6313424909580468E-4</v>
+        <v>-2.6326142874530389E-4</v>
       </c>
       <c r="H16">
-        <v>7.1607032831221256E-4</v>
+        <v>7.1624881933539408E-4</v>
       </c>
       <c r="I16">
-        <v>9.215915984279201E-4</v>
+        <v>9.2164970538139682E-4</v>
       </c>
       <c r="J16">
-        <v>-3.2505081919300544E-4</v>
+        <v>-3.2502564908160753E-4</v>
       </c>
       <c r="K16">
-        <v>-1.5779242744860811E-4</v>
+        <v>-1.5793164134294754E-4</v>
       </c>
       <c r="L16">
-        <v>1.8064402922648558E-4</v>
+        <v>1.8061883562657446E-4</v>
       </c>
       <c r="M16">
-        <v>-3.1756108121901508E-4</v>
+        <v>-3.175935004988209E-4</v>
       </c>
       <c r="N16">
-        <v>-4.6905901832576796E-4</v>
+        <v>-4.6912881963381402E-4</v>
       </c>
       <c r="O16">
-        <v>3.2182124432197055E-4</v>
+        <v>3.2185812934484859E-4</v>
       </c>
       <c r="P16">
-        <v>-7.0860473292364435E-4</v>
+        <v>-7.0848439702978503E-4</v>
       </c>
       <c r="Q16">
-        <v>1.2075237990345204E-2</v>
+        <v>1.2075948034216237E-2</v>
       </c>
       <c r="R16">
-        <v>9.0986881789409651E-3</v>
+        <v>9.0992433862796054E-3</v>
       </c>
       <c r="S16">
-        <v>9.152513979631724E-3</v>
+        <v>9.1529282177041718E-3</v>
       </c>
       <c r="T16">
-        <v>9.0699326156811096E-3</v>
+        <v>9.0704919941855238E-3</v>
       </c>
       <c r="U16">
-        <v>9.1547272755910514E-3</v>
+        <v>9.1552732052523622E-3</v>
       </c>
       <c r="V16">
-        <v>9.0829188293393929E-3</v>
+        <v>9.0834763367899415E-3</v>
       </c>
       <c r="W16">
-        <v>-9.3325764638094708E-5</v>
+        <v>-9.3347218570766438E-5</v>
       </c>
       <c r="X16">
-        <v>3.2880682921118329E-4</v>
+        <v>3.2897643488462736E-4</v>
       </c>
       <c r="Y16">
-        <v>-3.5531996191273785E-2</v>
+        <v>-3.5544470176122403E-2</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.2">
@@ -1976,76 +1976,76 @@
         <v>42</v>
       </c>
       <c r="B17">
-        <v>3.5281756633913419E-2</v>
+        <v>3.5274411052925378E-2</v>
       </c>
       <c r="C17">
-        <v>4.4966432280574709E-4</v>
+        <v>4.4969172702185364E-4</v>
       </c>
       <c r="D17">
-        <v>1.4438308230710073E-3</v>
+        <v>1.4442747913062243E-3</v>
       </c>
       <c r="E17">
-        <v>-1.0773862347420956E-5</v>
+        <v>-1.077712555550578E-5</v>
       </c>
       <c r="F17">
-        <v>-3.8707854340498671E-4</v>
+        <v>-3.8716513852304207E-4</v>
       </c>
       <c r="G17">
-        <v>-2.3366268862189121E-4</v>
+        <v>-2.3376743133066147E-4</v>
       </c>
       <c r="H17">
-        <v>3.8397096198027015E-4</v>
+        <v>3.8410221112102072E-4</v>
       </c>
       <c r="I17">
-        <v>9.3785476767055962E-4</v>
+        <v>9.3795861874180087E-4</v>
       </c>
       <c r="J17">
-        <v>-2.158657726506405E-4</v>
+        <v>-2.1588199243713357E-4</v>
       </c>
       <c r="K17">
-        <v>-6.6401838513888492E-4</v>
+        <v>-6.6416689999699782E-4</v>
       </c>
       <c r="L17">
-        <v>2.457055645072538E-4</v>
+        <v>2.4575039570695059E-4</v>
       </c>
       <c r="M17">
-        <v>-4.1960833954922741E-4</v>
+        <v>-4.1962949842579231E-4</v>
       </c>
       <c r="N17">
-        <v>-7.1658041887770734E-4</v>
+        <v>-7.1667185048940579E-4</v>
       </c>
       <c r="O17">
-        <v>-2.7623885150632188E-4</v>
+        <v>-2.7619838523818517E-4</v>
       </c>
       <c r="P17">
-        <v>-2.3266518961132876E-4</v>
+        <v>-2.325408938903858E-4</v>
       </c>
       <c r="Q17">
-        <v>9.0986881789409651E-3</v>
+        <v>9.0992433862796054E-3</v>
       </c>
       <c r="R17">
-        <v>1.2319275401630296E-2</v>
+        <v>1.2319996239166603E-2</v>
       </c>
       <c r="S17">
-        <v>9.1992553621125031E-3</v>
+        <v>9.1997588140308763E-3</v>
       </c>
       <c r="T17">
-        <v>9.0017974790533792E-3</v>
+        <v>9.0023513306020011E-3</v>
       </c>
       <c r="U17">
-        <v>9.1454367776697548E-3</v>
+        <v>9.1459742295460101E-3</v>
       </c>
       <c r="V17">
-        <v>9.0494880791689367E-3</v>
+        <v>9.050041919103656E-3</v>
       </c>
       <c r="W17">
-        <v>-7.3405906387087366E-5</v>
+        <v>-7.3419817233912727E-5</v>
       </c>
       <c r="X17">
-        <v>2.9141810043692862E-4</v>
+        <v>2.9153687380506239E-4</v>
       </c>
       <c r="Y17">
-        <v>-5.5972733833845739E-2</v>
+        <v>-5.5988083672354416E-2</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.2">
@@ -2053,76 +2053,76 @@
         <v>43</v>
       </c>
       <c r="B18">
-        <v>0.11915790468246124</v>
+        <v>0.11899269376577361</v>
       </c>
       <c r="C18">
-        <v>8.3209192765267437E-4</v>
+        <v>8.309067437706273E-4</v>
       </c>
       <c r="D18">
-        <v>1.4061250129435076E-3</v>
+        <v>1.407541414986945E-3</v>
       </c>
       <c r="E18">
-        <v>-1.0675723241624991E-5</v>
+        <v>-1.0685400757698298E-5</v>
       </c>
       <c r="F18">
-        <v>-6.1029048194654071E-4</v>
+        <v>-6.1038663719111853E-4</v>
       </c>
       <c r="G18">
-        <v>1.4051762578142467E-4</v>
+        <v>1.4054516612603844E-4</v>
       </c>
       <c r="H18">
-        <v>6.2107566485741653E-4</v>
+        <v>6.2129832502369193E-4</v>
       </c>
       <c r="I18">
-        <v>1.1607549993109239E-3</v>
+        <v>1.1602133432301888E-3</v>
       </c>
       <c r="J18">
-        <v>1.0708941484083951E-4</v>
+        <v>1.0665282318286394E-4</v>
       </c>
       <c r="K18">
-        <v>-9.2745899511592026E-4</v>
+        <v>-9.2843268530518248E-4</v>
       </c>
       <c r="L18">
-        <v>2.8312943050623761E-4</v>
+        <v>2.8181945827751109E-4</v>
       </c>
       <c r="M18">
-        <v>-3.2537621366163835E-4</v>
+        <v>-3.2529913164938159E-4</v>
       </c>
       <c r="N18">
-        <v>-1.4947499067584993E-3</v>
+        <v>-1.4945102424165509E-3</v>
       </c>
       <c r="O18">
-        <v>-5.0806908763307798E-4</v>
+        <v>-5.0768375328096396E-4</v>
       </c>
       <c r="P18">
-        <v>-4.6128882818035016E-4</v>
+        <v>-4.5953681704153369E-4</v>
       </c>
       <c r="Q18">
-        <v>9.152513979631724E-3</v>
+        <v>9.1529282177041718E-3</v>
       </c>
       <c r="R18">
-        <v>9.1992553621125031E-3</v>
+        <v>9.1997588140308763E-3</v>
       </c>
       <c r="S18">
-        <v>1.2602162345021968E-2</v>
+        <v>1.2600880563958963E-2</v>
       </c>
       <c r="T18">
-        <v>9.0445383081104308E-3</v>
+        <v>9.0451570456724292E-3</v>
       </c>
       <c r="U18">
-        <v>9.2432011230562522E-3</v>
+        <v>9.2434957487699532E-3</v>
       </c>
       <c r="V18">
-        <v>9.0666200942843347E-3</v>
+        <v>9.0671946737533524E-3</v>
       </c>
       <c r="W18">
-        <v>-1.3019832926160603E-4</v>
+        <v>-1.3035026285169256E-4</v>
       </c>
       <c r="X18">
-        <v>3.89336298102806E-4</v>
+        <v>3.9156635859698401E-4</v>
       </c>
       <c r="Y18">
-        <v>-5.3228862965667229E-2</v>
+        <v>-5.3277359124532006E-2</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.2">
@@ -2130,76 +2130,76 @@
         <v>44</v>
       </c>
       <c r="B19">
-        <v>1.3453782948559726E-2</v>
+        <v>1.345626889885025E-2</v>
       </c>
       <c r="C19">
-        <v>5.1636486182710995E-4</v>
+        <v>5.1643597614740725E-4</v>
       </c>
       <c r="D19">
-        <v>1.2629612017679426E-3</v>
+        <v>1.263294423463554E-3</v>
       </c>
       <c r="E19">
-        <v>-9.5137999705481938E-6</v>
+        <v>-9.5162780795942856E-6</v>
       </c>
       <c r="F19">
-        <v>-5.5778335818701397E-4</v>
+        <v>-5.5785807744340721E-4</v>
       </c>
       <c r="G19">
-        <v>-5.519837187028323E-4</v>
+        <v>-5.5210331818639907E-4</v>
       </c>
       <c r="H19">
-        <v>5.1625243358947555E-4</v>
+        <v>5.1637967594370593E-4</v>
       </c>
       <c r="I19">
-        <v>7.4951123555981212E-4</v>
+        <v>7.4961405640390174E-4</v>
       </c>
       <c r="J19">
-        <v>5.8503358031640473E-5</v>
+        <v>5.8516892856338987E-5</v>
       </c>
       <c r="K19">
-        <v>-4.9752945056342687E-4</v>
+        <v>-4.9762042177596381E-4</v>
       </c>
       <c r="L19">
-        <v>9.400923045754404E-5</v>
+        <v>9.4085157568694899E-5</v>
       </c>
       <c r="M19">
-        <v>-2.7766656221246255E-4</v>
+        <v>-2.7769854888019547E-4</v>
       </c>
       <c r="N19">
-        <v>-5.7221584141210844E-4</v>
+        <v>-5.7233937837377919E-4</v>
       </c>
       <c r="O19">
-        <v>-1.5760250379026619E-5</v>
+        <v>-1.5741621053791399E-5</v>
       </c>
       <c r="P19">
-        <v>-4.1505052783768017E-4</v>
+        <v>-4.150214162990573E-4</v>
       </c>
       <c r="Q19">
-        <v>9.0699326156811096E-3</v>
+        <v>9.0704919941855238E-3</v>
       </c>
       <c r="R19">
-        <v>9.0017974790533792E-3</v>
+        <v>9.0023513306020011E-3</v>
       </c>
       <c r="S19">
-        <v>9.0445383081104308E-3</v>
+        <v>9.0451570456724292E-3</v>
       </c>
       <c r="T19">
-        <v>1.118989239300063E-2</v>
+        <v>1.1190532690968983E-2</v>
       </c>
       <c r="U19">
-        <v>9.0510845392375687E-3</v>
+        <v>9.0516311242653039E-3</v>
       </c>
       <c r="V19">
-        <v>8.9920949264979018E-3</v>
+        <v>8.9926376723614993E-3</v>
       </c>
       <c r="W19">
-        <v>-1.0625516236494319E-4</v>
+        <v>-1.062652756716239E-4</v>
       </c>
       <c r="X19">
-        <v>4.9932194704069895E-4</v>
+        <v>4.9934655680046892E-4</v>
       </c>
       <c r="Y19">
-        <v>-4.9229459033065845E-2</v>
+        <v>-4.9241013287212226E-2</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.2">
@@ -2207,76 +2207,76 @@
         <v>45</v>
       </c>
       <c r="B20">
-        <v>1.3913329566552706E-2</v>
+        <v>1.3903899726750308E-2</v>
       </c>
       <c r="C20">
-        <v>1.7084223439435857E-4</v>
+        <v>1.7082526894713007E-4</v>
       </c>
       <c r="D20">
-        <v>1.5359531350203626E-3</v>
+        <v>1.5363959200552016E-3</v>
       </c>
       <c r="E20">
-        <v>-1.1756102432024641E-5</v>
+        <v>-1.1759368423350442E-5</v>
       </c>
       <c r="F20">
-        <v>-4.5355422815356386E-4</v>
+        <v>-4.5367507191610562E-4</v>
       </c>
       <c r="G20">
-        <v>-3.9664521688407423E-4</v>
+        <v>-3.9680319285552434E-4</v>
       </c>
       <c r="H20">
-        <v>3.9982679822226882E-4</v>
+        <v>3.9994738844769274E-4</v>
       </c>
       <c r="I20">
-        <v>1.1488763990644686E-3</v>
+        <v>1.1489110652464554E-3</v>
       </c>
       <c r="J20">
-        <v>-1.2000629166868809E-4</v>
+        <v>-1.1998153827468688E-4</v>
       </c>
       <c r="K20">
-        <v>-2.9326280586914211E-4</v>
+        <v>-2.9336562375335655E-4</v>
       </c>
       <c r="L20">
-        <v>6.6740216175676281E-4</v>
+        <v>6.6737962189110682E-4</v>
       </c>
       <c r="M20">
-        <v>-2.0694007130019456E-4</v>
+        <v>-2.0693714069744689E-4</v>
       </c>
       <c r="N20">
-        <v>-6.0552285209864668E-4</v>
+        <v>-6.0557999574334734E-4</v>
       </c>
       <c r="O20">
-        <v>2.1922550568397123E-4</v>
+        <v>2.1926810676775339E-4</v>
       </c>
       <c r="P20">
-        <v>-1.5095874068804765E-4</v>
+        <v>-1.5085902177469494E-4</v>
       </c>
       <c r="Q20">
-        <v>9.1547272755910514E-3</v>
+        <v>9.1552732052523622E-3</v>
       </c>
       <c r="R20">
-        <v>9.1454367776697548E-3</v>
+        <v>9.1459742295460101E-3</v>
       </c>
       <c r="S20">
-        <v>9.2432011230562522E-3</v>
+        <v>9.2434957487699532E-3</v>
       </c>
       <c r="T20">
-        <v>9.0510845392375687E-3</v>
+        <v>9.0516311242653039E-3</v>
       </c>
       <c r="U20">
-        <v>1.1363421947333576E-2</v>
+        <v>1.1364039921707984E-2</v>
       </c>
       <c r="V20">
-        <v>9.0623684842705381E-3</v>
+        <v>9.0629107026245735E-3</v>
       </c>
       <c r="W20">
-        <v>-9.846589372160177E-5</v>
+        <v>-9.8489935979540616E-5</v>
       </c>
       <c r="X20">
-        <v>3.7416261987828752E-4</v>
+        <v>3.7435262496879253E-4</v>
       </c>
       <c r="Y20">
-        <v>-5.8015549226256874E-2</v>
+        <v>-5.8030625533849134E-2</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.2">
@@ -2284,76 +2284,76 @@
         <v>46</v>
       </c>
       <c r="B21">
-        <v>-8.8602525221107745E-2</v>
+        <v>-8.8597285494387903E-2</v>
       </c>
       <c r="C21">
-        <v>7.3688752101665222E-4</v>
+        <v>7.3700127852097672E-4</v>
       </c>
       <c r="D21">
-        <v>1.311178040704606E-3</v>
+        <v>1.3115773147099365E-3</v>
       </c>
       <c r="E21">
-        <v>-9.5504226583854651E-6</v>
+        <v>-9.5534058688779026E-6</v>
       </c>
       <c r="F21">
-        <v>-3.0286210280648825E-4</v>
+        <v>-3.0297118443714348E-4</v>
       </c>
       <c r="G21">
-        <v>-1.3583423428414898E-7</v>
+        <v>-2.9916415842864974E-7</v>
       </c>
       <c r="H21">
-        <v>7.2269423195278496E-4</v>
+        <v>7.2283373151140634E-4</v>
       </c>
       <c r="I21">
-        <v>8.6127751849141021E-4</v>
+        <v>8.6136483622944961E-4</v>
       </c>
       <c r="J21">
-        <v>-5.4107941612495207E-4</v>
+        <v>-5.4105670192655664E-4</v>
       </c>
       <c r="K21">
-        <v>-3.665445947828895E-4</v>
+        <v>-3.6664292016380662E-4</v>
       </c>
       <c r="L21">
-        <v>2.2231884965593772E-4</v>
+        <v>2.2238624859621223E-4</v>
       </c>
       <c r="M21">
-        <v>-3.0318246631905557E-4</v>
+        <v>-3.0323731948758768E-4</v>
       </c>
       <c r="N21">
-        <v>-4.9098548314260252E-4</v>
+        <v>-4.9110413306726599E-4</v>
       </c>
       <c r="O21">
-        <v>1.4198655100670964E-4</v>
+        <v>1.4195395439349588E-4</v>
       </c>
       <c r="P21">
-        <v>-5.1687455332126843E-4</v>
+        <v>-5.1684723191767741E-4</v>
       </c>
       <c r="Q21">
-        <v>9.0829188293393929E-3</v>
+        <v>9.0834763367899415E-3</v>
       </c>
       <c r="R21">
-        <v>9.0494880791689367E-3</v>
+        <v>9.050041919103656E-3</v>
       </c>
       <c r="S21">
-        <v>9.0666200942843347E-3</v>
+        <v>9.0671946737533524E-3</v>
       </c>
       <c r="T21">
-        <v>8.9920949264979018E-3</v>
+        <v>8.9926376723614993E-3</v>
       </c>
       <c r="U21">
-        <v>9.0623684842705381E-3</v>
+        <v>9.0629107026245735E-3</v>
       </c>
       <c r="V21">
-        <v>1.1580911401719345E-2</v>
+        <v>1.1581568265054531E-2</v>
       </c>
       <c r="W21">
-        <v>-1.0800137532225124E-4</v>
+        <v>-1.0801340622833765E-4</v>
       </c>
       <c r="X21">
-        <v>4.0621572446263542E-4</v>
+        <v>4.0624947794898119E-4</v>
       </c>
       <c r="Y21">
-        <v>-5.2227684954312625E-2</v>
+        <v>-5.2241337165325002E-2</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.2">
@@ -2361,76 +2361,76 @@
         <v>47</v>
       </c>
       <c r="B22">
-        <v>-4.0132273368803997E-2</v>
+        <v>-4.0144177783449593E-2</v>
       </c>
       <c r="C22">
-        <v>-7.9075494791071407E-5</v>
+        <v>-7.9151029552920537E-5</v>
       </c>
       <c r="D22">
-        <v>-6.0076720498855943E-5</v>
+        <v>-6.0050833899493589E-5</v>
       </c>
       <c r="E22">
-        <v>3.8261469408698318E-7</v>
+        <v>3.8245581064729384E-7</v>
       </c>
       <c r="F22">
-        <v>-6.8679618888095595E-5</v>
+        <v>-6.8673621271978305E-5</v>
       </c>
       <c r="G22">
-        <v>-7.7953170142740572E-5</v>
+        <v>-7.7964990227346112E-5</v>
       </c>
       <c r="H22">
-        <v>-5.7591349200144994E-5</v>
+        <v>-5.7591344688285846E-5</v>
       </c>
       <c r="I22">
-        <v>2.6254312530237228E-5</v>
+        <v>2.6233599425287853E-5</v>
       </c>
       <c r="J22">
-        <v>1.2991590171457755E-4</v>
+        <v>1.2991010158539505E-4</v>
       </c>
       <c r="K22">
-        <v>4.1880366462488609E-5</v>
+        <v>4.1844362811155984E-5</v>
       </c>
       <c r="L22">
-        <v>-2.6329307756217495E-5</v>
+        <v>-2.6400060074644198E-5</v>
       </c>
       <c r="M22">
-        <v>2.2234038349129201E-5</v>
+        <v>2.2241903466405089E-5</v>
       </c>
       <c r="N22">
-        <v>6.5166316608058637E-5</v>
+        <v>6.5200146862335402E-5</v>
       </c>
       <c r="O22">
-        <v>5.4496578314349765E-5</v>
+        <v>5.4530800481503681E-5</v>
       </c>
       <c r="P22">
-        <v>5.0756281960641033E-5</v>
+        <v>5.0843511466612946E-5</v>
       </c>
       <c r="Q22">
-        <v>-9.3325764638094708E-5</v>
+        <v>-9.3347218570766438E-5</v>
       </c>
       <c r="R22">
-        <v>-7.3405906387087366E-5</v>
+        <v>-7.3419817233912727E-5</v>
       </c>
       <c r="S22">
-        <v>-1.3019832926160603E-4</v>
+        <v>-1.3035026285169256E-4</v>
       </c>
       <c r="T22">
-        <v>-1.0625516236494319E-4</v>
+        <v>-1.062652756716239E-4</v>
       </c>
       <c r="U22">
-        <v>-9.846589372160177E-5</v>
+        <v>-9.8489935979540616E-5</v>
       </c>
       <c r="V22">
-        <v>-1.0800137532225124E-4</v>
+        <v>-1.0801340622833765E-4</v>
       </c>
       <c r="W22">
-        <v>6.9904220786336561E-5</v>
+        <v>6.990424412946526E-5</v>
       </c>
       <c r="X22">
-        <v>-4.9824852550285929E-4</v>
+        <v>-4.9818190918030308E-4</v>
       </c>
       <c r="Y22">
-        <v>1.3664630881055351E-3</v>
+        <v>1.3654990943034462E-3</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.2">
@@ -2438,76 +2438,76 @@
         <v>48</v>
       </c>
       <c r="B23">
-        <v>0.20969464185683462</v>
+        <v>0.20983889692407459</v>
       </c>
       <c r="C23">
-        <v>1.7967249437391601E-4</v>
+        <v>1.8073783339145636E-4</v>
       </c>
       <c r="D23">
-        <v>2.0807677731464469E-4</v>
+        <v>2.0734956898646462E-4</v>
       </c>
       <c r="E23">
-        <v>-1.0672267744552206E-6</v>
+        <v>-1.0624288981172418E-6</v>
       </c>
       <c r="F23">
-        <v>5.8318881328912886E-4</v>
+        <v>5.8315810217423464E-4</v>
       </c>
       <c r="G23">
-        <v>8.560236571222013E-4</v>
+        <v>8.561282207184967E-4</v>
       </c>
       <c r="H23">
-        <v>3.7094442234440294E-4</v>
+        <v>3.7086542311981865E-4</v>
       </c>
       <c r="I23">
-        <v>6.8865382215900191E-5</v>
+        <v>6.9311461262675693E-5</v>
       </c>
       <c r="J23">
-        <v>-7.6411163723786452E-4</v>
+        <v>-7.638186510975295E-4</v>
       </c>
       <c r="K23">
-        <v>-1.8097421900054901E-4</v>
+        <v>-1.8034555545380811E-4</v>
       </c>
       <c r="L23">
-        <v>4.0170218584037703E-4</v>
+        <v>4.0281613969062177E-4</v>
       </c>
       <c r="M23">
-        <v>1.6975790142951044E-4</v>
+        <v>1.6971353593052494E-4</v>
       </c>
       <c r="N23">
-        <v>-7.823868714326894E-5</v>
+        <v>-7.8600624646599053E-5</v>
       </c>
       <c r="O23">
-        <v>-5.4112602704414411E-5</v>
+        <v>-5.4496344426982826E-5</v>
       </c>
       <c r="P23">
-        <v>1.3244538250348713E-4</v>
+        <v>1.3112722604240071E-4</v>
       </c>
       <c r="Q23">
-        <v>3.2880682921118329E-4</v>
+        <v>3.2897643488462736E-4</v>
       </c>
       <c r="R23">
-        <v>2.9141810043692862E-4</v>
+        <v>2.9153687380506239E-4</v>
       </c>
       <c r="S23">
-        <v>3.89336298102806E-4</v>
+        <v>3.9156635859698401E-4</v>
       </c>
       <c r="T23">
-        <v>4.9932194704069895E-4</v>
+        <v>4.9934655680046892E-4</v>
       </c>
       <c r="U23">
-        <v>3.7416261987828752E-4</v>
+        <v>3.7435262496879253E-4</v>
       </c>
       <c r="V23">
-        <v>4.0621572446263542E-4</v>
+        <v>4.0624947794898119E-4</v>
       </c>
       <c r="W23">
-        <v>-4.9824852550285929E-4</v>
+        <v>-4.9818190918030308E-4</v>
       </c>
       <c r="X23">
-        <v>5.8725078948183148E-3</v>
+        <v>5.871367293781727E-3</v>
       </c>
       <c r="Y23">
-        <v>-4.2879551668433824E-3</v>
+        <v>-4.2629935029920366E-3</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.2">
@@ -2515,76 +2515,76 @@
         <v>49</v>
       </c>
       <c r="B24">
-        <v>-0.4867131076385427</v>
+        <v>-0.48889273775295861</v>
       </c>
       <c r="C24">
-        <v>-1.6786004743844087E-2</v>
+        <v>-1.6808861133236104E-2</v>
       </c>
       <c r="D24">
-        <v>-0.2606092566568865</v>
+        <v>-0.26068014295401309</v>
       </c>
       <c r="E24">
-        <v>2.0807988194184255E-3</v>
+        <v>2.0813413306304922E-3</v>
       </c>
       <c r="F24">
-        <v>0.18104754929897471</v>
+        <v>0.18106981320598359</v>
       </c>
       <c r="G24">
-        <v>0.16648058498717488</v>
+        <v>0.16650170403807674</v>
       </c>
       <c r="H24">
-        <v>-1.4598934105944851E-2</v>
+        <v>-1.4602595817448792E-2</v>
       </c>
       <c r="I24">
-        <v>-2.8443720688763968E-2</v>
+        <v>-2.8459061067412694E-2</v>
       </c>
       <c r="J24">
-        <v>-0.15992006007432602</v>
+        <v>-0.15992406178289431</v>
       </c>
       <c r="K24">
-        <v>-6.0027937355755789E-3</v>
+        <v>-6.0137935834939371E-3</v>
       </c>
       <c r="L24">
-        <v>-1.6766972410609253E-2</v>
+        <v>-1.6787752027816405E-2</v>
       </c>
       <c r="M24">
-        <v>-1.5544252096871589E-2</v>
+        <v>-1.5546372834418024E-2</v>
       </c>
       <c r="N24">
-        <v>-2.4154787573449715E-2</v>
+        <v>-2.4154563808679808E-2</v>
       </c>
       <c r="O24">
-        <v>-3.4910163465996208E-2</v>
+        <v>-3.4916024665207573E-2</v>
       </c>
       <c r="P24">
-        <v>1.484495010740073E-2</v>
+        <v>1.4871309672353936E-2</v>
       </c>
       <c r="Q24">
-        <v>-3.5531996191273785E-2</v>
+        <v>-3.5544470176122403E-2</v>
       </c>
       <c r="R24">
-        <v>-5.5972733833845739E-2</v>
+        <v>-5.5988083672354416E-2</v>
       </c>
       <c r="S24">
-        <v>-5.3228862965667229E-2</v>
+        <v>-5.3277359124532006E-2</v>
       </c>
       <c r="T24">
-        <v>-4.9229459033065845E-2</v>
+        <v>-4.9241013287212226E-2</v>
       </c>
       <c r="U24">
-        <v>-5.8015549226256874E-2</v>
+        <v>-5.8030625533849134E-2</v>
       </c>
       <c r="V24">
-        <v>-5.2227684954312625E-2</v>
+        <v>-5.2241337165325002E-2</v>
       </c>
       <c r="W24">
-        <v>1.3664630881055351E-3</v>
+        <v>1.3654990943034462E-3</v>
       </c>
       <c r="X24">
-        <v>-4.2879551668433824E-3</v>
+        <v>-4.2629935029920366E-3</v>
       </c>
       <c r="Y24">
-        <v>8.1937386786608073</v>
+        <v>8.1960807677630143</v>
       </c>
     </row>
   </sheetData>
@@ -2700,97 +2700,97 @@
         <v>27</v>
       </c>
       <c r="B2">
-        <v>0.48725317902561055</v>
+        <v>0.46828156083912664</v>
       </c>
       <c r="C2">
-        <v>1.4023943484551759E-3</v>
+        <v>1.317933254590131E-3</v>
       </c>
       <c r="D2">
-        <v>2.4287219891213941E-4</v>
+        <v>2.6351995467891723E-4</v>
       </c>
       <c r="E2">
-        <v>-1.7429664898839259E-6</v>
+        <v>-1.8949087682106189E-6</v>
       </c>
       <c r="F2">
-        <v>1.376122337789315E-4</v>
+        <v>1.6125286979863651E-4</v>
       </c>
       <c r="G2">
-        <v>1.0619743153305071E-4</v>
+        <v>1.4019254357231393E-4</v>
       </c>
       <c r="H2">
-        <v>5.7210452920590894E-5</v>
+        <v>5.2905596644327236E-5</v>
       </c>
       <c r="I2">
-        <v>-9.4386538690615702E-6</v>
+        <v>-1.7529261826953199E-5</v>
       </c>
       <c r="J2">
-        <v>-2.6256428078038848E-4</v>
+        <v>-2.2022144852791754E-4</v>
       </c>
       <c r="K2">
-        <v>6.5929083599635622E-4</v>
+        <v>6.6123127470460355E-4</v>
       </c>
       <c r="L2">
-        <v>-3.8218426804469499E-6</v>
+        <v>-4.8913121880072967E-5</v>
       </c>
       <c r="M2">
-        <v>5.6139993627165761E-5</v>
+        <v>6.0159217809408101E-5</v>
       </c>
       <c r="N2">
-        <v>8.5235100534041805E-5</v>
+        <v>7.9045820025245081E-5</v>
       </c>
       <c r="O2">
-        <v>1.5412556938098774E-4</v>
+        <v>1.1942233552537671E-4</v>
       </c>
       <c r="P2">
-        <v>1.2724761698980827E-4</v>
+        <v>1.1547551740743927E-4</v>
       </c>
       <c r="Q2">
-        <v>-4.1912642414828775E-4</v>
+        <v>-4.2326165195228981E-4</v>
       </c>
       <c r="R2">
-        <v>7.8794856558135075E-4</v>
+        <v>6.7479034677417641E-4</v>
       </c>
       <c r="S2">
-        <v>-2.2511761873168627E-4</v>
+        <v>-2.9874274436318573E-4</v>
       </c>
       <c r="T2">
-        <v>-2.9401555776640111E-4</v>
+        <v>-1.2882799477750343E-4</v>
       </c>
       <c r="U2">
-        <v>-5.993302321163045E-5</v>
+        <v>-4.3888650747473957E-5</v>
       </c>
       <c r="V2">
-        <v>1.2888864281596204E-4</v>
+        <v>1.1905073398588788E-4</v>
       </c>
       <c r="W2">
-        <v>1.3345126425377005E-4</v>
+        <v>1.2246231362551363E-4</v>
       </c>
       <c r="X2">
-        <v>1.3106945136016793E-4</v>
+        <v>1.1841634004566988E-4</v>
       </c>
       <c r="Y2">
-        <v>7.3175256894544811E-5</v>
+        <v>5.3230216531714952E-5</v>
       </c>
       <c r="Z2">
-        <v>1.6233783158817053E-4</v>
+        <v>1.3865831618414337E-4</v>
       </c>
       <c r="AA2">
-        <v>1.2388701297518954E-4</v>
+        <v>1.0818608546091598E-4</v>
       </c>
       <c r="AB2">
-        <v>2.0847743153764003E-5</v>
+        <v>6.904116465748897E-6</v>
       </c>
       <c r="AC2">
-        <v>3.9004104743595812E-6</v>
+        <v>2.5353164022284618E-6</v>
       </c>
       <c r="AD2">
-        <v>-3.2800634213444929E-5</v>
+        <v>-2.3776572513753403E-5</v>
       </c>
       <c r="AE2">
-        <v>-1.6362622963248278E-5</v>
+        <v>-6.2605724090432444E-6</v>
       </c>
       <c r="AF2">
-        <v>-9.8211081736195426E-3</v>
+        <v>-1.0362830863151266E-2</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.2">
@@ -2798,97 +2798,97 @@
         <v>28</v>
       </c>
       <c r="B3">
-        <v>-0.12095583018363691</v>
+        <v>-0.13305849153237556</v>
       </c>
       <c r="C3">
-        <v>2.4287219891213941E-4</v>
+        <v>2.6351995467891723E-4</v>
       </c>
       <c r="D3">
-        <v>3.9527956041074744E-3</v>
+        <v>3.9911821609429216E-3</v>
       </c>
       <c r="E3">
-        <v>-3.2281745429263941E-5</v>
+        <v>-3.2617005872278605E-5</v>
       </c>
       <c r="F3">
-        <v>-3.1197645712481847E-3</v>
+        <v>-3.0743431384759601E-3</v>
       </c>
       <c r="G3">
-        <v>-2.8849964840070713E-3</v>
+        <v>-2.8461126722139837E-3</v>
       </c>
       <c r="H3">
-        <v>-1.2630467781720063E-5</v>
+        <v>-1.6699693319072303E-5</v>
       </c>
       <c r="I3">
-        <v>-3.4558698066657068E-5</v>
+        <v>-3.889118890994421E-5</v>
       </c>
       <c r="J3">
-        <v>2.9619189174806548E-3</v>
+        <v>2.9036669500218798E-3</v>
       </c>
       <c r="K3">
-        <v>-1.1510488516653424E-4</v>
+        <v>-1.0827520633596363E-4</v>
       </c>
       <c r="L3">
-        <v>6.4350311175299414E-4</v>
+        <v>6.2770874967373914E-4</v>
       </c>
       <c r="M3">
-        <v>1.0613943597936881E-4</v>
+        <v>9.6512158729210318E-5</v>
       </c>
       <c r="N3">
-        <v>-1.3100128436809369E-4</v>
+        <v>-1.3184482315622015E-4</v>
       </c>
       <c r="O3">
-        <v>-8.7506815788145585E-5</v>
+        <v>-8.1319415389565462E-5</v>
       </c>
       <c r="P3">
-        <v>-1.8659072133111153E-4</v>
+        <v>-1.8703019726721941E-4</v>
       </c>
       <c r="Q3">
-        <v>-2.0851444792344175E-4</v>
+        <v>-2.0887139217288945E-4</v>
       </c>
       <c r="R3">
-        <v>1.459489014538802E-4</v>
+        <v>3.3549961559651859E-4</v>
       </c>
       <c r="S3">
-        <v>-2.7466335224897356E-4</v>
+        <v>-2.1927914050563421E-4</v>
       </c>
       <c r="T3">
-        <v>-5.5695224003948773E-5</v>
+        <v>-4.7693563485250515E-4</v>
       </c>
       <c r="U3">
-        <v>-8.3519287051491732E-5</v>
+        <v>-8.7403088317757407E-5</v>
       </c>
       <c r="V3">
-        <v>-5.6131187514539549E-5</v>
+        <v>-3.9630962419177906E-5</v>
       </c>
       <c r="W3">
-        <v>-6.7465016128392952E-5</v>
+        <v>-5.6088664379352893E-5</v>
       </c>
       <c r="X3">
-        <v>9.7113256569275608E-6</v>
+        <v>2.3621705846563201E-5</v>
       </c>
       <c r="Y3">
-        <v>-2.7242360513751035E-5</v>
+        <v>1.2143799227627705E-6</v>
       </c>
       <c r="Z3">
-        <v>6.6150673977263819E-5</v>
+        <v>6.9302106205107461E-5</v>
       </c>
       <c r="AA3">
-        <v>7.5648819666561395E-5</v>
+        <v>9.9680704468585457E-5</v>
       </c>
       <c r="AB3">
-        <v>-2.1534158072024356E-5</v>
+        <v>-7.81267756554474E-6</v>
       </c>
       <c r="AC3">
-        <v>7.954545316162789E-6</v>
+        <v>7.9028390590845342E-6</v>
       </c>
       <c r="AD3">
-        <v>-2.3302600625496606E-5</v>
+        <v>-3.6344385382469646E-5</v>
       </c>
       <c r="AE3">
-        <v>-1.1881164137514388E-4</v>
+        <v>-1.1806164469294056E-4</v>
       </c>
       <c r="AF3">
-        <v>-0.12073367643394517</v>
+        <v>-0.12185803817751206</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.2">
@@ -2896,97 +2896,97 @@
         <v>29</v>
       </c>
       <c r="B4">
-        <v>2.4479032100635924E-3</v>
+        <v>2.5587336153346401E-3</v>
       </c>
       <c r="C4">
-        <v>-1.7429664898839259E-6</v>
+        <v>-1.8949087682106189E-6</v>
       </c>
       <c r="D4">
-        <v>-3.2281745429263941E-5</v>
+        <v>-3.2617005872278605E-5</v>
       </c>
       <c r="E4">
-        <v>2.6538923691489421E-7</v>
+        <v>2.6828608101512658E-7</v>
       </c>
       <c r="F4">
-        <v>2.6923308276625025E-5</v>
+        <v>2.6529668322655101E-5</v>
       </c>
       <c r="G4">
-        <v>2.4837826352108803E-5</v>
+        <v>2.4491446781841578E-5</v>
       </c>
       <c r="H4">
-        <v>1.4152207595901491E-7</v>
+        <v>1.7343125147841508E-7</v>
       </c>
       <c r="I4">
-        <v>1.5420584067691331E-7</v>
+        <v>1.9391287751345271E-7</v>
       </c>
       <c r="J4">
-        <v>-2.6486276980159339E-5</v>
+        <v>-2.6012675408419359E-5</v>
       </c>
       <c r="K4">
-        <v>8.1217854129133488E-7</v>
+        <v>7.5152924264724531E-7</v>
       </c>
       <c r="L4">
-        <v>-5.1681576350768416E-6</v>
+        <v>-5.0196387272318454E-6</v>
       </c>
       <c r="M4">
-        <v>-9.525496043867143E-7</v>
+        <v>-8.7456991016698362E-7</v>
       </c>
       <c r="N4">
-        <v>9.8398391760685445E-7</v>
+        <v>9.9457475663084313E-7</v>
       </c>
       <c r="O4">
-        <v>6.4323715881421417E-7</v>
+        <v>6.0846141394254764E-7</v>
       </c>
       <c r="P4">
-        <v>1.4353804087846752E-6</v>
+        <v>1.4432278013997931E-6</v>
       </c>
       <c r="Q4">
-        <v>1.8037157605078595E-6</v>
+        <v>1.8094565872085687E-6</v>
       </c>
       <c r="R4">
-        <v>-1.4848012337321137E-6</v>
+        <v>-3.0130221747405795E-6</v>
       </c>
       <c r="S4">
-        <v>2.2750375750720358E-6</v>
+        <v>1.6623732069506259E-6</v>
       </c>
       <c r="T4">
-        <v>3.0226665811251352E-7</v>
+        <v>3.984075981260774E-6</v>
       </c>
       <c r="U4">
-        <v>6.0524281928056372E-7</v>
+        <v>6.3141847957079455E-7</v>
       </c>
       <c r="V4">
-        <v>4.9716219899972034E-7</v>
+        <v>3.6666186084683935E-7</v>
       </c>
       <c r="W4">
-        <v>6.662090024405409E-7</v>
+        <v>5.8161907022155884E-7</v>
       </c>
       <c r="X4">
-        <v>1.38548718467261E-7</v>
+        <v>3.2856827072145524E-8</v>
       </c>
       <c r="Y4">
-        <v>2.4592369572416545E-7</v>
+        <v>2.6728374349146034E-8</v>
       </c>
       <c r="Z4">
-        <v>-3.6777087458663565E-7</v>
+        <v>-3.7698988840557685E-7</v>
       </c>
       <c r="AA4">
-        <v>-4.9821489612415087E-7</v>
+        <v>-6.8591618313773562E-7</v>
       </c>
       <c r="AB4">
-        <v>1.7642125534409045E-7</v>
+        <v>7.4841568163490618E-8</v>
       </c>
       <c r="AC4">
-        <v>-8.8276431555639443E-8</v>
+        <v>-8.6962150874775284E-8</v>
       </c>
       <c r="AD4">
-        <v>8.8175852370998235E-8</v>
+        <v>1.9120497312020849E-7</v>
       </c>
       <c r="AE4">
-        <v>8.6192674716333495E-7</v>
+        <v>8.4897259201063401E-7</v>
       </c>
       <c r="AF4">
-        <v>9.8004909252421158E-4</v>
+        <v>9.899097002269196E-4</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.2">
@@ -2994,97 +2994,97 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>1.387842281524813</v>
+        <v>1.3694363247794523</v>
       </c>
       <c r="C5">
-        <v>1.376122337789315E-4</v>
+        <v>1.6125286979863651E-4</v>
       </c>
       <c r="D5">
-        <v>-3.1197645712481847E-3</v>
+        <v>-3.0743431384759601E-3</v>
       </c>
       <c r="E5">
-        <v>2.6923308276625025E-5</v>
+        <v>2.6529668322655101E-5</v>
       </c>
       <c r="F5">
-        <v>6.5662181812897007E-3</v>
+        <v>6.6015099205308618E-3</v>
       </c>
       <c r="G5">
-        <v>4.4284622041411772E-3</v>
+        <v>4.4686807341489318E-3</v>
       </c>
       <c r="H5">
-        <v>3.6955261712149322E-5</v>
+        <v>3.0361065631737474E-5</v>
       </c>
       <c r="I5">
-        <v>-8.1903891452066169E-5</v>
+        <v>-9.1843111118318846E-5</v>
       </c>
       <c r="J5">
-        <v>-6.1118219882119601E-3</v>
+        <v>-6.1390699349622921E-3</v>
       </c>
       <c r="K5">
-        <v>3.9441223486048546E-5</v>
+        <v>3.9967890983191867E-5</v>
       </c>
       <c r="L5">
-        <v>2.8054979351586559E-4</v>
+        <v>2.3842254359761166E-4</v>
       </c>
       <c r="M5">
-        <v>-1.5832672271775226E-4</v>
+        <v>-1.6210494769831538E-4</v>
       </c>
       <c r="N5">
-        <v>-6.0067415039244745E-6</v>
+        <v>-1.0757101683266101E-5</v>
       </c>
       <c r="O5">
-        <v>-2.0086948044259305E-5</v>
+        <v>-2.5411319357183416E-5</v>
       </c>
       <c r="P5">
-        <v>1.3679014965022485E-4</v>
+        <v>1.2613560276452523E-4</v>
       </c>
       <c r="Q5">
-        <v>1.7392951375968559E-4</v>
+        <v>1.7638354082061833E-4</v>
       </c>
       <c r="R5">
-        <v>3.5359481747339761E-4</v>
+        <v>5.334614974869048E-4</v>
       </c>
       <c r="S5">
-        <v>-5.0320506515459662E-4</v>
+        <v>-1.0446205190958319E-3</v>
       </c>
       <c r="T5">
-        <v>-9.331374014842457E-4</v>
+        <v>-5.1706008620285709E-4</v>
       </c>
       <c r="U5">
-        <v>1.3152189557902143E-5</v>
+        <v>2.754369199701838E-6</v>
       </c>
       <c r="V5">
-        <v>6.306579232923798E-5</v>
+        <v>7.7288522244261734E-5</v>
       </c>
       <c r="W5">
-        <v>1.4470626196641523E-4</v>
+        <v>1.5317646621142156E-4</v>
       </c>
       <c r="X5">
-        <v>1.435653601878778E-4</v>
+        <v>1.4883785957289786E-4</v>
       </c>
       <c r="Y5">
-        <v>4.6333843239345501E-5</v>
+        <v>6.0600137503937987E-5</v>
       </c>
       <c r="Z5">
-        <v>9.461183932895495E-5</v>
+        <v>1.030180871239017E-4</v>
       </c>
       <c r="AA5">
-        <v>-1.5450365248449727E-5</v>
+        <v>-2.615179518489566E-6</v>
       </c>
       <c r="AB5">
-        <v>2.2784830465763517E-5</v>
+        <v>2.8694224247772376E-5</v>
       </c>
       <c r="AC5">
-        <v>-2.562358652305935E-5</v>
+        <v>-2.65208927625434E-5</v>
       </c>
       <c r="AD5">
-        <v>1.9954943073725862E-5</v>
+        <v>1.2217974530180642E-5</v>
       </c>
       <c r="AE5">
-        <v>4.1295043706562895E-5</v>
+        <v>4.8669687654673971E-5</v>
       </c>
       <c r="AF5">
-        <v>9.0213049877748031E-2</v>
+        <v>8.891250148184171E-2</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.2">
@@ -3092,97 +3092,97 @@
         <v>31</v>
       </c>
       <c r="B6">
-        <v>1.1109799283611093</v>
+        <v>1.1027322902605532</v>
       </c>
       <c r="C6">
-        <v>1.0619743153305071E-4</v>
+        <v>1.4019254357231393E-4</v>
       </c>
       <c r="D6">
-        <v>-2.8849964840070713E-3</v>
+        <v>-2.8461126722139837E-3</v>
       </c>
       <c r="E6">
-        <v>2.4837826352108803E-5</v>
+        <v>2.4491446781841578E-5</v>
       </c>
       <c r="F6">
-        <v>4.4284622041411772E-3</v>
+        <v>4.4686807341489318E-3</v>
       </c>
       <c r="G6">
-        <v>7.2061004302717072E-3</v>
+        <v>7.2606191181155584E-3</v>
       </c>
       <c r="H6">
-        <v>-2.4395485181322716E-5</v>
+        <v>-2.8816378452953847E-5</v>
       </c>
       <c r="I6">
-        <v>-6.8580656132906197E-5</v>
+        <v>-7.6316453111400714E-5</v>
       </c>
       <c r="J6">
-        <v>-5.3275577779112945E-3</v>
+        <v>-5.3722389513483695E-3</v>
       </c>
       <c r="K6">
-        <v>3.0970564203409642E-5</v>
+        <v>3.3980678954891735E-5</v>
       </c>
       <c r="L6">
-        <v>2.3004361085097666E-5</v>
+        <v>1.0631622524553269E-6</v>
       </c>
       <c r="M6">
-        <v>-9.238939590995067E-5</v>
+        <v>-8.7598100233475529E-5</v>
       </c>
       <c r="N6">
-        <v>6.8097054835612649E-5</v>
+        <v>6.6364127081302259E-5</v>
       </c>
       <c r="O6">
-        <v>2.4205367652443879E-5</v>
+        <v>2.8065530651967974E-5</v>
       </c>
       <c r="P6">
-        <v>1.5193521622598218E-4</v>
+        <v>1.5498686885990869E-4</v>
       </c>
       <c r="Q6">
-        <v>1.6886192199491246E-4</v>
+        <v>1.7383092497874272E-4</v>
       </c>
       <c r="R6">
-        <v>1.9957995172552832E-4</v>
+        <v>3.9766183659994004E-4</v>
       </c>
       <c r="S6">
-        <v>-4.1744464422944529E-4</v>
+        <v>-9.321461225941137E-4</v>
       </c>
       <c r="T6">
-        <v>-8.0820040715199812E-4</v>
+        <v>-5.128743988593509E-4</v>
       </c>
       <c r="U6">
-        <v>4.906263521241034E-5</v>
+        <v>3.5950533332993959E-5</v>
       </c>
       <c r="V6">
-        <v>1.0101082290138452E-4</v>
+        <v>1.1735735905567344E-4</v>
       </c>
       <c r="W6">
-        <v>5.7965831031604742E-5</v>
+        <v>5.5624645884946866E-5</v>
       </c>
       <c r="X6">
-        <v>-2.5862671698198558E-6</v>
+        <v>-6.1543642715794489E-6</v>
       </c>
       <c r="Y6">
-        <v>-4.3240048640454457E-5</v>
+        <v>-4.5158532275312371E-5</v>
       </c>
       <c r="Z6">
-        <v>-5.6786065210284731E-5</v>
+        <v>-5.2784243551179388E-5</v>
       </c>
       <c r="AA6">
-        <v>-1.5583452042863821E-4</v>
+        <v>-1.5847080904152558E-4</v>
       </c>
       <c r="AB6">
-        <v>-5.9981935310825935E-5</v>
+        <v>-6.1231019737612719E-5</v>
       </c>
       <c r="AC6">
-        <v>-2.1539599776004468E-5</v>
+        <v>-2.1592680214786318E-5</v>
       </c>
       <c r="AD6">
-        <v>-5.2777360766777942E-5</v>
+        <v>-5.6279052144281305E-5</v>
       </c>
       <c r="AE6">
-        <v>4.4807082904333578E-5</v>
+        <v>4.852695168872101E-5</v>
       </c>
       <c r="AF6">
-        <v>8.3696769059056486E-2</v>
+        <v>8.2591000956276639E-2</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.2">
@@ -3190,97 +3190,97 @@
         <v>32</v>
       </c>
       <c r="B7">
-        <v>4.0707480896544523E-2</v>
+        <v>3.905795925593878E-2</v>
       </c>
       <c r="C7">
-        <v>5.7210452920590894E-5</v>
+        <v>5.2905596644327236E-5</v>
       </c>
       <c r="D7">
-        <v>-1.2630467781720063E-5</v>
+        <v>-1.6699693319072303E-5</v>
       </c>
       <c r="E7">
-        <v>1.4152207595901491E-7</v>
+        <v>1.7343125147841508E-7</v>
       </c>
       <c r="F7">
-        <v>3.6955261712149322E-5</v>
+        <v>3.0361065631737474E-5</v>
       </c>
       <c r="G7">
-        <v>-2.4395485181322716E-5</v>
+        <v>-2.8816378452953847E-5</v>
       </c>
       <c r="H7">
-        <v>1.8008350324867231E-3</v>
+        <v>1.8053396591577989E-3</v>
       </c>
       <c r="I7">
-        <v>1.0046658368847616E-3</v>
+        <v>1.0075705447430221E-3</v>
       </c>
       <c r="J7">
-        <v>6.4020646173056171E-5</v>
+        <v>7.096464307682418E-5</v>
       </c>
       <c r="K7">
-        <v>-9.276549605458094E-5</v>
+        <v>-9.5817491673552506E-5</v>
       </c>
       <c r="L7">
-        <v>-7.6583277711712481E-5</v>
+        <v>-7.6062093547468929E-5</v>
       </c>
       <c r="M7">
-        <v>-6.3015617022360538E-6</v>
+        <v>-5.3617857572944134E-6</v>
       </c>
       <c r="N7">
-        <v>-1.9504066919595633E-5</v>
+        <v>-2.4116853083533811E-5</v>
       </c>
       <c r="O7">
-        <v>-3.8522040883761852E-5</v>
+        <v>-4.6698585106363228E-5</v>
       </c>
       <c r="P7">
-        <v>3.4026502123803213E-4</v>
+        <v>3.3649144332574543E-4</v>
       </c>
       <c r="Q7">
-        <v>5.6725075104128005E-5</v>
+        <v>5.6744577319602142E-5</v>
       </c>
       <c r="R7">
-        <v>4.3471605720680405E-5</v>
+        <v>2.7001880979072185E-5</v>
       </c>
       <c r="S7">
-        <v>-2.2661785328908856E-5</v>
+        <v>-3.5516595288080091E-5</v>
       </c>
       <c r="T7">
-        <v>-5.7469043889428104E-5</v>
+        <v>3.8815558325247458E-5</v>
       </c>
       <c r="U7">
-        <v>-1.4416054766716179E-5</v>
+        <v>-1.5690043718079186E-5</v>
       </c>
       <c r="V7">
-        <v>5.7839320015892922E-5</v>
+        <v>5.4984855633013877E-5</v>
       </c>
       <c r="W7">
-        <v>8.9744080367285635E-5</v>
+        <v>8.4693385359520821E-5</v>
       </c>
       <c r="X7">
-        <v>1.0561664733128601E-4</v>
+        <v>1.0227449040021161E-4</v>
       </c>
       <c r="Y7">
-        <v>1.253563055107607E-4</v>
+        <v>1.2191385129444571E-4</v>
       </c>
       <c r="Z7">
-        <v>1.4931859647228504E-4</v>
+        <v>1.4436710684840757E-4</v>
       </c>
       <c r="AA7">
-        <v>9.1864724172606199E-5</v>
+        <v>8.724676520181551E-5</v>
       </c>
       <c r="AB7">
-        <v>1.2677015335271161E-4</v>
+        <v>1.216628739850352E-4</v>
       </c>
       <c r="AC7">
-        <v>-1.2375192441873928E-7</v>
+        <v>-7.5258779324508928E-8</v>
       </c>
       <c r="AD7">
-        <v>6.6943520880069843E-6</v>
+        <v>5.0381547394161199E-6</v>
       </c>
       <c r="AE7">
-        <v>-7.5394154640962691E-6</v>
+        <v>-8.4157082835525834E-6</v>
       </c>
       <c r="AF7">
-        <v>-8.8888510185315336E-4</v>
+        <v>-7.4842086026358917E-4</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.2">
@@ -3288,97 +3288,97 @@
         <v>33</v>
       </c>
       <c r="B8">
-        <v>-1.4699788925427861E-2</v>
+        <v>-1.5066034547928358E-2</v>
       </c>
       <c r="C8">
-        <v>-9.4386538690615702E-6</v>
+        <v>-1.7529261826953199E-5</v>
       </c>
       <c r="D8">
-        <v>-3.4558698066657068E-5</v>
+        <v>-3.889118890994421E-5</v>
       </c>
       <c r="E8">
-        <v>1.5420584067691331E-7</v>
+        <v>1.9391287751345271E-7</v>
       </c>
       <c r="F8">
-        <v>-8.1903891452066169E-5</v>
+        <v>-9.1843111118318846E-5</v>
       </c>
       <c r="G8">
-        <v>-6.8580656132906197E-5</v>
+        <v>-7.6316453111400714E-5</v>
       </c>
       <c r="H8">
-        <v>1.0046658368847616E-3</v>
+        <v>1.0075705447430221E-3</v>
       </c>
       <c r="I8">
-        <v>1.4502975289868681E-3</v>
+        <v>1.4538949950025457E-3</v>
       </c>
       <c r="J8">
-        <v>1.6133381018938503E-4</v>
+        <v>1.7104066956493162E-4</v>
       </c>
       <c r="K8">
-        <v>-1.436979955878347E-4</v>
+        <v>-1.4644758320911014E-4</v>
       </c>
       <c r="L8">
-        <v>-3.1695056225983492E-5</v>
+        <v>-2.7988680859991437E-5</v>
       </c>
       <c r="M8">
-        <v>3.4720913991057934E-5</v>
+        <v>3.6893921217557126E-5</v>
       </c>
       <c r="N8">
-        <v>8.4960994955118592E-5</v>
+        <v>8.2605719810949547E-5</v>
       </c>
       <c r="O8">
-        <v>1.3391735913121093E-4</v>
+        <v>1.2999567124037076E-4</v>
       </c>
       <c r="P8">
-        <v>5.6354778732926631E-4</v>
+        <v>5.6161171625847804E-4</v>
       </c>
       <c r="Q8">
-        <v>1.3093487704130687E-5</v>
+        <v>1.3745747940808854E-5</v>
       </c>
       <c r="R8">
-        <v>-1.3775472791114062E-5</v>
+        <v>-5.0477405441336413E-5</v>
       </c>
       <c r="S8">
-        <v>6.6612424270576779E-5</v>
+        <v>1.1539642106720392E-4</v>
       </c>
       <c r="T8">
-        <v>7.8908114838060215E-5</v>
+        <v>6.8919768821180149E-5</v>
       </c>
       <c r="U8">
-        <v>1.5554265670880837E-6</v>
+        <v>3.1646010236562169E-6</v>
       </c>
       <c r="V8">
-        <v>-1.5639148942113326E-6</v>
+        <v>-3.3708711019775415E-6</v>
       </c>
       <c r="W8">
-        <v>-1.511264226981817E-4</v>
+        <v>-1.5199253212248224E-4</v>
       </c>
       <c r="X8">
-        <v>-1.1572734246231332E-4</v>
+        <v>-1.1537836761782016E-4</v>
       </c>
       <c r="Y8">
-        <v>2.1116077383386407E-5</v>
+        <v>2.1642693637046503E-5</v>
       </c>
       <c r="Z8">
-        <v>-1.4420484570888768E-4</v>
+        <v>-1.4584323727857406E-4</v>
       </c>
       <c r="AA8">
-        <v>-1.1077226515824007E-4</v>
+        <v>-1.1108130216969212E-4</v>
       </c>
       <c r="AB8">
-        <v>-1.1622786640813599E-4</v>
+        <v>-1.170967151515451E-4</v>
       </c>
       <c r="AC8">
-        <v>1.9269307085190652E-5</v>
+        <v>1.9389961749731991E-5</v>
       </c>
       <c r="AD8">
-        <v>-8.1355723930311825E-6</v>
+        <v>-8.5274694678563897E-6</v>
       </c>
       <c r="AE8">
-        <v>7.5426767904021802E-6</v>
+        <v>6.5353898931124832E-6</v>
       </c>
       <c r="AF8">
-        <v>1.1886449373839716E-4</v>
+        <v>2.4179104459880023E-4</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.2">
@@ -3386,97 +3386,97 @@
         <v>34</v>
       </c>
       <c r="B9">
-        <v>-0.5234979315511783</v>
+        <v>-0.50468778583287344</v>
       </c>
       <c r="C9">
-        <v>-2.6256428078038848E-4</v>
+        <v>-2.2022144852791754E-4</v>
       </c>
       <c r="D9">
-        <v>2.9619189174806548E-3</v>
+        <v>2.9036669500218798E-3</v>
       </c>
       <c r="E9">
-        <v>-2.6486276980159339E-5</v>
+        <v>-2.6012675408419359E-5</v>
       </c>
       <c r="F9">
-        <v>-6.1118219882119601E-3</v>
+        <v>-6.1390699349622921E-3</v>
       </c>
       <c r="G9">
-        <v>-5.3275577779112945E-3</v>
+        <v>-5.3722389513483695E-3</v>
       </c>
       <c r="H9">
-        <v>6.4020646173056171E-5</v>
+        <v>7.096464307682418E-5</v>
       </c>
       <c r="I9">
-        <v>1.6133381018938503E-4</v>
+        <v>1.7104066956493162E-4</v>
       </c>
       <c r="J9">
-        <v>9.4636796867248948E-3</v>
+        <v>9.4388770424811905E-3</v>
       </c>
       <c r="K9">
-        <v>5.5999224830077972E-4</v>
+        <v>5.5569331545706271E-4</v>
       </c>
       <c r="L9">
-        <v>-2.5689893281114311E-3</v>
+        <v>-2.5102359203569794E-3</v>
       </c>
       <c r="M9">
-        <v>1.7090657125657348E-4</v>
+        <v>1.6607121125292862E-4</v>
       </c>
       <c r="N9">
-        <v>-7.8841990849270321E-5</v>
+        <v>-7.3395784211771013E-5</v>
       </c>
       <c r="O9">
-        <v>-8.8772564008486165E-5</v>
+        <v>-7.098638285532935E-5</v>
       </c>
       <c r="P9">
-        <v>-2.435896369688776E-4</v>
+        <v>-2.3381371213415658E-4</v>
       </c>
       <c r="Q9">
-        <v>-3.6335595410660546E-4</v>
+        <v>-3.6123510642958163E-4</v>
       </c>
       <c r="R9">
-        <v>-6.9186153377019926E-4</v>
+        <v>-7.1843000749185126E-4</v>
       </c>
       <c r="S9">
-        <v>3.826454553538328E-4</v>
+        <v>7.6959633285667885E-4</v>
       </c>
       <c r="T9">
-        <v>7.1909823055051753E-4</v>
+        <v>4.6056870370207292E-4</v>
       </c>
       <c r="U9">
-        <v>-8.5727475420305406E-5</v>
+        <v>-9.9701994357434716E-5</v>
       </c>
       <c r="V9">
-        <v>-1.8228392450622168E-4</v>
+        <v>-1.8217420460480294E-4</v>
       </c>
       <c r="W9">
-        <v>-1.6425174750533955E-4</v>
+        <v>-1.6400049026041308E-4</v>
       </c>
       <c r="X9">
-        <v>-1.5029601914325758E-4</v>
+        <v>-1.4747596137238556E-4</v>
       </c>
       <c r="Y9">
-        <v>-3.0435953866161936E-5</v>
+        <v>-2.8842142467410542E-5</v>
       </c>
       <c r="Z9">
-        <v>-1.4479438038654535E-4</v>
+        <v>-1.4158238213639318E-4</v>
       </c>
       <c r="AA9">
-        <v>3.6914701583406692E-5</v>
+        <v>3.8227683195932172E-5</v>
       </c>
       <c r="AB9">
-        <v>1.8256000519498855E-5</v>
+        <v>2.333301139561747E-5</v>
       </c>
       <c r="AC9">
-        <v>3.0587791750546361E-5</v>
+        <v>3.1534090340889229E-5</v>
       </c>
       <c r="AD9">
-        <v>1.2025088819238305E-4</v>
+        <v>1.2208290770163513E-4</v>
       </c>
       <c r="AE9">
-        <v>1.5399953978041669E-5</v>
+        <v>8.8173611989782186E-6</v>
       </c>
       <c r="AF9">
-        <v>-8.26777603667746E-2</v>
+        <v>-8.0972410481051138E-2</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.2">
@@ -3484,195 +3484,195 @@
         <v>35</v>
       </c>
       <c r="B10">
-        <v>0.28054411507663746</v>
+        <v>0.27838996416079476</v>
       </c>
       <c r="C10">
-        <v>6.5929083599635622E-4</v>
+        <v>6.6123127470460355E-4</v>
       </c>
       <c r="D10">
-        <v>-1.1510488516653424E-4</v>
+        <v>-1.0827520633596363E-4</v>
       </c>
       <c r="E10">
-        <v>8.1217854129133488E-7</v>
+        <v>7.5152924264724531E-7</v>
       </c>
       <c r="F10">
-        <v>3.9441223486048546E-5</v>
+        <v>3.9967890983191867E-5</v>
       </c>
       <c r="G10">
-        <v>3.0970564203409642E-5</v>
+        <v>3.3980678954891735E-5</v>
       </c>
       <c r="H10">
-        <v>-9.276549605458094E-5</v>
+        <v>-9.5817491673552506E-5</v>
       </c>
       <c r="I10">
-        <v>-1.436979955878347E-4</v>
+        <v>-1.4644758320911014E-4</v>
       </c>
       <c r="J10">
-        <v>5.5999224830077972E-4</v>
+        <v>5.5569331545706271E-4</v>
       </c>
       <c r="K10">
-        <v>2.1866069913197041E-3</v>
+        <v>2.1791906095711203E-3</v>
       </c>
       <c r="L10">
-        <v>-9.2992344661315361E-4</v>
+        <v>-9.3390791806195837E-4</v>
       </c>
       <c r="M10">
-        <v>9.3795448318696652E-5</v>
+        <v>9.2049353282732467E-5</v>
       </c>
       <c r="N10">
-        <v>7.0180692480375617E-4</v>
+        <v>7.0151635845918021E-4</v>
       </c>
       <c r="O10">
-        <v>1.3192664166903128E-3</v>
+        <v>1.3125258090180498E-3</v>
       </c>
       <c r="P10">
-        <v>1.3209334027606951E-3</v>
+        <v>1.3115516340900695E-3</v>
       </c>
       <c r="Q10">
-        <v>-7.9499645727432058E-4</v>
+        <v>-7.9344262078678395E-4</v>
       </c>
       <c r="R10">
-        <v>1.3458094284700129E-4</v>
+        <v>1.6357534692175877E-4</v>
       </c>
       <c r="S10">
-        <v>-1.553246597402212E-4</v>
+        <v>-3.1190163130372849E-4</v>
       </c>
       <c r="T10">
-        <v>-2.9534533075805758E-4</v>
+        <v>-8.7108686529680239E-5</v>
       </c>
       <c r="U10">
-        <v>3.5870791963787355E-4</v>
+        <v>3.5376683292267808E-4</v>
       </c>
       <c r="V10">
-        <v>-5.0795873741489768E-5</v>
+        <v>-4.6484309492659213E-5</v>
       </c>
       <c r="W10">
-        <v>-2.1145918025485661E-4</v>
+        <v>-2.0626614274486159E-4</v>
       </c>
       <c r="X10">
-        <v>-2.9710069986508885E-4</v>
+        <v>-2.9102294568792721E-4</v>
       </c>
       <c r="Y10">
-        <v>-2.7210251978592104E-4</v>
+        <v>-2.6567098142122941E-4</v>
       </c>
       <c r="Z10">
-        <v>-2.5539691257208904E-4</v>
+        <v>-2.5171508452830624E-4</v>
       </c>
       <c r="AA10">
-        <v>-2.0067173771618776E-4</v>
+        <v>-1.951670658954595E-4</v>
       </c>
       <c r="AB10">
-        <v>-3.5836503714540766E-4</v>
+        <v>-3.5260073014265619E-4</v>
       </c>
       <c r="AC10">
-        <v>1.0989811566303209E-5</v>
+        <v>1.0821262241786595E-5</v>
       </c>
       <c r="AD10">
-        <v>3.6627567156484659E-5</v>
+        <v>3.6093097805065867E-5</v>
       </c>
       <c r="AE10">
-        <v>3.6191158535631E-5</v>
+        <v>3.9237592265942796E-5</v>
       </c>
       <c r="AF10">
-        <v>1.7422100399287297E-3</v>
+        <v>1.5604631246996618E-3</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B11">
-        <v>-0.74116406068219265</v>
+        <v>-0.73159263351476467</v>
       </c>
       <c r="C11">
-        <v>-3.8218426804469499E-6</v>
+        <v>-4.8913121880072967E-5</v>
       </c>
       <c r="D11">
-        <v>6.4350311175299414E-4</v>
+        <v>6.2770874967373914E-4</v>
       </c>
       <c r="E11">
-        <v>-5.1681576350768416E-6</v>
+        <v>-5.0196387272318454E-6</v>
       </c>
       <c r="F11">
-        <v>2.8054979351586559E-4</v>
+        <v>2.3842254359761166E-4</v>
       </c>
       <c r="G11">
-        <v>2.3004361085097666E-5</v>
+        <v>1.0631622524553269E-6</v>
       </c>
       <c r="H11">
-        <v>-7.6583277711712481E-5</v>
+        <v>-7.6062093547468929E-5</v>
       </c>
       <c r="I11">
-        <v>-3.1695056225983492E-5</v>
+        <v>-2.7988680859991437E-5</v>
       </c>
       <c r="J11">
-        <v>-2.5689893281114311E-3</v>
+        <v>-2.5102359203569794E-3</v>
       </c>
       <c r="K11">
-        <v>-9.2992344661315361E-4</v>
+        <v>-9.3390791806195837E-4</v>
       </c>
       <c r="L11">
-        <v>4.1250207998630786E-3</v>
+        <v>4.1356211281798772E-3</v>
       </c>
       <c r="M11">
-        <v>1.0023846696788699E-6</v>
+        <v>3.6232436102933037E-6</v>
       </c>
       <c r="N11">
-        <v>1.2165066031736508E-4</v>
+        <v>1.1971662893532989E-4</v>
       </c>
       <c r="O11">
-        <v>1.6064099398632812E-4</v>
+        <v>1.505653018209651E-4</v>
       </c>
       <c r="P11">
-        <v>2.517259728055572E-4</v>
+        <v>2.4873667104816739E-4</v>
       </c>
       <c r="Q11">
-        <v>2.0502767681666902E-4</v>
+        <v>2.0245654437918447E-4</v>
       </c>
       <c r="R11">
-        <v>-2.4242249362033922E-4</v>
+        <v>-4.2244178030889353E-4</v>
       </c>
       <c r="S11">
-        <v>5.3434800485357092E-4</v>
+        <v>8.1219011060027499E-4</v>
       </c>
       <c r="T11">
-        <v>6.9419497770139551E-4</v>
+        <v>3.3389148418677141E-4</v>
       </c>
       <c r="U11">
-        <v>1.3409338565726183E-4</v>
+        <v>1.5073419211822446E-4</v>
       </c>
       <c r="V11">
-        <v>9.8889032875812541E-5</v>
+        <v>9.0337666218841175E-5</v>
       </c>
       <c r="W11">
-        <v>7.9520853194377586E-5</v>
+        <v>6.7893106911379349E-5</v>
       </c>
       <c r="X11">
-        <v>2.2787685722563608E-5</v>
+        <v>9.1786741238915684E-6</v>
       </c>
       <c r="Y11">
-        <v>-7.1815127635796276E-6</v>
+        <v>-2.4033414581407526E-5</v>
       </c>
       <c r="Z11">
-        <v>4.0926054849702194E-5</v>
+        <v>3.194206417965386E-5</v>
       </c>
       <c r="AA11">
-        <v>3.855480742998409E-5</v>
+        <v>2.1387047368748562E-5</v>
       </c>
       <c r="AB11">
-        <v>1.7665281624254948E-4</v>
+        <v>1.6773148791221059E-4</v>
       </c>
       <c r="AC11">
-        <v>1.2996587300830454E-5</v>
+        <v>1.338068976918949E-5</v>
       </c>
       <c r="AD11">
-        <v>-4.2586947257999309E-5</v>
+        <v>-4.2790836759010187E-5</v>
       </c>
       <c r="AE11">
-        <v>-5.668123728520217E-5</v>
+        <v>-6.2428390317280889E-5</v>
       </c>
       <c r="AF11">
-        <v>-2.0037704559520836E-2</v>
+        <v>-1.9576070744094703E-2</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.2">
@@ -3680,97 +3680,97 @@
         <v>36</v>
       </c>
       <c r="B12">
-        <v>4.5733394426548328E-2</v>
+        <v>4.5004152394663557E-2</v>
       </c>
       <c r="C12">
-        <v>5.6139993627165761E-5</v>
+        <v>6.0159217809408101E-5</v>
       </c>
       <c r="D12">
-        <v>1.0613943597936881E-4</v>
+        <v>9.6512158729210318E-5</v>
       </c>
       <c r="E12">
-        <v>-9.525496043867143E-7</v>
+        <v>-8.7456991016698362E-7</v>
       </c>
       <c r="F12">
-        <v>-1.5832672271775226E-4</v>
+        <v>-1.6210494769831538E-4</v>
       </c>
       <c r="G12">
-        <v>-9.238939590995067E-5</v>
+        <v>-8.7598100233475529E-5</v>
       </c>
       <c r="H12">
-        <v>-6.3015617022360538E-6</v>
+        <v>-5.3617857572944134E-6</v>
       </c>
       <c r="I12">
-        <v>3.4720913991057934E-5</v>
+        <v>3.6893921217557126E-5</v>
       </c>
       <c r="J12">
-        <v>1.7090657125657348E-4</v>
+        <v>1.6607121125292862E-4</v>
       </c>
       <c r="K12">
-        <v>9.3795448318696652E-5</v>
+        <v>9.2049353282732467E-5</v>
       </c>
       <c r="L12">
-        <v>1.0023846696788699E-6</v>
+        <v>3.6232436102933037E-6</v>
       </c>
       <c r="M12">
-        <v>1.6573290140312461E-3</v>
+        <v>1.6622718457168252E-3</v>
       </c>
       <c r="N12">
-        <v>8.2248691414557563E-4</v>
+        <v>8.2511256477257931E-4</v>
       </c>
       <c r="O12">
-        <v>8.4515597956036641E-4</v>
+        <v>8.475390906643827E-4</v>
       </c>
       <c r="P12">
-        <v>8.5879000544015235E-4</v>
+        <v>8.6181643411142026E-4</v>
       </c>
       <c r="Q12">
-        <v>-2.8053886209039567E-5</v>
+        <v>-2.4454183319798611E-5</v>
       </c>
       <c r="R12">
-        <v>-4.5460339183357929E-5</v>
+        <v>-4.6234290833055967E-5</v>
       </c>
       <c r="S12">
-        <v>5.3963192933774505E-6</v>
+        <v>7.1503245069130675E-5</v>
       </c>
       <c r="T12">
-        <v>6.2339736771488885E-5</v>
+        <v>4.7584987379977188E-5</v>
       </c>
       <c r="U12">
-        <v>5.9191160134951844E-5</v>
+        <v>5.6004843837205204E-5</v>
       </c>
       <c r="V12">
-        <v>7.8117580987995206E-5</v>
+        <v>7.7953104558420858E-5</v>
       </c>
       <c r="W12">
-        <v>-1.4858500685012085E-4</v>
+        <v>-1.4442909588583091E-4</v>
       </c>
       <c r="X12">
-        <v>-1.02968327912793E-4</v>
+        <v>-1.0044767566196326E-4</v>
       </c>
       <c r="Y12">
-        <v>-1.3065368451483641E-4</v>
+        <v>-1.2464882319047031E-4</v>
       </c>
       <c r="Z12">
-        <v>-9.2374662380601642E-5</v>
+        <v>-9.1092954269858745E-5</v>
       </c>
       <c r="AA12">
-        <v>-1.3977880512156812E-4</v>
+        <v>-1.3600591306319029E-4</v>
       </c>
       <c r="AB12">
-        <v>-4.0230297744125077E-5</v>
+        <v>-3.7767557070671242E-5</v>
       </c>
       <c r="AC12">
-        <v>1.0302928446353325E-5</v>
+        <v>1.0084306560428356E-5</v>
       </c>
       <c r="AD12">
-        <v>-6.366220707879457E-5</v>
+        <v>-6.3177250266289336E-5</v>
       </c>
       <c r="AE12">
-        <v>-1.2898703690403159E-5</v>
+        <v>-1.0207168516141178E-5</v>
       </c>
       <c r="AF12">
-        <v>-3.9375238607508162E-3</v>
+        <v>-3.6488735544846183E-3</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.2">
@@ -3778,97 +3778,97 @@
         <v>37</v>
       </c>
       <c r="B13">
-        <v>6.8725675613250797E-2</v>
+        <v>6.6195445378885109E-2</v>
       </c>
       <c r="C13">
-        <v>8.5235100534041805E-5</v>
+        <v>7.9045820025245081E-5</v>
       </c>
       <c r="D13">
-        <v>-1.3100128436809369E-4</v>
+        <v>-1.3184482315622015E-4</v>
       </c>
       <c r="E13">
-        <v>9.8398391760685445E-7</v>
+        <v>9.9457475663084313E-7</v>
       </c>
       <c r="F13">
-        <v>-6.0067415039244745E-6</v>
+        <v>-1.0757101683266101E-5</v>
       </c>
       <c r="G13">
-        <v>6.8097054835612649E-5</v>
+        <v>6.6364127081302259E-5</v>
       </c>
       <c r="H13">
-        <v>-1.9504066919595633E-5</v>
+        <v>-2.4116853083533811E-5</v>
       </c>
       <c r="I13">
-        <v>8.4960994955118592E-5</v>
+        <v>8.2605719810949547E-5</v>
       </c>
       <c r="J13">
-        <v>-7.8841990849270321E-5</v>
+        <v>-7.3395784211771013E-5</v>
       </c>
       <c r="K13">
-        <v>7.0180692480375617E-4</v>
+        <v>7.0151635845918021E-4</v>
       </c>
       <c r="L13">
-        <v>1.2165066031736508E-4</v>
+        <v>1.1971662893532989E-4</v>
       </c>
       <c r="M13">
-        <v>8.2248691414557563E-4</v>
+        <v>8.2511256477257931E-4</v>
       </c>
       <c r="N13">
-        <v>1.9352751438251076E-3</v>
+        <v>1.9377806896897719E-3</v>
       </c>
       <c r="O13">
-        <v>1.5874126387094712E-3</v>
+        <v>1.5878241110124573E-3</v>
       </c>
       <c r="P13">
-        <v>1.6975543070582313E-3</v>
+        <v>1.6971493001531265E-3</v>
       </c>
       <c r="Q13">
-        <v>-9.4906574066254984E-5</v>
+        <v>-9.2968393790273808E-5</v>
       </c>
       <c r="R13">
-        <v>-5.5509477907005771E-6</v>
+        <v>-2.4854932899001718E-5</v>
       </c>
       <c r="S13">
-        <v>5.0192496597594219E-5</v>
+        <v>-2.2702103437804316E-5</v>
       </c>
       <c r="T13">
-        <v>-4.2348101070800487E-5</v>
+        <v>2.1865485366483043E-5</v>
       </c>
       <c r="U13">
-        <v>4.4926220063263363E-4</v>
+        <v>4.5167361398785219E-4</v>
       </c>
       <c r="V13">
-        <v>1.4556349198360934E-4</v>
+        <v>1.5002552897824662E-4</v>
       </c>
       <c r="W13">
-        <v>-2.2796661723335993E-4</v>
+        <v>-2.1996446149501973E-4</v>
       </c>
       <c r="X13">
-        <v>-2.4941802218425026E-4</v>
+        <v>-2.4244449458122675E-4</v>
       </c>
       <c r="Y13">
-        <v>-3.0043872716400857E-4</v>
+        <v>-2.9083518978950033E-4</v>
       </c>
       <c r="Z13">
-        <v>-2.5412350266922025E-4</v>
+        <v>-2.4887505658916865E-4</v>
       </c>
       <c r="AA13">
-        <v>-2.8770017743928798E-4</v>
+        <v>-2.8005638457713684E-4</v>
       </c>
       <c r="AB13">
-        <v>-2.0856127885315033E-4</v>
+        <v>-2.0339001972587178E-4</v>
       </c>
       <c r="AC13">
-        <v>1.4548855961440797E-5</v>
+        <v>1.4648079613180153E-5</v>
       </c>
       <c r="AD13">
-        <v>-1.3244629703063927E-5</v>
+        <v>-1.5044552863043405E-5</v>
       </c>
       <c r="AE13">
-        <v>1.8165728128279783E-5</v>
+        <v>1.6109562603758331E-5</v>
       </c>
       <c r="AF13">
-        <v>2.2686468873432813E-3</v>
+        <v>2.2789462033859474E-3</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.2">
@@ -3876,97 +3876,97 @@
         <v>38</v>
       </c>
       <c r="B14">
-        <v>7.72091447970151E-2</v>
+        <v>7.2682851392894932E-2</v>
       </c>
       <c r="C14">
-        <v>1.5412556938098774E-4</v>
+        <v>1.1942233552537671E-4</v>
       </c>
       <c r="D14">
-        <v>-8.7506815788145585E-5</v>
+        <v>-8.1319415389565462E-5</v>
       </c>
       <c r="E14">
-        <v>6.4323715881421417E-7</v>
+        <v>6.0846141394254764E-7</v>
       </c>
       <c r="F14">
-        <v>-2.0086948044259305E-5</v>
+        <v>-2.5411319357183416E-5</v>
       </c>
       <c r="G14">
-        <v>2.4205367652443879E-5</v>
+        <v>2.8065530651967974E-5</v>
       </c>
       <c r="H14">
-        <v>-3.8522040883761852E-5</v>
+        <v>-4.6698585106363228E-5</v>
       </c>
       <c r="I14">
-        <v>1.3391735913121093E-4</v>
+        <v>1.2999567124037076E-4</v>
       </c>
       <c r="J14">
-        <v>-8.8772564008486165E-5</v>
+        <v>-7.098638285532935E-5</v>
       </c>
       <c r="K14">
-        <v>1.3192664166903128E-3</v>
+        <v>1.3125258090180498E-3</v>
       </c>
       <c r="L14">
-        <v>1.6064099398632812E-4</v>
+        <v>1.505653018209651E-4</v>
       </c>
       <c r="M14">
-        <v>8.4515597956036641E-4</v>
+        <v>8.475390906643827E-4</v>
       </c>
       <c r="N14">
-        <v>1.5874126387094712E-3</v>
+        <v>1.5878241110124573E-3</v>
       </c>
       <c r="O14">
-        <v>3.3309980350952166E-3</v>
+        <v>3.3253740814743367E-3</v>
       </c>
       <c r="P14">
-        <v>2.6281071940719254E-3</v>
+        <v>2.6192812688955011E-3</v>
       </c>
       <c r="Q14">
-        <v>-6.0609176290801851E-5</v>
+        <v>-5.9622122030124049E-5</v>
       </c>
       <c r="R14">
-        <v>1.5470776933777228E-4</v>
+        <v>8.2890003315921635E-5</v>
       </c>
       <c r="S14">
-        <v>4.9753705705128323E-5</v>
+        <v>1.4186033712839091E-4</v>
       </c>
       <c r="T14">
-        <v>1.0804341930913466E-4</v>
+        <v>2.1820419236548286E-5</v>
       </c>
       <c r="U14">
-        <v>9.0404317481287554E-4</v>
+        <v>9.190654310700431E-4</v>
       </c>
       <c r="V14">
-        <v>7.6992634687152563E-5</v>
+        <v>7.6340792777190511E-5</v>
       </c>
       <c r="W14">
-        <v>-2.5685675830949698E-4</v>
+        <v>-2.5105798887131714E-4</v>
       </c>
       <c r="X14">
-        <v>-3.3086972915194034E-4</v>
+        <v>-3.2623527497734495E-4</v>
       </c>
       <c r="Y14">
-        <v>-3.4348086675609502E-4</v>
+        <v>-3.361037257944504E-4</v>
       </c>
       <c r="Z14">
-        <v>-2.1823233229966918E-4</v>
+        <v>-2.1536049324493009E-4</v>
       </c>
       <c r="AA14">
-        <v>-3.4910654710936461E-4</v>
+        <v>-3.4239409481394325E-4</v>
       </c>
       <c r="AB14">
-        <v>-2.2080638520407311E-4</v>
+        <v>-2.1777243440040928E-4</v>
       </c>
       <c r="AC14">
-        <v>3.0786045339419217E-5</v>
+        <v>3.0603459678323622E-5</v>
       </c>
       <c r="AD14">
-        <v>-7.2938601358510553E-5</v>
+        <v>-7.6728373431216371E-5</v>
       </c>
       <c r="AE14">
-        <v>-6.0624952156468261E-5</v>
+        <v>-6.0861654323060739E-5</v>
       </c>
       <c r="AF14">
-        <v>-6.1661017433234377E-4</v>
+        <v>-8.2375056725186857E-4</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.2">
@@ -3974,97 +3974,97 @@
         <v>39</v>
       </c>
       <c r="B15">
-        <v>0.15526123972573094</v>
+        <v>0.15058340100915391</v>
       </c>
       <c r="C15">
-        <v>1.2724761698980827E-4</v>
+        <v>1.1547551740743927E-4</v>
       </c>
       <c r="D15">
-        <v>-1.8659072133111153E-4</v>
+        <v>-1.8703019726721941E-4</v>
       </c>
       <c r="E15">
-        <v>1.4353804087846752E-6</v>
+        <v>1.4432278013997931E-6</v>
       </c>
       <c r="F15">
-        <v>1.3679014965022485E-4</v>
+        <v>1.2613560276452523E-4</v>
       </c>
       <c r="G15">
-        <v>1.5193521622598218E-4</v>
+        <v>1.5498686885990869E-4</v>
       </c>
       <c r="H15">
-        <v>3.4026502123803213E-4</v>
+        <v>3.3649144332574543E-4</v>
       </c>
       <c r="I15">
-        <v>5.6354778732926631E-4</v>
+        <v>5.6161171625847804E-4</v>
       </c>
       <c r="J15">
-        <v>-2.435896369688776E-4</v>
+        <v>-2.3381371213415658E-4</v>
       </c>
       <c r="K15">
-        <v>1.3209334027606951E-3</v>
+        <v>1.3115516340900695E-3</v>
       </c>
       <c r="L15">
-        <v>2.517259728055572E-4</v>
+        <v>2.4873667104816739E-4</v>
       </c>
       <c r="M15">
-        <v>8.5879000544015235E-4</v>
+        <v>8.6181643411142026E-4</v>
       </c>
       <c r="N15">
-        <v>1.6975543070582313E-3</v>
+        <v>1.6971493001531265E-3</v>
       </c>
       <c r="O15">
-        <v>2.6281071940719254E-3</v>
+        <v>2.6192812688955011E-3</v>
       </c>
       <c r="P15">
-        <v>3.6953065976039982E-3</v>
+        <v>3.6861282889782644E-3</v>
       </c>
       <c r="Q15">
-        <v>2.1477023856255212E-5</v>
+        <v>2.4060358673338626E-5</v>
       </c>
       <c r="R15">
-        <v>8.5486696451647832E-5</v>
+        <v>5.7202121184093968E-5</v>
       </c>
       <c r="S15">
-        <v>-3.4861246310112569E-5</v>
+        <v>3.7473955108548998E-5</v>
       </c>
       <c r="T15">
-        <v>9.5855110387021297E-6</v>
+        <v>1.348479476101028E-5</v>
       </c>
       <c r="U15">
-        <v>1.1246650520041418E-3</v>
+        <v>1.1281194748449643E-3</v>
       </c>
       <c r="V15">
-        <v>2.1531454714899612E-5</v>
+        <v>2.3381858180763701E-5</v>
       </c>
       <c r="W15">
-        <v>-1.9175661010680575E-4</v>
+        <v>-1.8873634597326491E-4</v>
       </c>
       <c r="X15">
-        <v>-4.0795362771711089E-4</v>
+        <v>-4.0550502924804237E-4</v>
       </c>
       <c r="Y15">
-        <v>-3.4378450321511007E-4</v>
+        <v>-3.4081909917388657E-4</v>
       </c>
       <c r="Z15">
-        <v>-1.9388571336950797E-4</v>
+        <v>-1.9405216603030507E-4</v>
       </c>
       <c r="AA15">
-        <v>-3.2793406210695315E-4</v>
+        <v>-3.2387872231870365E-4</v>
       </c>
       <c r="AB15">
-        <v>-1.5545698381863246E-4</v>
+        <v>-1.5439345875577432E-4</v>
       </c>
       <c r="AC15">
-        <v>2.900263651559643E-5</v>
+        <v>2.8749809877302813E-5</v>
       </c>
       <c r="AD15">
-        <v>-6.7969074724705996E-5</v>
+        <v>-6.9070441358058026E-5</v>
       </c>
       <c r="AE15">
-        <v>6.3133461328519595E-6</v>
+        <v>7.8556709443727314E-6</v>
       </c>
       <c r="AF15">
-        <v>1.8750322611581632E-3</v>
+        <v>1.8947356936218698E-3</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.2">
@@ -4072,97 +4072,97 @@
         <v>40</v>
       </c>
       <c r="B16">
-        <v>0.70039811024406151</v>
+        <v>0.69699352119333824</v>
       </c>
       <c r="C16">
-        <v>-4.1912642414828775E-4</v>
+        <v>-4.2326165195228981E-4</v>
       </c>
       <c r="D16">
-        <v>-2.0851444792344175E-4</v>
+        <v>-2.0887139217288945E-4</v>
       </c>
       <c r="E16">
-        <v>1.8037157605078595E-6</v>
+        <v>1.8094565872085687E-6</v>
       </c>
       <c r="F16">
-        <v>1.7392951375968559E-4</v>
+        <v>1.7638354082061833E-4</v>
       </c>
       <c r="G16">
-        <v>1.6886192199491246E-4</v>
+        <v>1.7383092497874272E-4</v>
       </c>
       <c r="H16">
-        <v>5.6725075104128005E-5</v>
+        <v>5.6744577319602142E-5</v>
       </c>
       <c r="I16">
-        <v>1.3093487704130687E-5</v>
+        <v>1.3745747940808854E-5</v>
       </c>
       <c r="J16">
-        <v>-3.6335595410660546E-4</v>
+        <v>-3.6123510642958163E-4</v>
       </c>
       <c r="K16">
-        <v>-7.9499645727432058E-4</v>
+        <v>-7.9344262078678395E-4</v>
       </c>
       <c r="L16">
-        <v>2.0502767681666902E-4</v>
+        <v>2.0245654437918447E-4</v>
       </c>
       <c r="M16">
-        <v>-2.8053886209039567E-5</v>
+        <v>-2.4454183319798611E-5</v>
       </c>
       <c r="N16">
-        <v>-9.4906574066254984E-5</v>
+        <v>-9.2968393790273808E-5</v>
       </c>
       <c r="O16">
-        <v>-6.0609176290801851E-5</v>
+        <v>-5.9622122030124049E-5</v>
       </c>
       <c r="P16">
-        <v>2.1477023856255212E-5</v>
+        <v>2.4060358673338626E-5</v>
       </c>
       <c r="Q16">
-        <v>2.0251351429110506E-3</v>
+        <v>2.0263887279008746E-3</v>
       </c>
       <c r="R16">
-        <v>7.7412795257932054E-5</v>
+        <v>6.5070232064915541E-5</v>
       </c>
       <c r="S16">
-        <v>-5.5950405445270949E-5</v>
+        <v>-2.8370685089056883E-6</v>
       </c>
       <c r="T16">
-        <v>-1.0271487050409834E-5</v>
+        <v>9.4704023656464191E-6</v>
       </c>
       <c r="U16">
-        <v>5.5314154604624837E-5</v>
+        <v>5.9004889913628268E-5</v>
       </c>
       <c r="V16">
-        <v>-2.8653459268976279E-4</v>
+        <v>-2.9070223405364387E-4</v>
       </c>
       <c r="W16">
-        <v>3.1952292265807682E-4</v>
+        <v>3.1426355071809928E-4</v>
       </c>
       <c r="X16">
-        <v>3.0820624492360993E-4</v>
+        <v>3.0083896246165551E-4</v>
       </c>
       <c r="Y16">
-        <v>4.1541802196723128E-4</v>
+        <v>4.0775648551883732E-4</v>
       </c>
       <c r="Z16">
-        <v>4.400216802932542E-4</v>
+        <v>4.3272826800487568E-4</v>
       </c>
       <c r="AA16">
-        <v>2.2695569696376585E-4</v>
+        <v>2.2044725784620933E-4</v>
       </c>
       <c r="AB16">
-        <v>3.164770103205837E-4</v>
+        <v>3.0965431843519556E-4</v>
       </c>
       <c r="AC16">
-        <v>-2.7909371255910195E-6</v>
+        <v>-2.8648510659164898E-6</v>
       </c>
       <c r="AD16">
-        <v>-5.8552944791506577E-5</v>
+        <v>-5.9196877903071657E-5</v>
       </c>
       <c r="AE16">
-        <v>-2.0434884494165411E-5</v>
+        <v>-2.0531197943280403E-5</v>
       </c>
       <c r="AF16">
-        <v>6.0889401524989763E-3</v>
+        <v>6.096500656888419E-3</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.2">
@@ -4170,97 +4170,97 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>-9.1440507807326071E-2</v>
+        <v>-0.18001015393793976</v>
       </c>
       <c r="C17">
-        <v>7.8794856558135075E-4</v>
+        <v>6.7479034677417641E-4</v>
       </c>
       <c r="D17">
-        <v>1.459489014538802E-4</v>
+        <v>3.3549961559651859E-4</v>
       </c>
       <c r="E17">
-        <v>-1.4848012337321137E-6</v>
+        <v>-3.0130221747405795E-6</v>
       </c>
       <c r="F17">
-        <v>3.5359481747339761E-4</v>
+        <v>5.334614974869048E-4</v>
       </c>
       <c r="G17">
-        <v>1.9957995172552832E-4</v>
+        <v>3.9766183659994004E-4</v>
       </c>
       <c r="H17">
-        <v>4.3471605720680405E-5</v>
+        <v>2.7001880979072185E-5</v>
       </c>
       <c r="I17">
-        <v>-1.3775472791114062E-5</v>
+        <v>-5.0477405441336413E-5</v>
       </c>
       <c r="J17">
-        <v>-6.9186153377019926E-4</v>
+        <v>-7.1843000749185126E-4</v>
       </c>
       <c r="K17">
-        <v>1.3458094284700129E-4</v>
+        <v>1.6357534692175877E-4</v>
       </c>
       <c r="L17">
-        <v>-2.4242249362033922E-4</v>
+        <v>-4.2244178030889353E-4</v>
       </c>
       <c r="M17">
-        <v>-4.5460339183357929E-5</v>
+        <v>-4.6234290833055967E-5</v>
       </c>
       <c r="N17">
-        <v>-5.5509477907005771E-6</v>
+        <v>-2.4854932899001718E-5</v>
       </c>
       <c r="O17">
-        <v>1.5470776933777228E-4</v>
+        <v>8.2890003315921635E-5</v>
       </c>
       <c r="P17">
-        <v>8.5486696451647832E-5</v>
+        <v>5.7202121184093968E-5</v>
       </c>
       <c r="Q17">
-        <v>7.7412795257932054E-5</v>
+        <v>6.5070232064915541E-5</v>
       </c>
       <c r="R17">
-        <v>2.5516176036147107E-3</v>
+        <v>2.7652518618685278E-3</v>
       </c>
       <c r="S17">
-        <v>-1.4669726564043183E-3</v>
+        <v>-1.7887970744277814E-3</v>
       </c>
       <c r="T17">
-        <v>-1.4062077033850031E-3</v>
+        <v>-1.5953009365758301E-3</v>
       </c>
       <c r="U17">
-        <v>-3.8217195501605099E-4</v>
+        <v>-3.4638816861697649E-4</v>
       </c>
       <c r="V17">
-        <v>3.9059838023810264E-4</v>
+        <v>3.883545172748969E-4</v>
       </c>
       <c r="W17">
-        <v>1.3085887932505458E-4</v>
+        <v>1.2121926822444319E-4</v>
       </c>
       <c r="X17">
-        <v>4.3387426228939062E-5</v>
+        <v>3.4437390712475403E-5</v>
       </c>
       <c r="Y17">
-        <v>1.5536182369949356E-4</v>
+        <v>1.467512952495688E-4</v>
       </c>
       <c r="Z17">
-        <v>1.8135024026671694E-4</v>
+        <v>1.2784028704198366E-4</v>
       </c>
       <c r="AA17">
-        <v>1.1683960778865706E-4</v>
+        <v>1.192564933582504E-4</v>
       </c>
       <c r="AB17">
-        <v>1.5333264016528103E-4</v>
+        <v>1.3048039836500384E-4</v>
       </c>
       <c r="AC17">
-        <v>4.7143973248359785E-6</v>
+        <v>1.0884319646008893E-8</v>
       </c>
       <c r="AD17">
-        <v>6.0870600581627811E-5</v>
+        <v>6.0972931589001102E-5</v>
       </c>
       <c r="AE17">
-        <v>4.8794614115166062E-5</v>
+        <v>8.481826988177444E-5</v>
       </c>
       <c r="AF17">
-        <v>-4.3589147659581773E-3</v>
+        <v>-9.9367354861983545E-3</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.2">
@@ -4268,97 +4268,97 @@
         <v>53</v>
       </c>
       <c r="B18">
-        <v>0.19690863233773628</v>
+        <v>0.20230510212742045</v>
       </c>
       <c r="C18">
-        <v>-2.2511761873168627E-4</v>
+        <v>-2.9874274436318573E-4</v>
       </c>
       <c r="D18">
-        <v>-2.7466335224897356E-4</v>
+        <v>-2.1927914050563421E-4</v>
       </c>
       <c r="E18">
-        <v>2.2750375750720358E-6</v>
+        <v>1.6623732069506259E-6</v>
       </c>
       <c r="F18">
-        <v>-5.0320506515459662E-4</v>
+        <v>-1.0446205190958319E-3</v>
       </c>
       <c r="G18">
-        <v>-4.1744464422944529E-4</v>
+        <v>-9.321461225941137E-4</v>
       </c>
       <c r="H18">
-        <v>-2.2661785328908856E-5</v>
+        <v>-3.5516595288080091E-5</v>
       </c>
       <c r="I18">
-        <v>6.6612424270576779E-5</v>
+        <v>1.1539642106720392E-4</v>
       </c>
       <c r="J18">
-        <v>3.826454553538328E-4</v>
+        <v>7.6959633285667885E-4</v>
       </c>
       <c r="K18">
-        <v>-1.553246597402212E-4</v>
+        <v>-3.1190163130372849E-4</v>
       </c>
       <c r="L18">
-        <v>5.3434800485357092E-4</v>
+        <v>8.1219011060027499E-4</v>
       </c>
       <c r="M18">
-        <v>5.3963192933774505E-6</v>
+        <v>7.1503245069130675E-5</v>
       </c>
       <c r="N18">
-        <v>5.0192496597594219E-5</v>
+        <v>-2.2702103437804316E-5</v>
       </c>
       <c r="O18">
-        <v>4.9753705705128323E-5</v>
+        <v>1.4186033712839091E-4</v>
       </c>
       <c r="P18">
-        <v>-3.4861246310112569E-5</v>
+        <v>3.7473955108548998E-5</v>
       </c>
       <c r="Q18">
-        <v>-5.5950405445270949E-5</v>
+        <v>-2.8370685089056883E-6</v>
       </c>
       <c r="R18">
-        <v>-1.4669726564043183E-3</v>
+        <v>-1.7887970744277814E-3</v>
       </c>
       <c r="S18">
-        <v>4.4398038482355694E-3</v>
+        <v>6.3400322917872131E-3</v>
       </c>
       <c r="T18">
-        <v>1.193949137042077E-3</v>
+        <v>1.423299510050689E-3</v>
       </c>
       <c r="U18">
-        <v>1.8584129691221309E-4</v>
+        <v>1.0268980970879458E-4</v>
       </c>
       <c r="V18">
-        <v>-2.2725626399189443E-4</v>
+        <v>-2.4070265918691553E-4</v>
       </c>
       <c r="W18">
-        <v>-3.4002197660835606E-5</v>
+        <v>-9.0096142385287167E-5</v>
       </c>
       <c r="X18">
-        <v>7.5752914376313492E-5</v>
+        <v>-2.3687929021631859E-5</v>
       </c>
       <c r="Y18">
-        <v>3.2801598417574011E-5</v>
+        <v>9.3603901718592852E-5</v>
       </c>
       <c r="Z18">
-        <v>-6.4812539956370444E-6</v>
+        <v>-2.7170147437050388E-5</v>
       </c>
       <c r="AA18">
-        <v>3.2374485291783483E-5</v>
+        <v>-3.1612628740141854E-5</v>
       </c>
       <c r="AB18">
-        <v>-2.9013127443377508E-5</v>
+        <v>8.5678058381575238E-5</v>
       </c>
       <c r="AC18">
-        <v>3.0286934443505986E-6</v>
+        <v>1.5624033055573806E-5</v>
       </c>
       <c r="AD18">
-        <v>-1.1249496239385979E-4</v>
+        <v>-1.7872411875424592E-4</v>
       </c>
       <c r="AE18">
-        <v>-8.3169900872820043E-5</v>
+        <v>-1.6821745419701769E-4</v>
       </c>
       <c r="AF18">
-        <v>8.3108403005202891E-3</v>
+        <v>7.0811416908349023E-3</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.2">
@@ -4366,97 +4366,97 @@
         <v>54</v>
       </c>
       <c r="B19">
-        <v>0.13574285166008893</v>
+        <v>0.20846442851149286</v>
       </c>
       <c r="C19">
-        <v>-2.9401555776640111E-4</v>
+        <v>-1.2882799477750343E-4</v>
       </c>
       <c r="D19">
-        <v>-5.5695224003948773E-5</v>
+        <v>-4.7693563485250515E-4</v>
       </c>
       <c r="E19">
-        <v>3.0226665811251352E-7</v>
+        <v>3.984075981260774E-6</v>
       </c>
       <c r="F19">
-        <v>-9.331374014842457E-4</v>
+        <v>-5.1706008620285709E-4</v>
       </c>
       <c r="G19">
-        <v>-8.0820040715199812E-4</v>
+        <v>-5.128743988593509E-4</v>
       </c>
       <c r="H19">
-        <v>-5.7469043889428104E-5</v>
+        <v>3.8815558325247458E-5</v>
       </c>
       <c r="I19">
-        <v>7.8908114838060215E-5</v>
+        <v>6.8919768821180149E-5</v>
       </c>
       <c r="J19">
-        <v>7.1909823055051753E-4</v>
+        <v>4.6056870370207292E-4</v>
       </c>
       <c r="K19">
-        <v>-2.9534533075805758E-4</v>
+        <v>-8.7108686529680239E-5</v>
       </c>
       <c r="L19">
-        <v>6.9419497770139551E-4</v>
+        <v>3.3389148418677141E-4</v>
       </c>
       <c r="M19">
-        <v>6.2339736771488885E-5</v>
+        <v>4.7584987379977188E-5</v>
       </c>
       <c r="N19">
-        <v>-4.2348101070800487E-5</v>
+        <v>2.1865485366483043E-5</v>
       </c>
       <c r="O19">
-        <v>1.0804341930913466E-4</v>
+        <v>2.1820419236548286E-5</v>
       </c>
       <c r="P19">
-        <v>9.5855110387021297E-6</v>
+        <v>1.348479476101028E-5</v>
       </c>
       <c r="Q19">
-        <v>-1.0271487050409834E-5</v>
+        <v>9.4704023656464191E-6</v>
       </c>
       <c r="R19">
-        <v>-1.4062077033850031E-3</v>
+        <v>-1.5953009365758301E-3</v>
       </c>
       <c r="S19">
-        <v>1.193949137042077E-3</v>
+        <v>1.423299510050689E-3</v>
       </c>
       <c r="T19">
-        <v>6.0361572838891044E-3</v>
+        <v>4.794871695148104E-3</v>
       </c>
       <c r="U19">
-        <v>1.0367218748962481E-4</v>
+        <v>2.0086170280672914E-5</v>
       </c>
       <c r="V19">
-        <v>-2.171365028712036E-4</v>
+        <v>-1.2204080069225373E-4</v>
       </c>
       <c r="W19">
-        <v>-5.6459651957089033E-5</v>
+        <v>-4.8482046843859386E-5</v>
       </c>
       <c r="X19">
-        <v>-3.5487735153185568E-7</v>
+        <v>-6.6372444596110233E-5</v>
       </c>
       <c r="Y19">
-        <v>1.2812588710301581E-4</v>
+        <v>-1.5413901220451406E-4</v>
       </c>
       <c r="Z19">
-        <v>-2.417736306926585E-5</v>
+        <v>2.2633020274732615E-5</v>
       </c>
       <c r="AA19">
-        <v>2.4388886001330216E-5</v>
+        <v>-1.2648232008996389E-4</v>
       </c>
       <c r="AB19">
-        <v>1.1918428849947609E-4</v>
+        <v>-2.6678346156877066E-5</v>
       </c>
       <c r="AC19">
-        <v>1.3435094568229044E-5</v>
+        <v>5.5367129802432136E-6</v>
       </c>
       <c r="AD19">
-        <v>-1.9424870032547529E-4</v>
+        <v>7.5151238037992826E-5</v>
       </c>
       <c r="AE19">
-        <v>-1.5139558668159948E-4</v>
+        <v>-5.1538663644032368E-5</v>
       </c>
       <c r="AF19">
-        <v>2.2384526513898467E-3</v>
+        <v>1.4227122448520785E-2</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.2">
@@ -4464,97 +4464,97 @@
         <v>55</v>
       </c>
       <c r="B20">
-        <v>0.10241601649597953</v>
+        <v>0.10975265556717631</v>
       </c>
       <c r="C20">
-        <v>-5.993302321163045E-5</v>
+        <v>-4.3888650747473957E-5</v>
       </c>
       <c r="D20">
-        <v>-8.3519287051491732E-5</v>
+        <v>-8.7403088317757407E-5</v>
       </c>
       <c r="E20">
-        <v>6.0524281928056372E-7</v>
+        <v>6.3141847957079455E-7</v>
       </c>
       <c r="F20">
-        <v>1.3152189557902143E-5</v>
+        <v>2.754369199701838E-6</v>
       </c>
       <c r="G20">
-        <v>4.906263521241034E-5</v>
+        <v>3.5950533332993959E-5</v>
       </c>
       <c r="H20">
-        <v>-1.4416054766716179E-5</v>
+        <v>-1.5690043718079186E-5</v>
       </c>
       <c r="I20">
-        <v>1.5554265670880837E-6</v>
+        <v>3.1646010236562169E-6</v>
       </c>
       <c r="J20">
-        <v>-8.5727475420305406E-5</v>
+        <v>-9.9701994357434716E-5</v>
       </c>
       <c r="K20">
-        <v>3.5870791963787355E-4</v>
+        <v>3.5376683292267808E-4</v>
       </c>
       <c r="L20">
-        <v>1.3409338565726183E-4</v>
+        <v>1.5073419211822446E-4</v>
       </c>
       <c r="M20">
-        <v>5.9191160134951844E-5</v>
+        <v>5.6004843837205204E-5</v>
       </c>
       <c r="N20">
-        <v>4.4926220063263363E-4</v>
+        <v>4.5167361398785219E-4</v>
       </c>
       <c r="O20">
-        <v>9.0404317481287554E-4</v>
+        <v>9.190654310700431E-4</v>
       </c>
       <c r="P20">
-        <v>1.1246650520041418E-3</v>
+        <v>1.1281194748449643E-3</v>
       </c>
       <c r="Q20">
-        <v>5.5314154604624837E-5</v>
+        <v>5.9004889913628268E-5</v>
       </c>
       <c r="R20">
-        <v>-3.8217195501605099E-4</v>
+        <v>-3.4638816861697649E-4</v>
       </c>
       <c r="S20">
-        <v>1.8584129691221309E-4</v>
+        <v>1.0268980970879458E-4</v>
       </c>
       <c r="T20">
-        <v>1.0367218748962481E-4</v>
+        <v>2.0086170280672914E-5</v>
       </c>
       <c r="U20">
-        <v>1.4400396157607225E-3</v>
+        <v>1.4338082258748598E-3</v>
       </c>
       <c r="V20">
-        <v>-3.8707329911725092E-4</v>
+        <v>-3.7669489887032356E-4</v>
       </c>
       <c r="W20">
-        <v>8.1187177557658172E-5</v>
+        <v>8.6277608255261318E-5</v>
       </c>
       <c r="X20">
-        <v>4.1355961610113233E-5</v>
+        <v>4.6019033076032806E-5</v>
       </c>
       <c r="Y20">
-        <v>3.3519444259469817E-5</v>
+        <v>4.3922389092400556E-5</v>
       </c>
       <c r="Z20">
-        <v>3.9544232753743009E-6</v>
+        <v>1.1918264766500042E-5</v>
       </c>
       <c r="AA20">
-        <v>1.2193991519297951E-5</v>
+        <v>2.0337663410299181E-5</v>
       </c>
       <c r="AB20">
-        <v>-1.568933238852414E-5</v>
+        <v>-1.0155547831822251E-5</v>
       </c>
       <c r="AC20">
-        <v>1.9161655377142548E-5</v>
+        <v>1.9886218302450158E-5</v>
       </c>
       <c r="AD20">
-        <v>-2.6469572485578251E-5</v>
+        <v>-3.1775308139086621E-5</v>
       </c>
       <c r="AE20">
-        <v>1.1721360213440366E-5</v>
+        <v>6.0271614670592616E-6</v>
       </c>
       <c r="AF20">
-        <v>9.2174241503439544E-4</v>
+        <v>1.0161438826846517E-3</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.2">
@@ -4562,97 +4562,97 @@
         <v>56</v>
       </c>
       <c r="B21">
-        <v>-8.9575253778909236E-2</v>
+        <v>-9.5214537267864593E-2</v>
       </c>
       <c r="C21">
-        <v>1.2888864281596204E-4</v>
+        <v>1.1905073398588788E-4</v>
       </c>
       <c r="D21">
-        <v>-5.6131187514539549E-5</v>
+        <v>-3.9630962419177906E-5</v>
       </c>
       <c r="E21">
-        <v>4.9716219899972034E-7</v>
+        <v>3.6666186084683935E-7</v>
       </c>
       <c r="F21">
-        <v>6.306579232923798E-5</v>
+        <v>7.7288522244261734E-5</v>
       </c>
       <c r="G21">
-        <v>1.0101082290138452E-4</v>
+        <v>1.1735735905567344E-4</v>
       </c>
       <c r="H21">
-        <v>5.7839320015892922E-5</v>
+        <v>5.4984855633013877E-5</v>
       </c>
       <c r="I21">
-        <v>-1.5639148942113326E-6</v>
+        <v>-3.3708711019775415E-6</v>
       </c>
       <c r="J21">
-        <v>-1.8228392450622168E-4</v>
+        <v>-1.8217420460480294E-4</v>
       </c>
       <c r="K21">
-        <v>-5.0795873741489768E-5</v>
+        <v>-4.6484309492659213E-5</v>
       </c>
       <c r="L21">
-        <v>9.8889032875812541E-5</v>
+        <v>9.0337666218841175E-5</v>
       </c>
       <c r="M21">
-        <v>7.8117580987995206E-5</v>
+        <v>7.7953104558420858E-5</v>
       </c>
       <c r="N21">
-        <v>1.4556349198360934E-4</v>
+        <v>1.5002552897824662E-4</v>
       </c>
       <c r="O21">
-        <v>7.6992634687152563E-5</v>
+        <v>7.6340792777190511E-5</v>
       </c>
       <c r="P21">
-        <v>2.1531454714899612E-5</v>
+        <v>2.3381858180763701E-5</v>
       </c>
       <c r="Q21">
-        <v>-2.8653459268976279E-4</v>
+        <v>-2.9070223405364387E-4</v>
       </c>
       <c r="R21">
-        <v>3.9059838023810264E-4</v>
+        <v>3.883545172748969E-4</v>
       </c>
       <c r="S21">
-        <v>-2.2725626399189443E-4</v>
+        <v>-2.4070265918691553E-4</v>
       </c>
       <c r="T21">
-        <v>-2.171365028712036E-4</v>
+        <v>-1.2204080069225373E-4</v>
       </c>
       <c r="U21">
-        <v>-3.8707329911725092E-4</v>
+        <v>-3.7669489887032356E-4</v>
       </c>
       <c r="V21">
-        <v>4.1999028039556331E-3</v>
+        <v>4.2159126883528023E-3</v>
       </c>
       <c r="W21">
-        <v>6.4804282601003699E-5</v>
+        <v>6.6728005251545132E-5</v>
       </c>
       <c r="X21">
-        <v>1.5284707775118722E-4</v>
+        <v>1.5637276049661658E-4</v>
       </c>
       <c r="Y21">
-        <v>1.4279562944136283E-5</v>
+        <v>1.6367861033354371E-5</v>
       </c>
       <c r="Z21">
-        <v>1.3021739258220867E-4</v>
+        <v>1.2900647662039927E-4</v>
       </c>
       <c r="AA21">
-        <v>4.1623959418040041E-5</v>
+        <v>4.6779451483714639E-5</v>
       </c>
       <c r="AB21">
-        <v>6.1840868144289005E-5</v>
+        <v>6.1309649792859797E-5</v>
       </c>
       <c r="AC21">
-        <v>1.2279161423655032E-6</v>
+        <v>1.2533754994691592E-6</v>
       </c>
       <c r="AD21">
-        <v>1.4801331372515415E-5</v>
+        <v>1.0683123865898217E-5</v>
       </c>
       <c r="AE21">
-        <v>-8.643213029227865E-5</v>
+        <v>-8.60921585123263E-5</v>
       </c>
       <c r="AF21">
-        <v>1.3660439129549486E-3</v>
+        <v>8.5672300024444877E-4</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.2">
@@ -4660,97 +4660,97 @@
         <v>41</v>
       </c>
       <c r="B22">
-        <v>0.24206049386872983</v>
+        <v>0.23991662873098082</v>
       </c>
       <c r="C22">
-        <v>1.3345126425377005E-4</v>
+        <v>1.2246231362551363E-4</v>
       </c>
       <c r="D22">
-        <v>-6.7465016128392952E-5</v>
+        <v>-5.6088664379352893E-5</v>
       </c>
       <c r="E22">
-        <v>6.662090024405409E-7</v>
+        <v>5.8161907022155884E-7</v>
       </c>
       <c r="F22">
-        <v>1.4470626196641523E-4</v>
+        <v>1.5317646621142156E-4</v>
       </c>
       <c r="G22">
-        <v>5.7965831031604742E-5</v>
+        <v>5.5624645884946866E-5</v>
       </c>
       <c r="H22">
-        <v>8.9744080367285635E-5</v>
+        <v>8.4693385359520821E-5</v>
       </c>
       <c r="I22">
-        <v>-1.511264226981817E-4</v>
+        <v>-1.5199253212248224E-4</v>
       </c>
       <c r="J22">
-        <v>-1.6425174750533955E-4</v>
+        <v>-1.6400049026041308E-4</v>
       </c>
       <c r="K22">
-        <v>-2.1145918025485661E-4</v>
+        <v>-2.0626614274486159E-4</v>
       </c>
       <c r="L22">
-        <v>7.9520853194377586E-5</v>
+        <v>6.7893106911379349E-5</v>
       </c>
       <c r="M22">
-        <v>-1.4858500685012085E-4</v>
+        <v>-1.4442909588583091E-4</v>
       </c>
       <c r="N22">
-        <v>-2.2796661723335993E-4</v>
+        <v>-2.1996446149501973E-4</v>
       </c>
       <c r="O22">
-        <v>-2.5685675830949698E-4</v>
+        <v>-2.5105798887131714E-4</v>
       </c>
       <c r="P22">
-        <v>-1.9175661010680575E-4</v>
+        <v>-1.8873634597326491E-4</v>
       </c>
       <c r="Q22">
-        <v>3.1952292265807682E-4</v>
+        <v>3.1426355071809928E-4</v>
       </c>
       <c r="R22">
-        <v>1.3085887932505458E-4</v>
+        <v>1.2121926822444319E-4</v>
       </c>
       <c r="S22">
-        <v>-3.4002197660835606E-5</v>
+        <v>-9.0096142385287167E-5</v>
       </c>
       <c r="T22">
-        <v>-5.6459651957089033E-5</v>
+        <v>-4.8482046843859386E-5</v>
       </c>
       <c r="U22">
-        <v>8.1187177557658172E-5</v>
+        <v>8.6277608255261318E-5</v>
       </c>
       <c r="V22">
-        <v>6.4804282601003699E-5</v>
+        <v>6.6728005251545132E-5</v>
       </c>
       <c r="W22">
-        <v>6.5553899059784372E-3</v>
+        <v>6.565999906691578E-3</v>
       </c>
       <c r="X22">
-        <v>5.5775166253274749E-3</v>
+        <v>5.5886845572016754E-3</v>
       </c>
       <c r="Y22">
-        <v>5.5693492150370606E-3</v>
+        <v>5.5836897298863347E-3</v>
       </c>
       <c r="Z22">
-        <v>5.600355025463884E-3</v>
+        <v>5.6096126105041749E-3</v>
       </c>
       <c r="AA22">
-        <v>5.5900887204728437E-3</v>
+        <v>5.6020299962277319E-3</v>
       </c>
       <c r="AB22">
-        <v>5.565013506240675E-3</v>
+        <v>5.5751490951724235E-3</v>
       </c>
       <c r="AC22">
-        <v>2.4294431255898242E-6</v>
+        <v>2.2049455490788755E-6</v>
       </c>
       <c r="AD22">
-        <v>2.1212966939832944E-5</v>
+        <v>1.8804419656084275E-5</v>
       </c>
       <c r="AE22">
-        <v>4.3754300290579744E-5</v>
+        <v>4.5988420942344845E-5</v>
       </c>
       <c r="AF22">
-        <v>-3.8754806573304476E-3</v>
+        <v>-4.2507347105164121E-3</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.2">
@@ -4758,97 +4758,97 @@
         <v>42</v>
       </c>
       <c r="B23">
-        <v>0.25977719823249595</v>
+        <v>0.25624357551963872</v>
       </c>
       <c r="C23">
-        <v>1.3106945136016793E-4</v>
+        <v>1.1841634004566988E-4</v>
       </c>
       <c r="D23">
-        <v>9.7113256569275608E-6</v>
+        <v>2.3621705846563201E-5</v>
       </c>
       <c r="E23">
-        <v>1.38548718467261E-7</v>
+        <v>3.2856827072145524E-8</v>
       </c>
       <c r="F23">
-        <v>1.435653601878778E-4</v>
+        <v>1.4883785957289786E-4</v>
       </c>
       <c r="G23">
-        <v>-2.5862671698198558E-6</v>
+        <v>-6.1543642715794489E-6</v>
       </c>
       <c r="H23">
-        <v>1.0561664733128601E-4</v>
+        <v>1.0227449040021161E-4</v>
       </c>
       <c r="I23">
-        <v>-1.1572734246231332E-4</v>
+        <v>-1.1537836761782016E-4</v>
       </c>
       <c r="J23">
-        <v>-1.5029601914325758E-4</v>
+        <v>-1.4747596137238556E-4</v>
       </c>
       <c r="K23">
-        <v>-2.9710069986508885E-4</v>
+        <v>-2.9102294568792721E-4</v>
       </c>
       <c r="L23">
-        <v>2.2787685722563608E-5</v>
+        <v>9.1786741238915684E-6</v>
       </c>
       <c r="M23">
-        <v>-1.02968327912793E-4</v>
+        <v>-1.0044767566196326E-4</v>
       </c>
       <c r="N23">
-        <v>-2.4941802218425026E-4</v>
+        <v>-2.4244449458122675E-4</v>
       </c>
       <c r="O23">
-        <v>-3.3086972915194034E-4</v>
+        <v>-3.2623527497734495E-4</v>
       </c>
       <c r="P23">
-        <v>-4.0795362771711089E-4</v>
+        <v>-4.0550502924804237E-4</v>
       </c>
       <c r="Q23">
-        <v>3.0820624492360993E-4</v>
+        <v>3.0083896246165551E-4</v>
       </c>
       <c r="R23">
-        <v>4.3387426228939062E-5</v>
+        <v>3.4437390712475403E-5</v>
       </c>
       <c r="S23">
-        <v>7.5752914376313492E-5</v>
+        <v>-2.3687929021631859E-5</v>
       </c>
       <c r="T23">
-        <v>-3.5487735153185568E-7</v>
+        <v>-6.6372444596110233E-5</v>
       </c>
       <c r="U23">
-        <v>4.1355961610113233E-5</v>
+        <v>4.6019033076032806E-5</v>
       </c>
       <c r="V23">
-        <v>1.5284707775118722E-4</v>
+        <v>1.5637276049661658E-4</v>
       </c>
       <c r="W23">
-        <v>5.5775166253274749E-3</v>
+        <v>5.5886845572016754E-3</v>
       </c>
       <c r="X23">
-        <v>6.5646968334980276E-3</v>
+        <v>6.5739828603584996E-3</v>
       </c>
       <c r="Y23">
-        <v>5.5875662533152962E-3</v>
+        <v>5.603033708659738E-3</v>
       </c>
       <c r="Z23">
-        <v>5.588998046554443E-3</v>
+        <v>5.5975466463629043E-3</v>
       </c>
       <c r="AA23">
-        <v>5.594063523029282E-3</v>
+        <v>5.6063691318284118E-3</v>
       </c>
       <c r="AB23">
-        <v>5.5470854162039031E-3</v>
+        <v>5.5571625800598769E-3</v>
       </c>
       <c r="AC23">
-        <v>3.112465242537512E-6</v>
+        <v>2.8547976749440013E-6</v>
       </c>
       <c r="AD23">
-        <v>3.9751670041318415E-5</v>
+        <v>3.6772286860930646E-5</v>
       </c>
       <c r="AE23">
-        <v>1.4410669271689358E-5</v>
+        <v>1.5565115333169384E-5</v>
       </c>
       <c r="AF23">
-        <v>-6.4913397276946706E-3</v>
+        <v>-6.9392962608397397E-3</v>
       </c>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.2">
@@ -4856,97 +4856,97 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>0.14695251080773772</v>
+        <v>0.14521188020378961</v>
       </c>
       <c r="C24">
-        <v>7.3175256894544811E-5</v>
+        <v>5.3230216531714952E-5</v>
       </c>
       <c r="D24">
-        <v>-2.7242360513751035E-5</v>
+        <v>1.2143799227627705E-6</v>
       </c>
       <c r="E24">
-        <v>2.4592369572416545E-7</v>
+        <v>2.6728374349146034E-8</v>
       </c>
       <c r="F24">
-        <v>4.6333843239345501E-5</v>
+        <v>6.0600137503937987E-5</v>
       </c>
       <c r="G24">
-        <v>-4.3240048640454457E-5</v>
+        <v>-4.5158532275312371E-5</v>
       </c>
       <c r="H24">
-        <v>1.253563055107607E-4</v>
+        <v>1.2191385129444571E-4</v>
       </c>
       <c r="I24">
-        <v>2.1116077383386407E-5</v>
+        <v>2.1642693637046503E-5</v>
       </c>
       <c r="J24">
-        <v>-3.0435953866161936E-5</v>
+        <v>-2.8842142467410542E-5</v>
       </c>
       <c r="K24">
-        <v>-2.7210251978592104E-4</v>
+        <v>-2.6567098142122941E-4</v>
       </c>
       <c r="L24">
-        <v>-7.1815127635796276E-6</v>
+        <v>-2.4033414581407526E-5</v>
       </c>
       <c r="M24">
-        <v>-1.3065368451483641E-4</v>
+        <v>-1.2464882319047031E-4</v>
       </c>
       <c r="N24">
-        <v>-3.0043872716400857E-4</v>
+        <v>-2.9083518978950033E-4</v>
       </c>
       <c r="O24">
-        <v>-3.4348086675609502E-4</v>
+        <v>-3.361037257944504E-4</v>
       </c>
       <c r="P24">
-        <v>-3.4378450321511007E-4</v>
+        <v>-3.4081909917388657E-4</v>
       </c>
       <c r="Q24">
-        <v>4.1541802196723128E-4</v>
+        <v>4.0775648551883732E-4</v>
       </c>
       <c r="R24">
-        <v>1.5536182369949356E-4</v>
+        <v>1.467512952495688E-4</v>
       </c>
       <c r="S24">
-        <v>3.2801598417574011E-5</v>
+        <v>9.3603901718592852E-5</v>
       </c>
       <c r="T24">
-        <v>1.2812588710301581E-4</v>
+        <v>-1.5413901220451406E-4</v>
       </c>
       <c r="U24">
-        <v>3.3519444259469817E-5</v>
+        <v>4.3922389092400556E-5</v>
       </c>
       <c r="V24">
-        <v>1.4279562944136283E-5</v>
+        <v>1.6367861033354371E-5</v>
       </c>
       <c r="W24">
-        <v>5.5693492150370606E-3</v>
+        <v>5.5836897298863347E-3</v>
       </c>
       <c r="X24">
-        <v>5.5875662533152962E-3</v>
+        <v>5.603033708659738E-3</v>
       </c>
       <c r="Y24">
-        <v>7.0873900815616904E-3</v>
+        <v>7.1160749970941902E-3</v>
       </c>
       <c r="Z24">
-        <v>5.5853909579848295E-3</v>
+        <v>5.5979776750722339E-3</v>
       </c>
       <c r="AA24">
-        <v>5.5865387760219978E-3</v>
+        <v>5.6023363320036202E-3</v>
       </c>
       <c r="AB24">
-        <v>5.5367004762778343E-3</v>
+        <v>5.5501722043315629E-3</v>
       </c>
       <c r="AC24">
-        <v>1.0668804859240165E-5</v>
+        <v>1.076773712683325E-5</v>
       </c>
       <c r="AD24">
-        <v>-6.4647051522359654E-5</v>
+        <v>-6.970219717220439E-5</v>
       </c>
       <c r="AE24">
-        <v>-3.9905022356864859E-5</v>
+        <v>-4.0481782723951606E-5</v>
       </c>
       <c r="AF24">
-        <v>-4.8444440937379825E-3</v>
+        <v>-5.7599498240735805E-3</v>
       </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.2">
@@ -4954,97 +4954,97 @@
         <v>44</v>
       </c>
       <c r="B25">
-        <v>0.11833250328237095</v>
+        <v>0.11376422781623149</v>
       </c>
       <c r="C25">
-        <v>1.6233783158817053E-4</v>
+        <v>1.3865831618414337E-4</v>
       </c>
       <c r="D25">
-        <v>6.6150673977263819E-5</v>
+        <v>6.9302106205107461E-5</v>
       </c>
       <c r="E25">
-        <v>-3.6777087458663565E-7</v>
+        <v>-3.7698988840557685E-7</v>
       </c>
       <c r="F25">
-        <v>9.461183932895495E-5</v>
+        <v>1.030180871239017E-4</v>
       </c>
       <c r="G25">
-        <v>-5.6786065210284731E-5</v>
+        <v>-5.2784243551179388E-5</v>
       </c>
       <c r="H25">
-        <v>1.4931859647228504E-4</v>
+        <v>1.4436710684840757E-4</v>
       </c>
       <c r="I25">
-        <v>-1.4420484570888768E-4</v>
+        <v>-1.4584323727857406E-4</v>
       </c>
       <c r="J25">
-        <v>-1.4479438038654535E-4</v>
+        <v>-1.4158238213639318E-4</v>
       </c>
       <c r="K25">
-        <v>-2.5539691257208904E-4</v>
+        <v>-2.5171508452830624E-4</v>
       </c>
       <c r="L25">
-        <v>4.0926054849702194E-5</v>
+        <v>3.194206417965386E-5</v>
       </c>
       <c r="M25">
-        <v>-9.2374662380601642E-5</v>
+        <v>-9.1092954269858745E-5</v>
       </c>
       <c r="N25">
-        <v>-2.5412350266922025E-4</v>
+        <v>-2.4887505658916865E-4</v>
       </c>
       <c r="O25">
-        <v>-2.1823233229966918E-4</v>
+        <v>-2.1536049324493009E-4</v>
       </c>
       <c r="P25">
-        <v>-1.9388571336950797E-4</v>
+        <v>-1.9405216603030507E-4</v>
       </c>
       <c r="Q25">
-        <v>4.400216802932542E-4</v>
+        <v>4.3272826800487568E-4</v>
       </c>
       <c r="R25">
-        <v>1.8135024026671694E-4</v>
+        <v>1.2784028704198366E-4</v>
       </c>
       <c r="S25">
-        <v>-6.4812539956370444E-6</v>
+        <v>-2.7170147437050388E-5</v>
       </c>
       <c r="T25">
-        <v>-2.417736306926585E-5</v>
+        <v>2.2633020274732615E-5</v>
       </c>
       <c r="U25">
-        <v>3.9544232753743009E-6</v>
+        <v>1.1918264766500042E-5</v>
       </c>
       <c r="V25">
-        <v>1.3021739258220867E-4</v>
+        <v>1.2900647662039927E-4</v>
       </c>
       <c r="W25">
-        <v>5.600355025463884E-3</v>
+        <v>5.6096126105041749E-3</v>
       </c>
       <c r="X25">
-        <v>5.588998046554443E-3</v>
+        <v>5.5975466463629043E-3</v>
       </c>
       <c r="Y25">
-        <v>5.5853909579848295E-3</v>
+        <v>5.5979776750722339E-3</v>
       </c>
       <c r="Z25">
-        <v>6.4675273863785271E-3</v>
+        <v>6.469535202487945E-3</v>
       </c>
       <c r="AA25">
-        <v>5.5910075039708072E-3</v>
+        <v>5.6007274304517964E-3</v>
       </c>
       <c r="AB25">
-        <v>5.5793096485652945E-3</v>
+        <v>5.5867791216551044E-3</v>
       </c>
       <c r="AC25">
-        <v>1.9620955763014466E-6</v>
+        <v>1.4202039484412414E-6</v>
       </c>
       <c r="AD25">
-        <v>2.1325139556028615E-6</v>
+        <v>-1.2177033538397688E-6</v>
       </c>
       <c r="AE25">
-        <v>1.0190866489515104E-5</v>
+        <v>1.2426743780448099E-5</v>
       </c>
       <c r="AF25">
-        <v>-8.1469642765172531E-3</v>
+        <v>-8.27618962564141E-3</v>
       </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.2">
@@ -5052,97 +5052,97 @@
         <v>45</v>
       </c>
       <c r="B26">
-        <v>0.20537885973884176</v>
+        <v>0.20219026314534</v>
       </c>
       <c r="C26">
-        <v>1.2388701297518954E-4</v>
+        <v>1.0818608546091598E-4</v>
       </c>
       <c r="D26">
-        <v>7.5648819666561395E-5</v>
+        <v>9.9680704468585457E-5</v>
       </c>
       <c r="E26">
-        <v>-4.9821489612415087E-7</v>
+        <v>-6.8591618313773562E-7</v>
       </c>
       <c r="F26">
-        <v>-1.5450365248449727E-5</v>
+        <v>-2.615179518489566E-6</v>
       </c>
       <c r="G26">
-        <v>-1.5583452042863821E-4</v>
+        <v>-1.5847080904152558E-4</v>
       </c>
       <c r="H26">
-        <v>9.1864724172606199E-5</v>
+        <v>8.724676520181551E-5</v>
       </c>
       <c r="I26">
-        <v>-1.1077226515824007E-4</v>
+        <v>-1.1108130216969212E-4</v>
       </c>
       <c r="J26">
-        <v>3.6914701583406692E-5</v>
+        <v>3.8227683195932172E-5</v>
       </c>
       <c r="K26">
-        <v>-2.0067173771618776E-4</v>
+        <v>-1.951670658954595E-4</v>
       </c>
       <c r="L26">
-        <v>3.855480742998409E-5</v>
+        <v>2.1387047368748562E-5</v>
       </c>
       <c r="M26">
-        <v>-1.3977880512156812E-4</v>
+        <v>-1.3600591306319029E-4</v>
       </c>
       <c r="N26">
-        <v>-2.8770017743928798E-4</v>
+        <v>-2.8005638457713684E-4</v>
       </c>
       <c r="O26">
-        <v>-3.4910654710936461E-4</v>
+        <v>-3.4239409481394325E-4</v>
       </c>
       <c r="P26">
-        <v>-3.2793406210695315E-4</v>
+        <v>-3.2387872231870365E-4</v>
       </c>
       <c r="Q26">
-        <v>2.2695569696376585E-4</v>
+        <v>2.2044725784620933E-4</v>
       </c>
       <c r="R26">
-        <v>1.1683960778865706E-4</v>
+        <v>1.192564933582504E-4</v>
       </c>
       <c r="S26">
-        <v>3.2374485291783483E-5</v>
+        <v>-3.1612628740141854E-5</v>
       </c>
       <c r="T26">
-        <v>2.4388886001330216E-5</v>
+        <v>-1.2648232008996389E-4</v>
       </c>
       <c r="U26">
-        <v>1.2193991519297951E-5</v>
+        <v>2.0337663410299181E-5</v>
       </c>
       <c r="V26">
-        <v>4.1623959418040041E-5</v>
+        <v>4.6779451483714639E-5</v>
       </c>
       <c r="W26">
-        <v>5.5900887204728437E-3</v>
+        <v>5.6020299962277319E-3</v>
       </c>
       <c r="X26">
-        <v>5.594063523029282E-3</v>
+        <v>5.6063691318284118E-3</v>
       </c>
       <c r="Y26">
-        <v>5.5865387760219978E-3</v>
+        <v>5.6023363320036202E-3</v>
       </c>
       <c r="Z26">
-        <v>5.5910075039708072E-3</v>
+        <v>5.6007274304517964E-3</v>
       </c>
       <c r="AA26">
-        <v>6.2775716921203454E-3</v>
+        <v>6.2919386641834708E-3</v>
       </c>
       <c r="AB26">
-        <v>5.5641582263380469E-3</v>
+        <v>5.5752842344851351E-3</v>
       </c>
       <c r="AC26">
-        <v>-1.114601365970909E-6</v>
+        <v>-1.1625259043383916E-6</v>
       </c>
       <c r="AD26">
-        <v>-1.1979624869085364E-5</v>
+        <v>-1.7669484237886222E-5</v>
       </c>
       <c r="AE26">
-        <v>-4.6923454415907393E-5</v>
+        <v>-4.7732134044238582E-5</v>
       </c>
       <c r="AF26">
-        <v>-8.1163562147327471E-3</v>
+        <v>-8.8774891191270508E-3</v>
       </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.2">
@@ -5150,97 +5150,97 @@
         <v>46</v>
       </c>
       <c r="B27">
-        <v>9.4328455719131885E-2</v>
+        <v>9.0700948916997357E-2</v>
       </c>
       <c r="C27">
-        <v>2.0847743153764003E-5</v>
+        <v>6.904116465748897E-6</v>
       </c>
       <c r="D27">
-        <v>-2.1534158072024356E-5</v>
+        <v>-7.81267756554474E-6</v>
       </c>
       <c r="E27">
-        <v>1.7642125534409045E-7</v>
+        <v>7.4841568163490618E-8</v>
       </c>
       <c r="F27">
-        <v>2.2784830465763517E-5</v>
+        <v>2.8694224247772376E-5</v>
       </c>
       <c r="G27">
-        <v>-5.9981935310825935E-5</v>
+        <v>-6.1231019737612719E-5</v>
       </c>
       <c r="H27">
-        <v>1.2677015335271161E-4</v>
+        <v>1.216628739850352E-4</v>
       </c>
       <c r="I27">
-        <v>-1.1622786640813599E-4</v>
+        <v>-1.170967151515451E-4</v>
       </c>
       <c r="J27">
-        <v>1.8256000519498855E-5</v>
+        <v>2.333301139561747E-5</v>
       </c>
       <c r="K27">
-        <v>-3.5836503714540766E-4</v>
+        <v>-3.5260073014265619E-4</v>
       </c>
       <c r="L27">
-        <v>1.7665281624254948E-4</v>
+        <v>1.6773148791221059E-4</v>
       </c>
       <c r="M27">
-        <v>-4.0230297744125077E-5</v>
+        <v>-3.7767557070671242E-5</v>
       </c>
       <c r="N27">
-        <v>-2.0856127885315033E-4</v>
+        <v>-2.0339001972587178E-4</v>
       </c>
       <c r="O27">
-        <v>-2.2080638520407311E-4</v>
+        <v>-2.1777243440040928E-4</v>
       </c>
       <c r="P27">
-        <v>-1.5545698381863246E-4</v>
+        <v>-1.5439345875577432E-4</v>
       </c>
       <c r="Q27">
-        <v>3.164770103205837E-4</v>
+        <v>3.0965431843519556E-4</v>
       </c>
       <c r="R27">
-        <v>1.5333264016528103E-4</v>
+        <v>1.3048039836500384E-4</v>
       </c>
       <c r="S27">
-        <v>-2.9013127443377508E-5</v>
+        <v>8.5678058381575238E-5</v>
       </c>
       <c r="T27">
-        <v>1.1918428849947609E-4</v>
+        <v>-2.6678346156877066E-5</v>
       </c>
       <c r="U27">
-        <v>-1.568933238852414E-5</v>
+        <v>-1.0155547831822251E-5</v>
       </c>
       <c r="V27">
-        <v>6.1840868144289005E-5</v>
+        <v>6.1309649792859797E-5</v>
       </c>
       <c r="W27">
-        <v>5.565013506240675E-3</v>
+        <v>5.5751490951724235E-3</v>
       </c>
       <c r="X27">
-        <v>5.5470854162039031E-3</v>
+        <v>5.5571625800598769E-3</v>
       </c>
       <c r="Y27">
-        <v>5.5367004762778343E-3</v>
+        <v>5.5501722043315629E-3</v>
       </c>
       <c r="Z27">
-        <v>5.5793096485652945E-3</v>
+        <v>5.5867791216551044E-3</v>
       </c>
       <c r="AA27">
-        <v>5.5641582263380469E-3</v>
+        <v>5.5752842344851351E-3</v>
       </c>
       <c r="AB27">
-        <v>6.4173170190779073E-3</v>
+        <v>6.4263435122981277E-3</v>
       </c>
       <c r="AC27">
-        <v>-6.8085806861010984E-7</v>
+        <v>-1.033716147270756E-6</v>
       </c>
       <c r="AD27">
-        <v>-1.0562724558663486E-5</v>
+        <v>-1.1612915465998835E-5</v>
       </c>
       <c r="AE27">
-        <v>-7.4102342771872887E-6</v>
+        <v>-6.1415532766426889E-6</v>
       </c>
       <c r="AF27">
-        <v>-4.6728760345997357E-3</v>
+        <v>-5.1189027836808718E-3</v>
       </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.2">
@@ -5248,97 +5248,97 @@
         <v>47</v>
       </c>
       <c r="B28">
-        <v>-1.2765603020222923E-2</v>
+        <v>-1.2784743266723547E-2</v>
       </c>
       <c r="C28">
-        <v>3.9004104743595812E-6</v>
+        <v>2.5353164022284618E-6</v>
       </c>
       <c r="D28">
-        <v>7.954545316162789E-6</v>
+        <v>7.9028390590845342E-6</v>
       </c>
       <c r="E28">
-        <v>-8.8276431555639443E-8</v>
+        <v>-8.6962150874775284E-8</v>
       </c>
       <c r="F28">
-        <v>-2.562358652305935E-5</v>
+        <v>-2.65208927625434E-5</v>
       </c>
       <c r="G28">
-        <v>-2.1539599776004468E-5</v>
+        <v>-2.1592680214786318E-5</v>
       </c>
       <c r="H28">
-        <v>-1.2375192441873928E-7</v>
+        <v>-7.5258779324508928E-8</v>
       </c>
       <c r="I28">
-        <v>1.9269307085190652E-5</v>
+        <v>1.9389961749731991E-5</v>
       </c>
       <c r="J28">
-        <v>3.0587791750546361E-5</v>
+        <v>3.1534090340889229E-5</v>
       </c>
       <c r="K28">
-        <v>1.0989811566303209E-5</v>
+        <v>1.0821262241786595E-5</v>
       </c>
       <c r="L28">
-        <v>1.2996587300830454E-5</v>
+        <v>1.338068976918949E-5</v>
       </c>
       <c r="M28">
-        <v>1.0302928446353325E-5</v>
+        <v>1.0084306560428356E-5</v>
       </c>
       <c r="N28">
-        <v>1.4548855961440797E-5</v>
+        <v>1.4648079613180153E-5</v>
       </c>
       <c r="O28">
-        <v>3.0786045339419217E-5</v>
+        <v>3.0603459678323622E-5</v>
       </c>
       <c r="P28">
-        <v>2.900263651559643E-5</v>
+        <v>2.8749809877302813E-5</v>
       </c>
       <c r="Q28">
-        <v>-2.7909371255910195E-6</v>
+        <v>-2.8648510659164898E-6</v>
       </c>
       <c r="R28">
-        <v>4.7143973248359785E-6</v>
+        <v>1.0884319646008893E-8</v>
       </c>
       <c r="S28">
-        <v>3.0286934443505986E-6</v>
+        <v>1.5624033055573806E-5</v>
       </c>
       <c r="T28">
-        <v>1.3435094568229044E-5</v>
+        <v>5.5367129802432136E-6</v>
       </c>
       <c r="U28">
-        <v>1.9161655377142548E-5</v>
+        <v>1.9886218302450158E-5</v>
       </c>
       <c r="V28">
-        <v>1.2279161423655032E-6</v>
+        <v>1.2533754994691592E-6</v>
       </c>
       <c r="W28">
-        <v>2.4294431255898242E-6</v>
+        <v>2.2049455490788755E-6</v>
       </c>
       <c r="X28">
-        <v>3.112465242537512E-6</v>
+        <v>2.8547976749440013E-6</v>
       </c>
       <c r="Y28">
-        <v>1.0668804859240165E-5</v>
+        <v>1.076773712683325E-5</v>
       </c>
       <c r="Z28">
-        <v>1.9620955763014466E-6</v>
+        <v>1.4202039484412414E-6</v>
       </c>
       <c r="AA28">
-        <v>-1.114601365970909E-6</v>
+        <v>-1.1625259043383916E-6</v>
       </c>
       <c r="AB28">
-        <v>-6.8085806861010984E-7</v>
+        <v>-1.033716147270756E-6</v>
       </c>
       <c r="AC28">
-        <v>1.1327667015425617E-5</v>
+        <v>1.1325146511577549E-5</v>
       </c>
       <c r="AD28">
-        <v>-5.1766632662052309E-5</v>
+        <v>-5.1944754159041913E-5</v>
       </c>
       <c r="AE28">
-        <v>-6.1226596975042628E-5</v>
+        <v>-6.1322572801623265E-5</v>
       </c>
       <c r="AF28">
-        <v>-4.0434643266515921E-4</v>
+        <v>-4.0443249410909276E-4</v>
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.2">
@@ -5346,97 +5346,97 @@
         <v>57</v>
       </c>
       <c r="B29">
-        <v>-0.10174073730846028</v>
+        <v>-0.10375050595729865</v>
       </c>
       <c r="C29">
-        <v>-3.2800634213444929E-5</v>
+        <v>-2.3776572513753403E-5</v>
       </c>
       <c r="D29">
-        <v>-2.3302600625496606E-5</v>
+        <v>-3.6344385382469646E-5</v>
       </c>
       <c r="E29">
-        <v>8.8175852370998235E-8</v>
+        <v>1.9120497312020849E-7</v>
       </c>
       <c r="F29">
-        <v>1.9954943073725862E-5</v>
+        <v>1.2217974530180642E-5</v>
       </c>
       <c r="G29">
-        <v>-5.2777360766777942E-5</v>
+        <v>-5.6279052144281305E-5</v>
       </c>
       <c r="H29">
-        <v>6.6943520880069843E-6</v>
+        <v>5.0381547394161199E-6</v>
       </c>
       <c r="I29">
-        <v>-8.1355723930311825E-6</v>
+        <v>-8.5274694678563897E-6</v>
       </c>
       <c r="J29">
-        <v>1.2025088819238305E-4</v>
+        <v>1.2208290770163513E-4</v>
       </c>
       <c r="K29">
-        <v>3.6627567156484659E-5</v>
+        <v>3.6093097805065867E-5</v>
       </c>
       <c r="L29">
-        <v>-4.2586947257999309E-5</v>
+        <v>-4.2790836759010187E-5</v>
       </c>
       <c r="M29">
-        <v>-6.366220707879457E-5</v>
+        <v>-6.3177250266289336E-5</v>
       </c>
       <c r="N29">
-        <v>-1.3244629703063927E-5</v>
+        <v>-1.5044552863043405E-5</v>
       </c>
       <c r="O29">
-        <v>-7.2938601358510553E-5</v>
+        <v>-7.6728373431216371E-5</v>
       </c>
       <c r="P29">
-        <v>-6.7969074724705996E-5</v>
+        <v>-6.9070441358058026E-5</v>
       </c>
       <c r="Q29">
-        <v>-5.8552944791506577E-5</v>
+        <v>-5.9196877903071657E-5</v>
       </c>
       <c r="R29">
-        <v>6.0870600581627811E-5</v>
+        <v>6.0972931589001102E-5</v>
       </c>
       <c r="S29">
-        <v>-1.1249496239385979E-4</v>
+        <v>-1.7872411875424592E-4</v>
       </c>
       <c r="T29">
-        <v>-1.9424870032547529E-4</v>
+        <v>7.5151238037992826E-5</v>
       </c>
       <c r="U29">
-        <v>-2.6469572485578251E-5</v>
+        <v>-3.1775308139086621E-5</v>
       </c>
       <c r="V29">
-        <v>1.4801331372515415E-5</v>
+        <v>1.0683123865898217E-5</v>
       </c>
       <c r="W29">
-        <v>2.1212966939832944E-5</v>
+        <v>1.8804419656084275E-5</v>
       </c>
       <c r="X29">
-        <v>3.9751670041318415E-5</v>
+        <v>3.6772286860930646E-5</v>
       </c>
       <c r="Y29">
-        <v>-6.4647051522359654E-5</v>
+        <v>-6.970219717220439E-5</v>
       </c>
       <c r="Z29">
-        <v>2.1325139556028615E-6</v>
+        <v>-1.2177033538397688E-6</v>
       </c>
       <c r="AA29">
-        <v>-1.1979624869085364E-5</v>
+        <v>-1.7669484237886222E-5</v>
       </c>
       <c r="AB29">
-        <v>-1.0562724558663486E-5</v>
+        <v>-1.1612915465998835E-5</v>
       </c>
       <c r="AC29">
-        <v>-5.1766632662052309E-5</v>
+        <v>-5.1944754159041913E-5</v>
       </c>
       <c r="AD29">
-        <v>2.0024169521837211E-3</v>
+        <v>1.9972247089062828E-3</v>
       </c>
       <c r="AE29">
-        <v>5.1836651356838208E-4</v>
+        <v>5.2015278159011269E-4</v>
       </c>
       <c r="AF29">
-        <v>1.8339807106376935E-3</v>
+        <v>2.2454379278869395E-3</v>
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.2">
@@ -5444,97 +5444,97 @@
         <v>58</v>
       </c>
       <c r="B30">
-        <v>-0.14254022296654414</v>
+        <v>-0.14415804782230582</v>
       </c>
       <c r="C30">
-        <v>-1.6362622963248278E-5</v>
+        <v>-6.2605724090432444E-6</v>
       </c>
       <c r="D30">
-        <v>-1.1881164137514388E-4</v>
+        <v>-1.1806164469294056E-4</v>
       </c>
       <c r="E30">
-        <v>8.6192674716333495E-7</v>
+        <v>8.4897259201063401E-7</v>
       </c>
       <c r="F30">
-        <v>4.1295043706562895E-5</v>
+        <v>4.8669687654673971E-5</v>
       </c>
       <c r="G30">
-        <v>4.4807082904333578E-5</v>
+        <v>4.852695168872101E-5</v>
       </c>
       <c r="H30">
-        <v>-7.5394154640962691E-6</v>
+        <v>-8.4157082835525834E-6</v>
       </c>
       <c r="I30">
-        <v>7.5426767904021802E-6</v>
+        <v>6.5353898931124832E-6</v>
       </c>
       <c r="J30">
-        <v>1.5399953978041669E-5</v>
+        <v>8.8173611989782186E-6</v>
       </c>
       <c r="K30">
-        <v>3.6191158535631E-5</v>
+        <v>3.9237592265942796E-5</v>
       </c>
       <c r="L30">
-        <v>-5.668123728520217E-5</v>
+        <v>-6.2428390317280889E-5</v>
       </c>
       <c r="M30">
-        <v>-1.2898703690403159E-5</v>
+        <v>-1.0207168516141178E-5</v>
       </c>
       <c r="N30">
-        <v>1.8165728128279783E-5</v>
+        <v>1.6109562603758331E-5</v>
       </c>
       <c r="O30">
-        <v>-6.0624952156468261E-5</v>
+        <v>-6.0861654323060739E-5</v>
       </c>
       <c r="P30">
-        <v>6.3133461328519595E-6</v>
+        <v>7.8556709443727314E-6</v>
       </c>
       <c r="Q30">
-        <v>-2.0434884494165411E-5</v>
+        <v>-2.0531197943280403E-5</v>
       </c>
       <c r="R30">
-        <v>4.8794614115166062E-5</v>
+        <v>8.481826988177444E-5</v>
       </c>
       <c r="S30">
-        <v>-8.3169900872820043E-5</v>
+        <v>-1.6821745419701769E-4</v>
       </c>
       <c r="T30">
-        <v>-1.5139558668159948E-4</v>
+        <v>-5.1538663644032368E-5</v>
       </c>
       <c r="U30">
-        <v>1.1721360213440366E-5</v>
+        <v>6.0271614670592616E-6</v>
       </c>
       <c r="V30">
-        <v>-8.643213029227865E-5</v>
+        <v>-8.60921585123263E-5</v>
       </c>
       <c r="W30">
-        <v>4.3754300290579744E-5</v>
+        <v>4.5988420942344845E-5</v>
       </c>
       <c r="X30">
-        <v>1.4410669271689358E-5</v>
+        <v>1.5565115333169384E-5</v>
       </c>
       <c r="Y30">
-        <v>-3.9905022356864859E-5</v>
+        <v>-4.0481782723951606E-5</v>
       </c>
       <c r="Z30">
-        <v>1.0190866489515104E-5</v>
+        <v>1.2426743780448099E-5</v>
       </c>
       <c r="AA30">
-        <v>-4.6923454415907393E-5</v>
+        <v>-4.7732134044238582E-5</v>
       </c>
       <c r="AB30">
-        <v>-7.4102342771872887E-6</v>
+        <v>-6.1415532766426889E-6</v>
       </c>
       <c r="AC30">
-        <v>-6.1226596975042628E-5</v>
+        <v>-6.1322572801623265E-5</v>
       </c>
       <c r="AD30">
-        <v>5.1836651356838208E-4</v>
+        <v>5.2015278159011269E-4</v>
       </c>
       <c r="AE30">
-        <v>1.8927486686804004E-3</v>
+        <v>1.8985645626088787E-3</v>
       </c>
       <c r="AF30">
-        <v>4.8829812015429063E-3</v>
+        <v>4.8771004306105443E-3</v>
       </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.2">
@@ -5542,97 +5542,97 @@
         <v>49</v>
       </c>
       <c r="B31">
-        <v>-3.8266336296705878</v>
+        <v>-3.4766705973745746</v>
       </c>
       <c r="C31">
-        <v>-9.8211081736195426E-3</v>
+        <v>-1.0362830863151266E-2</v>
       </c>
       <c r="D31">
-        <v>-0.12073367643394517</v>
+        <v>-0.12185803817751206</v>
       </c>
       <c r="E31">
-        <v>9.8004909252421158E-4</v>
+        <v>9.899097002269196E-4</v>
       </c>
       <c r="F31">
-        <v>9.0213049877748031E-2</v>
+        <v>8.891250148184171E-2</v>
       </c>
       <c r="G31">
-        <v>8.3696769059056486E-2</v>
+        <v>8.2591000956276639E-2</v>
       </c>
       <c r="H31">
-        <v>-8.8888510185315336E-4</v>
+        <v>-7.4842086026358917E-4</v>
       </c>
       <c r="I31">
-        <v>1.1886449373839716E-4</v>
+        <v>2.4179104459880023E-4</v>
       </c>
       <c r="J31">
-        <v>-8.26777603667746E-2</v>
+        <v>-8.0972410481051138E-2</v>
       </c>
       <c r="K31">
-        <v>1.7422100399287297E-3</v>
+        <v>1.5604631246996618E-3</v>
       </c>
       <c r="L31">
-        <v>-2.0037704559520836E-2</v>
+        <v>-1.9576070744094703E-2</v>
       </c>
       <c r="M31">
-        <v>-3.9375238607508162E-3</v>
+        <v>-3.6488735544846183E-3</v>
       </c>
       <c r="N31">
-        <v>2.2686468873432813E-3</v>
+        <v>2.2789462033859474E-3</v>
       </c>
       <c r="O31">
-        <v>-6.1661017433234377E-4</v>
+        <v>-8.2375056725186857E-4</v>
       </c>
       <c r="P31">
-        <v>1.8750322611581632E-3</v>
+        <v>1.8947356936218698E-3</v>
       </c>
       <c r="Q31">
-        <v>6.0889401524989763E-3</v>
+        <v>6.096500656888419E-3</v>
       </c>
       <c r="R31">
-        <v>-4.3589147659581773E-3</v>
+        <v>-9.9367354861983545E-3</v>
       </c>
       <c r="S31">
-        <v>8.3108403005202891E-3</v>
+        <v>7.0811416908349023E-3</v>
       </c>
       <c r="T31">
-        <v>2.2384526513898467E-3</v>
+        <v>1.4227122448520785E-2</v>
       </c>
       <c r="U31">
-        <v>9.2174241503439544E-4</v>
+        <v>1.0161438826846517E-3</v>
       </c>
       <c r="V31">
-        <v>1.3660439129549486E-3</v>
+        <v>8.5672300024444877E-4</v>
       </c>
       <c r="W31">
-        <v>-3.8754806573304476E-3</v>
+        <v>-4.2507347105164121E-3</v>
       </c>
       <c r="X31">
-        <v>-6.4913397276946706E-3</v>
+        <v>-6.9392962608397397E-3</v>
       </c>
       <c r="Y31">
-        <v>-4.8444440937379825E-3</v>
+        <v>-5.7599498240735805E-3</v>
       </c>
       <c r="Z31">
-        <v>-8.1469642765172531E-3</v>
+        <v>-8.27618962564141E-3</v>
       </c>
       <c r="AA31">
-        <v>-8.1163562147327471E-3</v>
+        <v>-8.8774891191270508E-3</v>
       </c>
       <c r="AB31">
-        <v>-4.6728760345997357E-3</v>
+        <v>-5.1189027836808718E-3</v>
       </c>
       <c r="AC31">
-        <v>-4.0434643266515921E-4</v>
+        <v>-4.0443249410909276E-4</v>
       </c>
       <c r="AD31">
-        <v>1.8339807106376935E-3</v>
+        <v>2.2454379278869395E-3</v>
       </c>
       <c r="AE31">
-        <v>4.8829812015429063E-3</v>
+        <v>4.8771004306105443E-3</v>
       </c>
       <c r="AF31">
-        <v>3.7246269383248922</v>
+        <v>3.757441185828533</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_retirement.xlsx
+++ b/input/ES/reg_retirement.xlsx
@@ -1,29 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/SimPathsEU_AUG/input/ES/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E7A8BD-DD46-6B4B-94CA-7EADC2818758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="Gof" sheetId="2" r:id="rId2"/>
-    <sheet name="R1a" sheetId="3" r:id="rId3"/>
-    <sheet name="R1b" sheetId="4" r:id="rId4"/>
+    <sheet name="Info" sheetId="1" r:id="rId2"/>
+    <sheet name="Gof" sheetId="2" r:id="rId4"/>
+    <sheet name="R1a" sheetId="3" r:id="rId5"/>
+    <sheet name="R1b" sheetId="4" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="140" uniqueCount="60">
   <si>
     <t>Description</t>
   </si>
@@ -200,21 +193,19 @@
   </si>
   <si>
     <t>Y2023</t>
+  </si>
+  <si>
+    <t>Reached_Retirement_Age_Les_c2_No</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -237,347 +228,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,7 +250,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -593,7 +258,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -601,7 +266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -609,7 +274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -617,7 +282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -625,7 +290,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -634,16 +299,15 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -663,83 +327,128 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2">
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.32016434260509796</v>
-      </c>
+        <v>0.32002982932169932</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
       <c r="E5" t="s">
         <v>23</v>
       </c>
       <c r="F5">
-        <v>1686.3826534733244</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1684.8355304795728</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6">
         <v>21276</v>
       </c>
+      <c r="C6"/>
+      <c r="D6"/>
       <c r="E6" t="s">
         <v>24</v>
       </c>
       <c r="F6">
-        <v>-4802802.9741875418</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-4803745.6972785164</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="F7"/>
+    </row>
+    <row r="8">
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="F8"/>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="F9"/>
+    </row>
+    <row r="10">
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="F10"/>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11">
-        <v>0.32501950235748978</v>
-      </c>
+        <v>0.32491458237456605</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11"/>
       <c r="E11" t="s">
         <v>23</v>
       </c>
       <c r="F11">
-        <v>3443.7101888757511</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>3439.5939195856995</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12">
         <v>62248</v>
       </c>
+      <c r="C12"/>
+      <c r="D12"/>
       <c r="E12" t="s">
         <v>24</v>
       </c>
       <c r="F12">
-        <v>-10761951.526744192</v>
+        <v>-10763627.588565452</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -816,1788 +525,1787 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
       <c r="B2">
-        <v>0.2887942671573514</v>
+        <v>0.28895202614977933</v>
       </c>
       <c r="C2">
-        <v>3.2772000983176466E-3</v>
+        <v>0.0032792079086632897</v>
       </c>
       <c r="D2">
-        <v>4.2483191885534346E-4</v>
+        <v>0.00042608194162544063</v>
       </c>
       <c r="E2">
-        <v>-2.5317882363579935E-6</v>
+        <v>-2.5423473035224351e-06</v>
       </c>
       <c r="F2">
-        <v>1.2284936470375972E-4</v>
+        <v>0.0001277736417461918</v>
       </c>
       <c r="G2">
-        <v>6.1169123473884548E-4</v>
+        <v>0.00061222217084306424</v>
       </c>
       <c r="H2">
-        <v>3.1967730147480588E-4</v>
+        <v>0.00032096859283766734</v>
       </c>
       <c r="I2">
-        <v>9.202019046648082E-5</v>
+        <v>8.9455321468731873e-05</v>
       </c>
       <c r="J2">
-        <v>-7.331760072023586E-5</v>
+        <v>-8.0041004401561785e-05</v>
       </c>
       <c r="K2">
-        <v>1.1337716315218516E-4</v>
+        <v>0.00015288528878599667</v>
       </c>
       <c r="L2">
-        <v>-1.9397742251601774E-4</v>
+        <v>-0.00018990157009662466</v>
       </c>
       <c r="M2">
-        <v>-5.7890159434744083E-5</v>
+        <v>-4.819900772676445e-05</v>
       </c>
       <c r="N2">
-        <v>-4.4495405509703144E-4</v>
+        <v>-0.00041367719293427857</v>
       </c>
       <c r="O2">
-        <v>-7.4780033940842635E-4</v>
+        <v>-0.0007160802721547934</v>
       </c>
       <c r="P2">
-        <v>-1.553361962015571E-3</v>
+        <v>-0.0015633069937882097</v>
       </c>
       <c r="Q2">
-        <v>3.7471880904776087E-4</v>
+        <v>0.0003755287546525751</v>
       </c>
       <c r="R2">
-        <v>4.4969172702185364E-4</v>
+        <v>0.00044776713366126734</v>
       </c>
       <c r="S2">
-        <v>8.309067437706273E-4</v>
+        <v>0.00082959803679514914</v>
       </c>
       <c r="T2">
-        <v>5.1643597614740725E-4</v>
+        <v>0.00051647145245573554</v>
       </c>
       <c r="U2">
-        <v>1.7082526894713007E-4</v>
+        <v>0.00017059230967167416</v>
       </c>
       <c r="V2">
-        <v>7.3700127852097672E-4</v>
+        <v>0.00073812788105235097</v>
       </c>
       <c r="W2">
-        <v>-7.9151029552920537E-5</v>
+        <v>-7.9289225411918182e-05</v>
       </c>
       <c r="X2">
-        <v>1.8073783339145636E-4</v>
+        <v>0.00018216001871530795</v>
       </c>
       <c r="Y2">
-        <v>-1.6808861133236104E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.016876669133454862</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3">
-        <v>-0.19443227834433768</v>
+        <v>-0.19534838749624184</v>
       </c>
       <c r="C3">
-        <v>4.2483191885534346E-4</v>
+        <v>0.00042608194162544063</v>
       </c>
       <c r="D3">
-        <v>8.3841316967444013E-3</v>
+        <v>0.0083841222498605012</v>
       </c>
       <c r="E3">
-        <v>-6.7423446384728058E-5</v>
+        <v>-6.7425200104710768e-05</v>
       </c>
       <c r="F3">
-        <v>-6.2672334140308275E-3</v>
+        <v>-0.0062707308369635284</v>
       </c>
       <c r="G3">
-        <v>-5.7452281984461551E-3</v>
+        <v>-0.0057474554300854311</v>
       </c>
       <c r="H3">
-        <v>3.2557029444143723E-4</v>
+        <v>0.00032517410045471845</v>
       </c>
       <c r="I3">
-        <v>7.1360480317597588E-4</v>
+        <v>0.00071500481140454944</v>
       </c>
       <c r="J3">
-        <v>5.8494260028782857E-3</v>
+        <v>0.0058558248444295358</v>
       </c>
       <c r="K3">
-        <v>-1.1665190321906438E-4</v>
+        <v>-0.0001270725377418222</v>
       </c>
       <c r="L3">
-        <v>5.0380571806615815E-4</v>
+        <v>0.0004950437296780269</v>
       </c>
       <c r="M3">
-        <v>2.9900318018807794E-4</v>
+        <v>0.00030027989377830883</v>
       </c>
       <c r="N3">
-        <v>3.7284900316576081E-4</v>
+        <v>0.00036404792273661557</v>
       </c>
       <c r="O3">
-        <v>6.0577660682216081E-4</v>
+        <v>0.00059641867524886857</v>
       </c>
       <c r="P3">
-        <v>-5.0972634126932037E-4</v>
+        <v>-0.00050893814953903438</v>
       </c>
       <c r="Q3">
-        <v>8.158134524309385E-4</v>
+        <v>0.00081198148442042373</v>
       </c>
       <c r="R3">
-        <v>1.4442747913062243E-3</v>
+        <v>0.0014396605690730341</v>
       </c>
       <c r="S3">
-        <v>1.407541414986945E-3</v>
+        <v>0.0014029889963918553</v>
       </c>
       <c r="T3">
-        <v>1.263294423463554E-3</v>
+        <v>0.0012590988922415863</v>
       </c>
       <c r="U3">
-        <v>1.5363959200552016E-3</v>
+        <v>0.0015308726288786462</v>
       </c>
       <c r="V3">
-        <v>1.3115773147099365E-3</v>
+        <v>0.0013075323164292198</v>
       </c>
       <c r="W3">
-        <v>-6.0050833899493589E-5</v>
+        <v>-5.9570187536984315e-05</v>
       </c>
       <c r="X3">
-        <v>2.0734956898646462E-4</v>
+        <v>0.00020227702582209517</v>
       </c>
       <c r="Y3">
-        <v>-0.26068014295401309</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.26066544532658087</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>29</v>
       </c>
       <c r="B4">
-        <v>2.9485875606328096E-3</v>
+        <v>0.0029560215184222631</v>
       </c>
       <c r="C4">
-        <v>-2.5317882363579935E-6</v>
+        <v>-2.5423473035224351e-06</v>
       </c>
       <c r="D4">
-        <v>-6.7423446384728058E-5</v>
+        <v>-6.7425200104710768e-05</v>
       </c>
       <c r="E4">
-        <v>5.4624661410713258E-7</v>
+        <v>5.4627359851964657e-07</v>
       </c>
       <c r="F4">
-        <v>5.3968788625929638E-5</v>
+        <v>5.3999886795836466e-05</v>
       </c>
       <c r="G4">
-        <v>4.9420569782659637E-5</v>
+        <v>4.9440454222567315e-05</v>
       </c>
       <c r="H4">
-        <v>-2.2163410276575095E-6</v>
+        <v>-2.2122227746422106e-06</v>
       </c>
       <c r="I4">
-        <v>-5.4288528804621259E-6</v>
+        <v>-5.4412186946213054e-06</v>
       </c>
       <c r="J4">
-        <v>-5.3024057438836605E-5</v>
+        <v>-5.3079155975802299e-05</v>
       </c>
       <c r="K4">
-        <v>1.1169784064416068E-6</v>
+        <v>1.2198559147149338e-06</v>
       </c>
       <c r="L4">
-        <v>-4.1874440949755346E-6</v>
+        <v>-4.120304281758462e-06</v>
       </c>
       <c r="M4">
-        <v>-2.2553300544623354E-6</v>
+        <v>-2.2597883457814501e-06</v>
       </c>
       <c r="N4">
-        <v>-2.5780367690972491E-6</v>
+        <v>-2.4941278154539336e-06</v>
       </c>
       <c r="O4">
-        <v>-3.8704749348174414E-6</v>
+        <v>-3.7812538931532292e-06</v>
       </c>
       <c r="P4">
-        <v>4.2309286353634087E-6</v>
+        <v>4.2216296363709266e-06</v>
       </c>
       <c r="Q4">
-        <v>-6.0054923637039605E-6</v>
+        <v>-5.976228130639364e-06</v>
       </c>
       <c r="R4">
-        <v>-1.077712555550578E-5</v>
+        <v>-1.0741315716370024e-05</v>
       </c>
       <c r="S4">
-        <v>-1.0685400757698298E-5</v>
+        <v>-1.0651247621253577e-05</v>
       </c>
       <c r="T4">
-        <v>-9.5162780795942856E-6</v>
+        <v>-9.4827576090265138e-06</v>
       </c>
       <c r="U4">
-        <v>-1.1759368423350442E-5</v>
+        <v>-1.171644617455113e-05</v>
       </c>
       <c r="V4">
-        <v>-9.5534058688779026E-6</v>
+        <v>-9.5214589330956743e-06</v>
       </c>
       <c r="W4">
-        <v>3.8245581064729384E-7</v>
+        <v>3.7841672517012069e-07</v>
       </c>
       <c r="X4">
-        <v>-1.0624288981172418E-6</v>
+        <v>-1.0180980463591e-06</v>
       </c>
       <c r="Y4">
-        <v>2.0813413306304922E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+        <v>0.0020812749983526221</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>30</v>
       </c>
       <c r="B5">
-        <v>1.567226700422804</v>
+        <v>1.5667851489846301</v>
       </c>
       <c r="C5">
-        <v>1.2284936470375972E-4</v>
+        <v>0.0001277736417461918</v>
       </c>
       <c r="D5">
-        <v>-6.2672334140308275E-3</v>
+        <v>-0.0062707308369635284</v>
       </c>
       <c r="E5">
-        <v>5.3968788625929638E-5</v>
+        <v>5.3999886795836466e-05</v>
       </c>
       <c r="F5">
-        <v>1.4396716369991434E-2</v>
+        <v>0.014400718363733963</v>
       </c>
       <c r="G5">
-        <v>8.6969395515247797E-3</v>
+        <v>0.0087058677531630189</v>
       </c>
       <c r="H5">
-        <v>8.9646471711207071E-5</v>
+        <v>8.5251831938672196e-05</v>
       </c>
       <c r="I5">
-        <v>-1.265523761466718E-4</v>
+        <v>-0.00012556047823492457</v>
       </c>
       <c r="J5">
-        <v>-1.1855212437201654E-2</v>
+        <v>-0.011863870313114616</v>
       </c>
       <c r="K5">
-        <v>1.7891674068608154E-3</v>
+        <v>0.0018117245972805408</v>
       </c>
       <c r="L5">
-        <v>-2.6378356889011217E-4</v>
+        <v>-0.00026201317336340541</v>
       </c>
       <c r="M5">
-        <v>1.8874269157246291E-4</v>
+        <v>0.00019404469137590356</v>
       </c>
       <c r="N5">
-        <v>6.368582083605169E-4</v>
+        <v>0.00065939044429250485</v>
       </c>
       <c r="O5">
-        <v>1.3453521981434576E-3</v>
+        <v>0.0013689478449855699</v>
       </c>
       <c r="P5">
-        <v>9.1680635442258074E-5</v>
+        <v>9.2774196442574342e-05</v>
       </c>
       <c r="Q5">
-        <v>-2.7265044014394141E-4</v>
+        <v>-0.00027304818440414963</v>
       </c>
       <c r="R5">
-        <v>-3.8716513852304207E-4</v>
+        <v>-0.00038996917383920388</v>
       </c>
       <c r="S5">
-        <v>-6.1038663719111853E-4</v>
+        <v>-0.00060754036464548715</v>
       </c>
       <c r="T5">
-        <v>-5.5785807744340721E-4</v>
+        <v>-0.00055609464639379269</v>
       </c>
       <c r="U5">
-        <v>-4.5367507191610562E-4</v>
+        <v>-0.00045459139896747783</v>
       </c>
       <c r="V5">
-        <v>-3.0297118443714348E-4</v>
+        <v>-0.00030461590084548788</v>
       </c>
       <c r="W5">
-        <v>-6.8673621271978305E-5</v>
+        <v>-6.8706949786379728e-05</v>
       </c>
       <c r="X5">
-        <v>5.8315810217423464E-4</v>
+        <v>0.0005850145535446355</v>
       </c>
       <c r="Y5">
-        <v>0.18106981320598359</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+        <v>0.18114126091484417</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>31</v>
       </c>
       <c r="B6">
-        <v>1.3400300852774567</v>
+        <v>1.3397062676705158</v>
       </c>
       <c r="C6">
-        <v>6.1169123473884548E-4</v>
+        <v>0.00061222217084306424</v>
       </c>
       <c r="D6">
-        <v>-5.7452281984461551E-3</v>
+        <v>-0.0057474554300854311</v>
       </c>
       <c r="E6">
-        <v>4.9420569782659637E-5</v>
+        <v>4.9440454222567315e-05</v>
       </c>
       <c r="F6">
-        <v>8.6969395515247797E-3</v>
+        <v>0.0087058677531630189</v>
       </c>
       <c r="G6">
-        <v>1.6883113258583576E-2</v>
+        <v>0.016874281000484111</v>
       </c>
       <c r="H6">
-        <v>2.2543583567750936E-4</v>
+        <v>0.00022474827461014049</v>
       </c>
       <c r="I6">
-        <v>4.3622779977941454E-4</v>
+        <v>0.00043470345912564813</v>
       </c>
       <c r="J6">
-        <v>-1.0471894121715189E-2</v>
+        <v>-0.010483448316872451</v>
       </c>
       <c r="K6">
-        <v>1.9013702091490343E-4</v>
+        <v>0.0002275304440461012</v>
       </c>
       <c r="L6">
-        <v>-1.9010366840431503E-4</v>
+        <v>-0.00019440379376878259</v>
       </c>
       <c r="M6">
-        <v>2.227411949269377E-4</v>
+        <v>0.00022962360282062369</v>
       </c>
       <c r="N6">
-        <v>-8.4553526749065605E-5</v>
+        <v>-5.4735860036164014e-05</v>
       </c>
       <c r="O6">
-        <v>2.6676730403549578E-4</v>
+        <v>0.00029759313440550286</v>
       </c>
       <c r="P6">
-        <v>1.7724556950660109E-4</v>
+        <v>0.00017348270766022467</v>
       </c>
       <c r="Q6">
-        <v>-2.6326142874530389E-4</v>
+        <v>-0.00026188707195839989</v>
       </c>
       <c r="R6">
-        <v>-2.3376743133066147E-4</v>
+        <v>-0.00023320823863586665</v>
       </c>
       <c r="S6">
-        <v>1.4054516612603844E-4</v>
+        <v>0.00013983279192682392</v>
       </c>
       <c r="T6">
-        <v>-5.5210331818639907E-4</v>
+        <v>-0.00054905308772949107</v>
       </c>
       <c r="U6">
-        <v>-3.9680319285552434E-4</v>
+        <v>-0.00039776619927753276</v>
       </c>
       <c r="V6">
-        <v>-2.9916415842864974E-7</v>
+        <v>-1.8100126882875794e-06</v>
       </c>
       <c r="W6">
-        <v>-7.7964990227346112E-5</v>
+        <v>-7.8138802062170318e-05</v>
       </c>
       <c r="X6">
-        <v>8.561282207184967E-4</v>
+        <v>0.00085755801382725316</v>
       </c>
       <c r="Y6">
-        <v>0.16650170403807674</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+        <v>0.16653561316098453</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>32</v>
       </c>
       <c r="B7">
-        <v>4.960623478266897E-2</v>
+        <v>0.04932022556198392</v>
       </c>
       <c r="C7">
-        <v>3.1967730147480588E-4</v>
+        <v>0.00032096859283766734</v>
       </c>
       <c r="D7">
-        <v>3.2557029444143723E-4</v>
+        <v>0.00032517410045471845</v>
       </c>
       <c r="E7">
-        <v>-2.2163410276575095E-6</v>
+        <v>-2.2122227746422106e-06</v>
       </c>
       <c r="F7">
-        <v>8.9646471711207071E-5</v>
+        <v>8.5251831938672196e-05</v>
       </c>
       <c r="G7">
-        <v>2.2543583567750936E-4</v>
+        <v>0.00022474827461014049</v>
       </c>
       <c r="H7">
-        <v>5.0805537555463787E-3</v>
+        <v>0.0050822306469432491</v>
       </c>
       <c r="I7">
-        <v>2.8965022173864036E-3</v>
+        <v>0.0029001834946196206</v>
       </c>
       <c r="J7">
-        <v>-2.2404361070656404E-4</v>
+        <v>-0.00021625973079862767</v>
       </c>
       <c r="K7">
-        <v>1.9018961101571421E-4</v>
+        <v>0.00015030567370792099</v>
       </c>
       <c r="L7">
-        <v>-7.6114521662576156E-5</v>
+        <v>-8.3323708424765412e-05</v>
       </c>
       <c r="M7">
-        <v>2.5633121703558395E-4</v>
+        <v>0.00025392819018553328</v>
       </c>
       <c r="N7">
-        <v>2.0213369778930752E-4</v>
+        <v>0.00017209167984878033</v>
       </c>
       <c r="O7">
-        <v>1.3913193622218099E-3</v>
+        <v>0.0013611989933790042</v>
       </c>
       <c r="P7">
-        <v>-4.0115391401050445E-4</v>
+        <v>-0.00039373481429071512</v>
       </c>
       <c r="Q7">
-        <v>7.1624881933539408E-4</v>
+        <v>0.00071408223312623663</v>
       </c>
       <c r="R7">
-        <v>3.8410221112102072E-4</v>
+        <v>0.00038317693240104336</v>
       </c>
       <c r="S7">
-        <v>6.2129832502369193E-4</v>
+        <v>0.00062014216709299543</v>
       </c>
       <c r="T7">
-        <v>5.1637967594370593E-4</v>
+        <v>0.00051451398447009342</v>
       </c>
       <c r="U7">
-        <v>3.9994738844769274E-4</v>
+        <v>0.00039584482630213448</v>
       </c>
       <c r="V7">
-        <v>7.2283373151140634E-4</v>
+        <v>0.00071959659101857032</v>
       </c>
       <c r="W7">
-        <v>-5.7591344688285846E-5</v>
+        <v>-5.7578600631331262e-05</v>
       </c>
       <c r="X7">
-        <v>3.7086542311981865E-4</v>
+        <v>0.00036923980199012052</v>
       </c>
       <c r="Y7">
-        <v>-1.4602595817448792E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.01456235400284589</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>33</v>
       </c>
       <c r="B8">
-        <v>2.1854364301091622E-2</v>
+        <v>0.02277505134966288</v>
       </c>
       <c r="C8">
-        <v>9.202019046648082E-5</v>
+        <v>8.9455321468731873e-05</v>
       </c>
       <c r="D8">
-        <v>7.1360480317597588E-4</v>
+        <v>0.00071500481140454944</v>
       </c>
       <c r="E8">
-        <v>-5.4288528804621259E-6</v>
+        <v>-5.4412186946213054e-06</v>
       </c>
       <c r="F8">
-        <v>-1.265523761466718E-4</v>
+        <v>-0.00012556047823492457</v>
       </c>
       <c r="G8">
-        <v>4.3622779977941454E-4</v>
+        <v>0.00043470345912564813</v>
       </c>
       <c r="H8">
-        <v>2.8965022173864036E-3</v>
+        <v>0.0029001834946196206</v>
       </c>
       <c r="I8">
-        <v>4.2939896559333387E-3</v>
+        <v>0.0042936389817905757</v>
       </c>
       <c r="J8">
-        <v>-2.2725836142650931E-4</v>
+        <v>-0.00022763287911035761</v>
       </c>
       <c r="K8">
-        <v>8.6165921000539098E-6</v>
+        <v>5.2564753737266348e-06</v>
       </c>
       <c r="L8">
-        <v>8.2616196208383074E-5</v>
+        <v>8.4705354735835131e-05</v>
       </c>
       <c r="M8">
-        <v>5.8723759636325663E-4</v>
+        <v>0.0005771056250456479</v>
       </c>
       <c r="N8">
-        <v>9.1916946422159515E-4</v>
+        <v>0.00091220149101568998</v>
       </c>
       <c r="O8">
-        <v>2.1145539484863007E-3</v>
+        <v>0.0021083581319738601</v>
       </c>
       <c r="P8">
-        <v>1.4804630244966144E-4</v>
+        <v>0.00014518658918413318</v>
       </c>
       <c r="Q8">
-        <v>9.2164970538139682E-4</v>
+        <v>0.00092075184664219237</v>
       </c>
       <c r="R8">
-        <v>9.3795861874180087E-4</v>
+        <v>0.00093942674631004365</v>
       </c>
       <c r="S8">
-        <v>1.1602133432301888E-3</v>
+        <v>0.0011585336135670626</v>
       </c>
       <c r="T8">
-        <v>7.4961405640390174E-4</v>
+        <v>0.00074957652391749777</v>
       </c>
       <c r="U8">
-        <v>1.1489110652464554E-3</v>
+        <v>0.0011492510222453026</v>
       </c>
       <c r="V8">
-        <v>8.6136483622944961E-4</v>
+        <v>0.00086122911721351724</v>
       </c>
       <c r="W8">
-        <v>2.6233599425287853E-5</v>
+        <v>2.632652791225256e-05</v>
       </c>
       <c r="X8">
-        <v>6.9311461262675693E-5</v>
+        <v>6.8658656077859011e-05</v>
       </c>
       <c r="Y8">
-        <v>-2.8459061067412694E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.028493076642081804</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>34</v>
       </c>
       <c r="B9">
-        <v>-1.033770163177413</v>
+        <v>-1.0331425165057135</v>
       </c>
       <c r="C9">
-        <v>-7.331760072023586E-5</v>
+        <v>-8.0041004401561785e-05</v>
       </c>
       <c r="D9">
-        <v>5.8494260028782857E-3</v>
+        <v>0.0058558248444295358</v>
       </c>
       <c r="E9">
-        <v>-5.3024057438836605E-5</v>
+        <v>-5.3079155975802299e-05</v>
       </c>
       <c r="F9">
-        <v>-1.1855212437201654E-2</v>
+        <v>-0.011863870313114616</v>
       </c>
       <c r="G9">
-        <v>-1.0471894121715189E-2</v>
+        <v>-0.010483448316872451</v>
       </c>
       <c r="H9">
-        <v>-2.2404361070656404E-4</v>
+        <v>-0.00021625973079862767</v>
       </c>
       <c r="I9">
-        <v>-2.2725836142650931E-4</v>
+        <v>-0.00022763287911035761</v>
       </c>
       <c r="J9">
-        <v>1.6580795905178934E-2</v>
+        <v>0.016591403236181211</v>
       </c>
       <c r="K9">
-        <v>-2.3754534627535113E-3</v>
+        <v>-0.0024043049378408132</v>
       </c>
       <c r="L9">
-        <v>8.3148213434212914E-5</v>
+        <v>8.9268331008959811e-05</v>
       </c>
       <c r="M9">
-        <v>-3.6269492924667548E-4</v>
+        <v>-0.00037023836414734005</v>
       </c>
       <c r="N9">
-        <v>-9.4747241147031744E-4</v>
+        <v>-0.00097326878880300144</v>
       </c>
       <c r="O9">
-        <v>-2.0133480897541241E-3</v>
+        <v>-0.0020410059809901557</v>
       </c>
       <c r="P9">
-        <v>-8.1519956650927261E-5</v>
+        <v>-8.2692152567627464e-05</v>
       </c>
       <c r="Q9">
-        <v>-3.2502564908160753E-4</v>
+        <v>-0.00032418835931692647</v>
       </c>
       <c r="R9">
-        <v>-2.1588199243713357E-4</v>
+        <v>-0.00021179480611657059</v>
       </c>
       <c r="S9">
-        <v>1.0665282318286394E-4</v>
+        <v>0.00010459524885630001</v>
       </c>
       <c r="T9">
-        <v>5.8516892856338987E-5</v>
+        <v>5.7058179169587608e-05</v>
       </c>
       <c r="U9">
-        <v>-1.1998153827468688E-4</v>
+        <v>-0.00011723372914448568</v>
       </c>
       <c r="V9">
-        <v>-5.4105670192655664E-4</v>
+        <v>-0.00053804589188520026</v>
       </c>
       <c r="W9">
-        <v>1.2991010158539505E-4</v>
+        <v>0.00012999513591543249</v>
       </c>
       <c r="X9">
-        <v>-7.638186510975295E-4</v>
+        <v>-0.00076636220934089838</v>
       </c>
       <c r="Y9">
-        <v>-0.15992406178289431</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+        <v>-0.16008034423523143</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>35</v>
       </c>
       <c r="B10">
-        <v>0.13804408599137261</v>
+        <v>0.14048682995042869</v>
       </c>
       <c r="C10">
-        <v>1.1337716315218516E-4</v>
+        <v>0.00015288528878599667</v>
       </c>
       <c r="D10">
-        <v>-1.1665190321906438E-4</v>
+        <v>-0.0001270725377418222</v>
       </c>
       <c r="E10">
-        <v>1.1169784064416068E-6</v>
+        <v>1.2198559147149338e-06</v>
       </c>
       <c r="F10">
-        <v>1.7891674068608154E-3</v>
+        <v>0.0018117245972805408</v>
       </c>
       <c r="G10">
-        <v>1.9013702091490343E-4</v>
+        <v>0.0002275304440461012</v>
       </c>
       <c r="H10">
-        <v>1.9018961101571421E-4</v>
+        <v>0.00015030567370792099</v>
       </c>
       <c r="I10">
-        <v>8.6165921000539098E-6</v>
+        <v>5.2564753737266348e-06</v>
       </c>
       <c r="J10">
-        <v>-2.3754534627535113E-3</v>
+        <v>-0.0024043049378408132</v>
       </c>
       <c r="K10">
-        <v>1.0047054685614894E-2</v>
+        <v>0.010095801612414487</v>
       </c>
       <c r="L10">
-        <v>2.2925265625620313E-4</v>
+        <v>0.00021190392282986054</v>
       </c>
       <c r="M10">
-        <v>3.6183057026887584E-3</v>
+        <v>0.0035695353963996466</v>
       </c>
       <c r="N10">
-        <v>8.6820930050419548E-3</v>
+        <v>0.0087214101122961244</v>
       </c>
       <c r="O10">
-        <v>8.6946667889408625E-3</v>
+        <v>0.0087353623480888338</v>
       </c>
       <c r="P10">
-        <v>-1.4810764956219033E-3</v>
+        <v>-0.0015008949733958223</v>
       </c>
       <c r="Q10">
-        <v>-1.5793164134294754E-4</v>
+        <v>-0.00015188262390142433</v>
       </c>
       <c r="R10">
-        <v>-6.6416689999699782E-4</v>
+        <v>-0.00068479383296105902</v>
       </c>
       <c r="S10">
-        <v>-9.2843268530518248E-4</v>
+        <v>-0.00090945759639161775</v>
       </c>
       <c r="T10">
-        <v>-4.9762042177596381E-4</v>
+        <v>-0.00049345002928025822</v>
       </c>
       <c r="U10">
-        <v>-2.9336562375335655E-4</v>
+        <v>-0.00030308872570340272</v>
       </c>
       <c r="V10">
-        <v>-3.6664292016380662E-4</v>
+        <v>-0.00037340911592429653</v>
       </c>
       <c r="W10">
-        <v>4.1844362811155984E-5</v>
+        <v>4.3661365617540977e-05</v>
       </c>
       <c r="X10">
-        <v>-1.8034555545380811E-4</v>
+        <v>-0.00021331245749532483</v>
       </c>
       <c r="Y10">
-        <v>-6.0137935834939371E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.0058203708595809534</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>36</v>
       </c>
       <c r="B11">
-        <v>0.16187379552959719</v>
+        <v>0.15712789513203268</v>
       </c>
       <c r="C11">
-        <v>-1.9397742251601774E-4</v>
+        <v>-0.00018990157009662466</v>
       </c>
       <c r="D11">
-        <v>5.0380571806615815E-4</v>
+        <v>0.0004950437296780269</v>
       </c>
       <c r="E11">
-        <v>-4.1874440949755346E-6</v>
+        <v>-4.120304281758462e-06</v>
       </c>
       <c r="F11">
-        <v>-2.6378356889011217E-4</v>
+        <v>-0.00026201317336340541</v>
       </c>
       <c r="G11">
-        <v>-1.9010366840431503E-4</v>
+        <v>-0.00019440379376878259</v>
       </c>
       <c r="H11">
-        <v>-7.6114521662576156E-5</v>
+        <v>-8.3323708424765412e-05</v>
       </c>
       <c r="I11">
-        <v>8.2616196208383074E-5</v>
+        <v>8.4705354735835131e-05</v>
       </c>
       <c r="J11">
-        <v>8.3148213434212914E-5</v>
+        <v>8.9268331008959811e-05</v>
       </c>
       <c r="K11">
-        <v>2.2925265625620313E-4</v>
+        <v>0.00021190392282986054</v>
       </c>
       <c r="L11">
-        <v>3.7257057413935513E-3</v>
+        <v>0.003737401182335618</v>
       </c>
       <c r="M11">
-        <v>1.581350863737784E-3</v>
+        <v>0.0015714264301785773</v>
       </c>
       <c r="N11">
-        <v>1.6904372280317792E-3</v>
+        <v>0.0016756322568311382</v>
       </c>
       <c r="O11">
-        <v>1.6528887520674488E-3</v>
+        <v>0.0016369413880199689</v>
       </c>
       <c r="P11">
-        <v>5.1824689684483254E-4</v>
+        <v>0.00052524419428915834</v>
       </c>
       <c r="Q11">
-        <v>1.8061883562657446E-4</v>
+        <v>0.00018494354611160832</v>
       </c>
       <c r="R11">
-        <v>2.4575039570695059E-4</v>
+        <v>0.0002470574468967097</v>
       </c>
       <c r="S11">
-        <v>2.8181945827751109E-4</v>
+        <v>0.00028828661919713005</v>
       </c>
       <c r="T11">
-        <v>9.4085157568694899E-5</v>
+        <v>9.4756114982073869e-05</v>
       </c>
       <c r="U11">
-        <v>6.6737962189110682E-4</v>
+        <v>0.00067910953308937126</v>
       </c>
       <c r="V11">
-        <v>2.2238624859621223E-4</v>
+        <v>0.00022599738256413486</v>
       </c>
       <c r="W11">
-        <v>-2.6400060074644198E-5</v>
+        <v>-2.6903043401677539e-05</v>
       </c>
       <c r="X11">
-        <v>4.0281613969062177E-4</v>
+        <v>0.00040639259862843783</v>
       </c>
       <c r="Y11">
-        <v>-1.6787752027816405E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.016489606447997539</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>37</v>
       </c>
       <c r="B12">
-        <v>3.1297148679227234E-2</v>
+        <v>0.038709605659895903</v>
       </c>
       <c r="C12">
-        <v>-5.7890159434744083E-5</v>
+        <v>-4.819900772676445e-05</v>
       </c>
       <c r="D12">
-        <v>2.9900318018807794E-4</v>
+        <v>0.00030027989377830883</v>
       </c>
       <c r="E12">
-        <v>-2.2553300544623354E-6</v>
+        <v>-2.2597883457814501e-06</v>
       </c>
       <c r="F12">
-        <v>1.8874269157246291E-4</v>
+        <v>0.00019404469137590356</v>
       </c>
       <c r="G12">
-        <v>2.227411949269377E-4</v>
+        <v>0.00022962360282062369</v>
       </c>
       <c r="H12">
-        <v>2.5633121703558395E-4</v>
+        <v>0.00025392819018553328</v>
       </c>
       <c r="I12">
-        <v>5.8723759636325663E-4</v>
+        <v>0.0005771056250456479</v>
       </c>
       <c r="J12">
-        <v>-3.6269492924667548E-4</v>
+        <v>-0.00037023836414734005</v>
       </c>
       <c r="K12">
-        <v>3.6183057026887584E-3</v>
+        <v>0.0035695353963996466</v>
       </c>
       <c r="L12">
-        <v>1.581350863737784E-3</v>
+        <v>0.0015714264301785773</v>
       </c>
       <c r="M12">
-        <v>5.7124422353091514E-3</v>
+        <v>0.0056350575963801837</v>
       </c>
       <c r="N12">
-        <v>5.1158356225267333E-3</v>
+        <v>0.0050558682247423443</v>
       </c>
       <c r="O12">
-        <v>5.2510710657778722E-3</v>
+        <v>0.0051888596269838265</v>
       </c>
       <c r="P12">
-        <v>5.0150019614737112E-4</v>
+        <v>0.00048182189550011927</v>
       </c>
       <c r="Q12">
-        <v>-3.175935004988209E-4</v>
+        <v>-0.00031309765868033339</v>
       </c>
       <c r="R12">
-        <v>-4.1962949842579231E-4</v>
+        <v>-0.00041469700503659387</v>
       </c>
       <c r="S12">
-        <v>-3.2529913164938159E-4</v>
+        <v>-0.00031677030948621321</v>
       </c>
       <c r="T12">
-        <v>-2.7769854888019547E-4</v>
+        <v>-0.00027258269664574841</v>
       </c>
       <c r="U12">
-        <v>-2.0693714069744689E-4</v>
+        <v>-0.00021043593007097025</v>
       </c>
       <c r="V12">
-        <v>-3.0323731948758768E-4</v>
+        <v>-0.00029849957080637746</v>
       </c>
       <c r="W12">
-        <v>2.2241903466405089E-5</v>
+        <v>2.1888226458871693e-05</v>
       </c>
       <c r="X12">
-        <v>1.6971353593052494E-4</v>
+        <v>0.00015509365242734677</v>
       </c>
       <c r="Y12">
-        <v>-1.5546372834418024E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.015531617014040294</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>38</v>
       </c>
       <c r="B13">
-        <v>-1.1056684234813732E-2</v>
+        <v>-0.0080823966161143838</v>
       </c>
       <c r="C13">
-        <v>-4.4495405509703144E-4</v>
+        <v>-0.00041367719293427857</v>
       </c>
       <c r="D13">
-        <v>3.7284900316576081E-4</v>
+        <v>0.00036404792273661557</v>
       </c>
       <c r="E13">
-        <v>-2.5780367690972491E-6</v>
+        <v>-2.4941278154539336e-06</v>
       </c>
       <c r="F13">
-        <v>6.368582083605169E-4</v>
+        <v>0.00065939044429250485</v>
       </c>
       <c r="G13">
-        <v>-8.4553526749065605E-5</v>
+        <v>-5.4735860036164014e-05</v>
       </c>
       <c r="H13">
-        <v>2.0213369778930752E-4</v>
+        <v>0.00017209167984878033</v>
       </c>
       <c r="I13">
-        <v>9.1916946422159515E-4</v>
+        <v>0.00091220149101568998</v>
       </c>
       <c r="J13">
-        <v>-9.4747241147031744E-4</v>
+        <v>-0.00097326878880300144</v>
       </c>
       <c r="K13">
-        <v>8.6820930050419548E-3</v>
+        <v>0.0087214101122961244</v>
       </c>
       <c r="L13">
-        <v>1.6904372280317792E-3</v>
+        <v>0.0016756322568311382</v>
       </c>
       <c r="M13">
-        <v>5.1158356225267333E-3</v>
+        <v>0.0050558682247423443</v>
       </c>
       <c r="N13">
-        <v>1.3646372490531199E-2</v>
+        <v>0.013667653632937343</v>
       </c>
       <c r="O13">
-        <v>1.0588892432423249E-2</v>
+        <v>0.010610839250388091</v>
       </c>
       <c r="P13">
-        <v>5.9286625073840058E-4</v>
+        <v>0.00056923812111167073</v>
       </c>
       <c r="Q13">
-        <v>-4.6912881963381402E-4</v>
+        <v>-0.00046100272930950283</v>
       </c>
       <c r="R13">
-        <v>-7.1667185048940579E-4</v>
+        <v>-0.0007300117378038918</v>
       </c>
       <c r="S13">
-        <v>-1.4945102424165509E-3</v>
+        <v>-0.0014761581629677287</v>
       </c>
       <c r="T13">
-        <v>-5.7233937837377919E-4</v>
+        <v>-0.00056630085552690328</v>
       </c>
       <c r="U13">
-        <v>-6.0557999574334734E-4</v>
+        <v>-0.00060981189701043124</v>
       </c>
       <c r="V13">
-        <v>-4.9110413306726599E-4</v>
+        <v>-0.00049296186557148546</v>
       </c>
       <c r="W13">
-        <v>6.5200146862335402E-5</v>
+        <v>6.6429765941664488e-05</v>
       </c>
       <c r="X13">
-        <v>-7.8600624646599053E-5</v>
+        <v>-0.0001061064384464544</v>
       </c>
       <c r="Y13">
-        <v>-2.4154563808679808E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.023964545151206884</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>39</v>
       </c>
       <c r="B14">
-        <v>0.26833953350676221</v>
+        <v>0.27183084648739686</v>
       </c>
       <c r="C14">
-        <v>-7.4780033940842635E-4</v>
+        <v>-0.0007160802721547934</v>
       </c>
       <c r="D14">
-        <v>6.0577660682216081E-4</v>
+        <v>0.00059641867524886857</v>
       </c>
       <c r="E14">
-        <v>-3.8704749348174414E-6</v>
+        <v>-3.7812538931532292e-06</v>
       </c>
       <c r="F14">
-        <v>1.3453521981434576E-3</v>
+        <v>0.0013689478449855699</v>
       </c>
       <c r="G14">
-        <v>2.6676730403549578E-4</v>
+        <v>0.00029759313440550286</v>
       </c>
       <c r="H14">
-        <v>1.3913193622218099E-3</v>
+        <v>0.0013611989933790042</v>
       </c>
       <c r="I14">
-        <v>2.1145539484863007E-3</v>
+        <v>0.0021083581319738601</v>
       </c>
       <c r="J14">
-        <v>-2.0133480897541241E-3</v>
+        <v>-0.0020410059809901557</v>
       </c>
       <c r="K14">
-        <v>8.6946667889408625E-3</v>
+        <v>0.0087353623480888338</v>
       </c>
       <c r="L14">
-        <v>1.6528887520674488E-3</v>
+        <v>0.0016369413880199689</v>
       </c>
       <c r="M14">
-        <v>5.2510710657778722E-3</v>
+        <v>0.0051888596269838265</v>
       </c>
       <c r="N14">
-        <v>1.0588892432423249E-2</v>
+        <v>0.010610839250388091</v>
       </c>
       <c r="O14">
-        <v>1.3410811607106271E-2</v>
+        <v>0.013434061205413871</v>
       </c>
       <c r="P14">
-        <v>7.1294352084205759E-4</v>
+        <v>0.00068775173991071983</v>
       </c>
       <c r="Q14">
-        <v>3.2185812934484859E-4</v>
+        <v>0.00032879265044232463</v>
       </c>
       <c r="R14">
-        <v>-2.7619838523818517E-4</v>
+        <v>-0.00029040401314599403</v>
       </c>
       <c r="S14">
-        <v>-5.0768375328096396E-4</v>
+        <v>-0.00049015985723418966</v>
       </c>
       <c r="T14">
-        <v>-1.5741621053791399E-5</v>
+        <v>-1.0636820977943245e-05</v>
       </c>
       <c r="U14">
-        <v>2.1926810676775339E-4</v>
+        <v>0.00021376059820605101</v>
       </c>
       <c r="V14">
-        <v>1.4195395439349588E-4</v>
+        <v>0.00013910559227940655</v>
       </c>
       <c r="W14">
-        <v>5.4530800481503681E-5</v>
+        <v>5.5824246682463627e-05</v>
       </c>
       <c r="X14">
-        <v>-5.4496344426982826E-5</v>
+        <v>-8.3194575211196359e-05</v>
       </c>
       <c r="Y14">
-        <v>-3.4916024665207573E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.034712531080204834</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>40</v>
       </c>
       <c r="B15">
-        <v>0.46805363414889128</v>
+        <v>0.46959115152366621</v>
       </c>
       <c r="C15">
-        <v>-1.553361962015571E-3</v>
+        <v>-0.0015633069937882097</v>
       </c>
       <c r="D15">
-        <v>-5.0972634126932037E-4</v>
+        <v>-0.00050893814953903438</v>
       </c>
       <c r="E15">
-        <v>4.2309286353634087E-6</v>
+        <v>4.2216296363709266e-06</v>
       </c>
       <c r="F15">
-        <v>9.1680635442258074E-5</v>
+        <v>9.2774196442574342e-05</v>
       </c>
       <c r="G15">
-        <v>1.7724556950660109E-4</v>
+        <v>0.00017348270766022467</v>
       </c>
       <c r="H15">
-        <v>-4.0115391401050445E-4</v>
+        <v>-0.00039373481429071512</v>
       </c>
       <c r="I15">
-        <v>1.4804630244966144E-4</v>
+        <v>0.00014518658918413318</v>
       </c>
       <c r="J15">
-        <v>-8.1519956650927261E-5</v>
+        <v>-8.2692152567627464e-05</v>
       </c>
       <c r="K15">
-        <v>-1.4810764956219033E-3</v>
+        <v>-0.0015008949733958223</v>
       </c>
       <c r="L15">
-        <v>5.1824689684483254E-4</v>
+        <v>0.00052524419428915834</v>
       </c>
       <c r="M15">
-        <v>5.0150019614737112E-4</v>
+        <v>0.00048182189550011927</v>
       </c>
       <c r="N15">
-        <v>5.9286625073840058E-4</v>
+        <v>0.00056923812111167073</v>
       </c>
       <c r="O15">
-        <v>7.1294352084205759E-4</v>
+        <v>0.00068775173991071983</v>
       </c>
       <c r="P15">
-        <v>6.168178004862801E-3</v>
+        <v>0.0061691004654893418</v>
       </c>
       <c r="Q15">
-        <v>-7.0848439702978503E-4</v>
+        <v>-0.00070595507484198577</v>
       </c>
       <c r="R15">
-        <v>-2.325408938903858E-4</v>
+        <v>-0.00022447869306467961</v>
       </c>
       <c r="S15">
-        <v>-4.5953681704153369E-4</v>
+        <v>-0.00046010193651794168</v>
       </c>
       <c r="T15">
-        <v>-4.150214162990573E-4</v>
+        <v>-0.00041266291223726495</v>
       </c>
       <c r="U15">
-        <v>-1.5085902177469494E-4</v>
+        <v>-0.00014433221484819105</v>
       </c>
       <c r="V15">
-        <v>-5.1684723191767741E-4</v>
+        <v>-0.00051246829038730413</v>
       </c>
       <c r="W15">
-        <v>5.0843511466612946E-5</v>
+        <v>5.0350304434154159e-05</v>
       </c>
       <c r="X15">
-        <v>1.3112722604240071E-4</v>
+        <v>0.00013761287005871416</v>
       </c>
       <c r="Y15">
-        <v>1.4871309672353936E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+        <v>0.014888060808974674</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>41</v>
       </c>
       <c r="B16">
-        <v>-2.5917432865169447E-2</v>
+        <v>-0.026114800589334887</v>
       </c>
       <c r="C16">
-        <v>3.7471880904776087E-4</v>
+        <v>0.0003755287546525751</v>
       </c>
       <c r="D16">
-        <v>8.158134524309385E-4</v>
+        <v>0.00081198148442042373</v>
       </c>
       <c r="E16">
-        <v>-6.0054923637039605E-6</v>
+        <v>-5.976228130639364e-06</v>
       </c>
       <c r="F16">
-        <v>-2.7265044014394141E-4</v>
+        <v>-0.00027304818440414963</v>
       </c>
       <c r="G16">
-        <v>-2.6326142874530389E-4</v>
+        <v>-0.00026188707195839989</v>
       </c>
       <c r="H16">
-        <v>7.1624881933539408E-4</v>
+        <v>0.00071408223312623663</v>
       </c>
       <c r="I16">
-        <v>9.2164970538139682E-4</v>
+        <v>0.00092075184664219237</v>
       </c>
       <c r="J16">
-        <v>-3.2502564908160753E-4</v>
+        <v>-0.00032418835931692647</v>
       </c>
       <c r="K16">
-        <v>-1.5793164134294754E-4</v>
+        <v>-0.00015188262390142433</v>
       </c>
       <c r="L16">
-        <v>1.8061883562657446E-4</v>
+        <v>0.00018494354611160832</v>
       </c>
       <c r="M16">
-        <v>-3.175935004988209E-4</v>
+        <v>-0.00031309765868033339</v>
       </c>
       <c r="N16">
-        <v>-4.6912881963381402E-4</v>
+        <v>-0.00046100272930950283</v>
       </c>
       <c r="O16">
-        <v>3.2185812934484859E-4</v>
+        <v>0.00032879265044232463</v>
       </c>
       <c r="P16">
-        <v>-7.0848439702978503E-4</v>
+        <v>-0.00070595507484198577</v>
       </c>
       <c r="Q16">
-        <v>1.2075948034216237E-2</v>
+        <v>0.012064331525252787</v>
       </c>
       <c r="R16">
-        <v>9.0992433862796054E-3</v>
+        <v>0.0090879382735266755</v>
       </c>
       <c r="S16">
-        <v>9.1529282177041718E-3</v>
+        <v>0.0091420631976824544</v>
       </c>
       <c r="T16">
-        <v>9.0704919941855238E-3</v>
+        <v>0.009059442024733199</v>
       </c>
       <c r="U16">
-        <v>9.1552732052523622E-3</v>
+        <v>0.0091454577794445654</v>
       </c>
       <c r="V16">
-        <v>9.0834763367899415E-3</v>
+        <v>0.0090728958959440317</v>
       </c>
       <c r="W16">
-        <v>-9.3347218570766438E-5</v>
+        <v>-9.318329319005583e-05</v>
       </c>
       <c r="X16">
-        <v>3.2897643488462736E-4</v>
+        <v>0.000329072474872843</v>
       </c>
       <c r="Y16">
-        <v>-3.5544470176122403E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.035419868292293544</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>42</v>
       </c>
       <c r="B17">
-        <v>3.5274411052925378E-2</v>
+        <v>0.034586014025953613</v>
       </c>
       <c r="C17">
-        <v>4.4969172702185364E-4</v>
+        <v>0.00044776713366126734</v>
       </c>
       <c r="D17">
-        <v>1.4442747913062243E-3</v>
+        <v>0.0014396605690730341</v>
       </c>
       <c r="E17">
-        <v>-1.077712555550578E-5</v>
+        <v>-1.0741315716370024e-05</v>
       </c>
       <c r="F17">
-        <v>-3.8716513852304207E-4</v>
+        <v>-0.00038996917383920388</v>
       </c>
       <c r="G17">
-        <v>-2.3376743133066147E-4</v>
+        <v>-0.00023320823863586665</v>
       </c>
       <c r="H17">
-        <v>3.8410221112102072E-4</v>
+        <v>0.00038317693240104336</v>
       </c>
       <c r="I17">
-        <v>9.3795861874180087E-4</v>
+        <v>0.00093942674631004365</v>
       </c>
       <c r="J17">
-        <v>-2.1588199243713357E-4</v>
+        <v>-0.00021179480611657059</v>
       </c>
       <c r="K17">
-        <v>-6.6416689999699782E-4</v>
+        <v>-0.00068479383296105902</v>
       </c>
       <c r="L17">
-        <v>2.4575039570695059E-4</v>
+        <v>0.0002470574468967097</v>
       </c>
       <c r="M17">
-        <v>-4.1962949842579231E-4</v>
+        <v>-0.00041469700503659387</v>
       </c>
       <c r="N17">
-        <v>-7.1667185048940579E-4</v>
+        <v>-0.0007300117378038918</v>
       </c>
       <c r="O17">
-        <v>-2.7619838523818517E-4</v>
+        <v>-0.00029040401314599403</v>
       </c>
       <c r="P17">
-        <v>-2.325408938903858E-4</v>
+        <v>-0.00022447869306467961</v>
       </c>
       <c r="Q17">
-        <v>9.0992433862796054E-3</v>
+        <v>0.0090879382735266755</v>
       </c>
       <c r="R17">
-        <v>1.2319996239166603E-2</v>
+        <v>0.012313760734629847</v>
       </c>
       <c r="S17">
-        <v>9.1997588140308763E-3</v>
+        <v>0.0091895764286037216</v>
       </c>
       <c r="T17">
-        <v>9.0023513306020011E-3</v>
+        <v>0.0089918782420620978</v>
       </c>
       <c r="U17">
-        <v>9.1459742295460101E-3</v>
+        <v>0.0091368939535224122</v>
       </c>
       <c r="V17">
-        <v>9.050041919103656E-3</v>
+        <v>0.0090404377603022917</v>
       </c>
       <c r="W17">
-        <v>-7.3419817233912727E-5</v>
+        <v>-7.3419535549368114e-05</v>
       </c>
       <c r="X17">
-        <v>2.9153687380506239E-4</v>
+        <v>0.000293683324131135</v>
       </c>
       <c r="Y17">
-        <v>-5.5988083672354416E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.055817530052485381</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>43</v>
       </c>
       <c r="B18">
-        <v>0.11899269376577361</v>
+        <v>0.11857938807929864</v>
       </c>
       <c r="C18">
-        <v>8.309067437706273E-4</v>
+        <v>0.00082959803679514914</v>
       </c>
       <c r="D18">
-        <v>1.407541414986945E-3</v>
+        <v>0.0014029889963918553</v>
       </c>
       <c r="E18">
-        <v>-1.0685400757698298E-5</v>
+        <v>-1.0651247621253577e-05</v>
       </c>
       <c r="F18">
-        <v>-6.1038663719111853E-4</v>
+        <v>-0.00060754036464548715</v>
       </c>
       <c r="G18">
-        <v>1.4054516612603844E-4</v>
+        <v>0.00013983279192682392</v>
       </c>
       <c r="H18">
-        <v>6.2129832502369193E-4</v>
+        <v>0.00062014216709299543</v>
       </c>
       <c r="I18">
-        <v>1.1602133432301888E-3</v>
+        <v>0.0011585336135670626</v>
       </c>
       <c r="J18">
-        <v>1.0665282318286394E-4</v>
+        <v>0.00010459524885630001</v>
       </c>
       <c r="K18">
-        <v>-9.2843268530518248E-4</v>
+        <v>-0.00090945759639161775</v>
       </c>
       <c r="L18">
-        <v>2.8181945827751109E-4</v>
+        <v>0.00028828661919713005</v>
       </c>
       <c r="M18">
-        <v>-3.2529913164938159E-4</v>
+        <v>-0.00031677030948621321</v>
       </c>
       <c r="N18">
-        <v>-1.4945102424165509E-3</v>
+        <v>-0.0014761581629677287</v>
       </c>
       <c r="O18">
-        <v>-5.0768375328096396E-4</v>
+        <v>-0.00049015985723418966</v>
       </c>
       <c r="P18">
-        <v>-4.5953681704153369E-4</v>
+        <v>-0.00046010193651794168</v>
       </c>
       <c r="Q18">
-        <v>9.1529282177041718E-3</v>
+        <v>0.0091420631976824544</v>
       </c>
       <c r="R18">
-        <v>9.1997588140308763E-3</v>
+        <v>0.0091895764286037216</v>
       </c>
       <c r="S18">
-        <v>1.2600880563958963E-2</v>
+        <v>0.012588326546902562</v>
       </c>
       <c r="T18">
-        <v>9.0451570456724292E-3</v>
+        <v>0.0090344375993805914</v>
       </c>
       <c r="U18">
-        <v>9.2434957487699532E-3</v>
+        <v>0.009234623471639055</v>
       </c>
       <c r="V18">
-        <v>9.0671946737533524E-3</v>
+        <v>0.0090572299713308508</v>
       </c>
       <c r="W18">
-        <v>-1.3035026285169256E-4</v>
+        <v>-0.00013020491830092464</v>
       </c>
       <c r="X18">
-        <v>3.9156635859698401E-4</v>
+        <v>0.00039201324691550202</v>
       </c>
       <c r="Y18">
-        <v>-5.3277359124532006E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.053136355699460042</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>44</v>
       </c>
       <c r="B19">
-        <v>1.345626889885025E-2</v>
+        <v>0.0130712311931404</v>
       </c>
       <c r="C19">
-        <v>5.1643597614740725E-4</v>
+        <v>0.00051647145245573554</v>
       </c>
       <c r="D19">
-        <v>1.263294423463554E-3</v>
+        <v>0.0012590988922415863</v>
       </c>
       <c r="E19">
-        <v>-9.5162780795942856E-6</v>
+        <v>-9.4827576090265138e-06</v>
       </c>
       <c r="F19">
-        <v>-5.5785807744340721E-4</v>
+        <v>-0.00055609464639379269</v>
       </c>
       <c r="G19">
-        <v>-5.5210331818639907E-4</v>
+        <v>-0.00054905308772949107</v>
       </c>
       <c r="H19">
-        <v>5.1637967594370593E-4</v>
+        <v>0.00051451398447009342</v>
       </c>
       <c r="I19">
-        <v>7.4961405640390174E-4</v>
+        <v>0.00074957652391749777</v>
       </c>
       <c r="J19">
-        <v>5.8516892856338987E-5</v>
+        <v>5.7058179169587608e-05</v>
       </c>
       <c r="K19">
-        <v>-4.9762042177596381E-4</v>
+        <v>-0.00049345002928025822</v>
       </c>
       <c r="L19">
-        <v>9.4085157568694899E-5</v>
+        <v>9.4756114982073869e-05</v>
       </c>
       <c r="M19">
-        <v>-2.7769854888019547E-4</v>
+        <v>-0.00027258269664574841</v>
       </c>
       <c r="N19">
-        <v>-5.7233937837377919E-4</v>
+        <v>-0.00056630085552690328</v>
       </c>
       <c r="O19">
-        <v>-1.5741621053791399E-5</v>
+        <v>-1.0636820977943245e-05</v>
       </c>
       <c r="P19">
-        <v>-4.150214162990573E-4</v>
+        <v>-0.00041266291223726495</v>
       </c>
       <c r="Q19">
-        <v>9.0704919941855238E-3</v>
+        <v>0.009059442024733199</v>
       </c>
       <c r="R19">
-        <v>9.0023513306020011E-3</v>
+        <v>0.0089918782420620978</v>
       </c>
       <c r="S19">
-        <v>9.0451570456724292E-3</v>
+        <v>0.0090344375993805914</v>
       </c>
       <c r="T19">
-        <v>1.1190532690968983E-2</v>
+        <v>0.011178322109693174</v>
       </c>
       <c r="U19">
-        <v>9.0516311242653039E-3</v>
+        <v>0.0090413424177446366</v>
       </c>
       <c r="V19">
-        <v>8.9926376723614993E-3</v>
+        <v>0.008982145587705331</v>
       </c>
       <c r="W19">
-        <v>-1.062652756716239E-4</v>
+        <v>-0.00010611620605994641</v>
       </c>
       <c r="X19">
-        <v>4.9934655680046892E-4</v>
+        <v>0.00049952153895423384</v>
       </c>
       <c r="Y19">
-        <v>-4.9241013287212226E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.049107511423740924</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>45</v>
       </c>
       <c r="B20">
-        <v>1.3903899726750308E-2</v>
+        <v>0.013967264549363593</v>
       </c>
       <c r="C20">
-        <v>1.7082526894713007E-4</v>
+        <v>0.00017059230967167416</v>
       </c>
       <c r="D20">
-        <v>1.5363959200552016E-3</v>
+        <v>0.0015308726288786462</v>
       </c>
       <c r="E20">
-        <v>-1.1759368423350442E-5</v>
+        <v>-1.171644617455113e-05</v>
       </c>
       <c r="F20">
-        <v>-4.5367507191610562E-4</v>
+        <v>-0.00045459139896747783</v>
       </c>
       <c r="G20">
-        <v>-3.9680319285552434E-4</v>
+        <v>-0.00039776619927753276</v>
       </c>
       <c r="H20">
-        <v>3.9994738844769274E-4</v>
+        <v>0.00039584482630213448</v>
       </c>
       <c r="I20">
-        <v>1.1489110652464554E-3</v>
+        <v>0.0011492510222453026</v>
       </c>
       <c r="J20">
-        <v>-1.1998153827468688E-4</v>
+        <v>-0.00011723372914448568</v>
       </c>
       <c r="K20">
-        <v>-2.9336562375335655E-4</v>
+        <v>-0.00030308872570340272</v>
       </c>
       <c r="L20">
-        <v>6.6737962189110682E-4</v>
+        <v>0.00067910953308937126</v>
       </c>
       <c r="M20">
-        <v>-2.0693714069744689E-4</v>
+        <v>-0.00021043593007097025</v>
       </c>
       <c r="N20">
-        <v>-6.0557999574334734E-4</v>
+        <v>-0.00060981189701043124</v>
       </c>
       <c r="O20">
-        <v>2.1926810676775339E-4</v>
+        <v>0.00021376059820605101</v>
       </c>
       <c r="P20">
-        <v>-1.5085902177469494E-4</v>
+        <v>-0.00014433221484819105</v>
       </c>
       <c r="Q20">
-        <v>9.1552732052523622E-3</v>
+        <v>0.0091454577794445654</v>
       </c>
       <c r="R20">
-        <v>9.1459742295460101E-3</v>
+        <v>0.0091368939535224122</v>
       </c>
       <c r="S20">
-        <v>9.2434957487699532E-3</v>
+        <v>0.009234623471639055</v>
       </c>
       <c r="T20">
-        <v>9.0516311242653039E-3</v>
+        <v>0.0090413424177446366</v>
       </c>
       <c r="U20">
-        <v>1.1364039921707984E-2</v>
+        <v>0.011357868540631045</v>
       </c>
       <c r="V20">
-        <v>9.0629107026245735E-3</v>
+        <v>0.0090542775408282306</v>
       </c>
       <c r="W20">
-        <v>-9.8489935979540616E-5</v>
+        <v>-9.8612145634633568e-05</v>
       </c>
       <c r="X20">
-        <v>3.7435262496879253E-4</v>
+        <v>0.00037693288745419256</v>
       </c>
       <c r="Y20">
-        <v>-5.8030625533849134E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.057839897434941987</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
         <v>46</v>
       </c>
       <c r="B21">
-        <v>-8.8597285494387903E-2</v>
+        <v>-0.088587176656274275</v>
       </c>
       <c r="C21">
-        <v>7.3700127852097672E-4</v>
+        <v>0.00073812788105235097</v>
       </c>
       <c r="D21">
-        <v>1.3115773147099365E-3</v>
+        <v>0.0013075323164292198</v>
       </c>
       <c r="E21">
-        <v>-9.5534058688779026E-6</v>
+        <v>-9.5214589330956743e-06</v>
       </c>
       <c r="F21">
-        <v>-3.0297118443714348E-4</v>
+        <v>-0.00030461590084548788</v>
       </c>
       <c r="G21">
-        <v>-2.9916415842864974E-7</v>
+        <v>-1.8100126882875794e-06</v>
       </c>
       <c r="H21">
-        <v>7.2283373151140634E-4</v>
+        <v>0.00071959659101857032</v>
       </c>
       <c r="I21">
-        <v>8.6136483622944961E-4</v>
+        <v>0.00086122911721351724</v>
       </c>
       <c r="J21">
-        <v>-5.4105670192655664E-4</v>
+        <v>-0.00053804589188520026</v>
       </c>
       <c r="K21">
-        <v>-3.6664292016380662E-4</v>
+        <v>-0.00037340911592429653</v>
       </c>
       <c r="L21">
-        <v>2.2238624859621223E-4</v>
+        <v>0.00022599738256413486</v>
       </c>
       <c r="M21">
-        <v>-3.0323731948758768E-4</v>
+        <v>-0.00029849957080637746</v>
       </c>
       <c r="N21">
-        <v>-4.9110413306726599E-4</v>
+        <v>-0.00049296186557148546</v>
       </c>
       <c r="O21">
-        <v>1.4195395439349588E-4</v>
+        <v>0.00013910559227940655</v>
       </c>
       <c r="P21">
-        <v>-5.1684723191767741E-4</v>
+        <v>-0.00051246829038730413</v>
       </c>
       <c r="Q21">
-        <v>9.0834763367899415E-3</v>
+        <v>0.0090728958959440317</v>
       </c>
       <c r="R21">
-        <v>9.050041919103656E-3</v>
+        <v>0.0090404377603022917</v>
       </c>
       <c r="S21">
-        <v>9.0671946737533524E-3</v>
+        <v>0.0090572299713308508</v>
       </c>
       <c r="T21">
-        <v>8.9926376723614993E-3</v>
+        <v>0.008982145587705331</v>
       </c>
       <c r="U21">
-        <v>9.0629107026245735E-3</v>
+        <v>0.0090542775408282306</v>
       </c>
       <c r="V21">
-        <v>1.1581568265054531E-2</v>
+        <v>0.011571097413536827</v>
       </c>
       <c r="W21">
-        <v>-1.0801340622833765E-4</v>
+        <v>-0.00010803571981922645</v>
       </c>
       <c r="X21">
-        <v>4.0624947794898119E-4</v>
+        <v>0.00040753651309606348</v>
       </c>
       <c r="Y21">
-        <v>-5.2241337165325002E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.052102318018486304</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
         <v>47</v>
       </c>
       <c r="B22">
-        <v>-4.0144177783449593E-2</v>
+        <v>-0.040131579819459355</v>
       </c>
       <c r="C22">
-        <v>-7.9151029552920537E-5</v>
+        <v>-7.9289225411918182e-05</v>
       </c>
       <c r="D22">
-        <v>-6.0050833899493589E-5</v>
+        <v>-5.9570187536984315e-05</v>
       </c>
       <c r="E22">
-        <v>3.8245581064729384E-7</v>
+        <v>3.7841672517012069e-07</v>
       </c>
       <c r="F22">
-        <v>-6.8673621271978305E-5</v>
+        <v>-6.8706949786379728e-05</v>
       </c>
       <c r="G22">
-        <v>-7.7964990227346112E-5</v>
+        <v>-7.8138802062170318e-05</v>
       </c>
       <c r="H22">
-        <v>-5.7591344688285846E-5</v>
+        <v>-5.7578600631331262e-05</v>
       </c>
       <c r="I22">
-        <v>2.6233599425287853E-5</v>
+        <v>2.632652791225256e-05</v>
       </c>
       <c r="J22">
-        <v>1.2991010158539505E-4</v>
+        <v>0.00012999513591543249</v>
       </c>
       <c r="K22">
-        <v>4.1844362811155984E-5</v>
+        <v>4.3661365617540977e-05</v>
       </c>
       <c r="L22">
-        <v>-2.6400060074644198E-5</v>
+        <v>-2.6903043401677539e-05</v>
       </c>
       <c r="M22">
-        <v>2.2241903466405089E-5</v>
+        <v>2.1888226458871693e-05</v>
       </c>
       <c r="N22">
-        <v>6.5200146862335402E-5</v>
+        <v>6.6429765941664488e-05</v>
       </c>
       <c r="O22">
-        <v>5.4530800481503681E-5</v>
+        <v>5.5824246682463627e-05</v>
       </c>
       <c r="P22">
-        <v>5.0843511466612946E-5</v>
+        <v>5.0350304434154159e-05</v>
       </c>
       <c r="Q22">
-        <v>-9.3347218570766438E-5</v>
+        <v>-9.318329319005583e-05</v>
       </c>
       <c r="R22">
-        <v>-7.3419817233912727E-5</v>
+        <v>-7.3419535549368114e-05</v>
       </c>
       <c r="S22">
-        <v>-1.3035026285169256E-4</v>
+        <v>-0.00013020491830092464</v>
       </c>
       <c r="T22">
-        <v>-1.062652756716239E-4</v>
+        <v>-0.00010611620605994641</v>
       </c>
       <c r="U22">
-        <v>-9.8489935979540616E-5</v>
+        <v>-9.8612145634633568e-05</v>
       </c>
       <c r="V22">
-        <v>-1.0801340622833765E-4</v>
+        <v>-0.00010803571981922645</v>
       </c>
       <c r="W22">
-        <v>6.990424412946526E-5</v>
+        <v>6.9956891531420892e-05</v>
       </c>
       <c r="X22">
-        <v>-4.9818190918030308E-4</v>
+        <v>-0.00049853515140051001</v>
       </c>
       <c r="Y22">
-        <v>1.3654990943034462E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+        <v>0.0013492451742211121</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
         <v>48</v>
       </c>
       <c r="B23">
-        <v>0.20983889692407459</v>
+        <v>0.20999337784571992</v>
       </c>
       <c r="C23">
-        <v>1.8073783339145636E-4</v>
+        <v>0.00018216001871530795</v>
       </c>
       <c r="D23">
-        <v>2.0734956898646462E-4</v>
+        <v>0.00020227702582209517</v>
       </c>
       <c r="E23">
-        <v>-1.0624288981172418E-6</v>
+        <v>-1.0180980463591e-06</v>
       </c>
       <c r="F23">
-        <v>5.8315810217423464E-4</v>
+        <v>0.0005850145535446355</v>
       </c>
       <c r="G23">
-        <v>8.561282207184967E-4</v>
+        <v>0.00085755801382725316</v>
       </c>
       <c r="H23">
-        <v>3.7086542311981865E-4</v>
+        <v>0.00036923980199012052</v>
       </c>
       <c r="I23">
-        <v>6.9311461262675693E-5</v>
+        <v>6.8658656077859011e-05</v>
       </c>
       <c r="J23">
-        <v>-7.638186510975295E-4</v>
+        <v>-0.00076636220934089838</v>
       </c>
       <c r="K23">
-        <v>-1.8034555545380811E-4</v>
+        <v>-0.00021331245749532483</v>
       </c>
       <c r="L23">
-        <v>4.0281613969062177E-4</v>
+        <v>0.00040639259862843783</v>
       </c>
       <c r="M23">
-        <v>1.6971353593052494E-4</v>
+        <v>0.00015509365242734677</v>
       </c>
       <c r="N23">
-        <v>-7.8600624646599053E-5</v>
+        <v>-0.0001061064384464544</v>
       </c>
       <c r="O23">
-        <v>-5.4496344426982826E-5</v>
+        <v>-8.3194575211196359e-05</v>
       </c>
       <c r="P23">
-        <v>1.3112722604240071E-4</v>
+        <v>0.00013761287005871416</v>
       </c>
       <c r="Q23">
-        <v>3.2897643488462736E-4</v>
+        <v>0.000329072474872843</v>
       </c>
       <c r="R23">
-        <v>2.9153687380506239E-4</v>
+        <v>0.000293683324131135</v>
       </c>
       <c r="S23">
-        <v>3.9156635859698401E-4</v>
+        <v>0.00039201324691550202</v>
       </c>
       <c r="T23">
-        <v>4.9934655680046892E-4</v>
+        <v>0.00049952153895423384</v>
       </c>
       <c r="U23">
-        <v>3.7435262496879253E-4</v>
+        <v>0.00037693288745419256</v>
       </c>
       <c r="V23">
-        <v>4.0624947794898119E-4</v>
+        <v>0.00040753651309606348</v>
       </c>
       <c r="W23">
-        <v>-4.9818190918030308E-4</v>
+        <v>-0.00049853515140051001</v>
       </c>
       <c r="X23">
-        <v>5.871367293781727E-3</v>
+        <v>0.0058724209807367441</v>
       </c>
       <c r="Y23">
-        <v>-4.2629935029920366E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+        <v>-0.0040856761577326706</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
         <v>49</v>
       </c>
       <c r="B24">
-        <v>-0.48889273775295861</v>
+        <v>-0.46472523268020427</v>
       </c>
       <c r="C24">
-        <v>-1.6808861133236104E-2</v>
+        <v>-0.016876669133454862</v>
       </c>
       <c r="D24">
-        <v>-0.26068014295401309</v>
+        <v>-0.26066544532658087</v>
       </c>
       <c r="E24">
-        <v>2.0813413306304922E-3</v>
+        <v>0.0020812749983526221</v>
       </c>
       <c r="F24">
-        <v>0.18106981320598359</v>
+        <v>0.18114126091484417</v>
       </c>
       <c r="G24">
-        <v>0.16650170403807674</v>
+        <v>0.16653561316098453</v>
       </c>
       <c r="H24">
-        <v>-1.4602595817448792E-2</v>
+        <v>-0.01456235400284589</v>
       </c>
       <c r="I24">
-        <v>-2.8459061067412694E-2</v>
+        <v>-0.028493076642081804</v>
       </c>
       <c r="J24">
-        <v>-0.15992406178289431</v>
+        <v>-0.16008034423523143</v>
       </c>
       <c r="K24">
-        <v>-6.0137935834939371E-3</v>
+        <v>-0.0058203708595809534</v>
       </c>
       <c r="L24">
-        <v>-1.6787752027816405E-2</v>
+        <v>-0.016489606447997539</v>
       </c>
       <c r="M24">
-        <v>-1.5546372834418024E-2</v>
+        <v>-0.015531617014040294</v>
       </c>
       <c r="N24">
-        <v>-2.4154563808679808E-2</v>
+        <v>-0.023964545151206884</v>
       </c>
       <c r="O24">
-        <v>-3.4916024665207573E-2</v>
+        <v>-0.034712531080204834</v>
       </c>
       <c r="P24">
-        <v>1.4871309672353936E-2</v>
+        <v>0.014888060808974674</v>
       </c>
       <c r="Q24">
-        <v>-3.5544470176122403E-2</v>
+        <v>-0.035419868292293544</v>
       </c>
       <c r="R24">
-        <v>-5.5988083672354416E-2</v>
+        <v>-0.055817530052485381</v>
       </c>
       <c r="S24">
-        <v>-5.3277359124532006E-2</v>
+        <v>-0.053136355699460042</v>
       </c>
       <c r="T24">
-        <v>-4.9241013287212226E-2</v>
+        <v>-0.049107511423740924</v>
       </c>
       <c r="U24">
-        <v>-5.8030625533849134E-2</v>
+        <v>-0.057839897434941987</v>
       </c>
       <c r="V24">
-        <v>-5.2241337165325002E-2</v>
+        <v>-0.052102318018486304</v>
       </c>
       <c r="W24">
-        <v>1.3654990943034462E-3</v>
+        <v>0.0013492451742211121</v>
       </c>
       <c r="X24">
-        <v>-4.2629935029920366E-3</v>
+        <v>-0.0040856761577326706</v>
       </c>
       <c r="Y24">
-        <v>8.1960807677630143</v>
+        <v>8.1952885931595603</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AF31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -2631,7 +2339,7 @@
       <c r="K1" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>51</v>
       </c>
       <c r="M1" t="s">
@@ -2695,2947 +2403,2946 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
       <c r="B2">
-        <v>0.46828156083912664</v>
+        <v>0.46793575394715908</v>
       </c>
       <c r="C2">
-        <v>1.317933254590131E-3</v>
+        <v>0.0013238640994565757</v>
       </c>
       <c r="D2">
-        <v>2.6351995467891723E-4</v>
+        <v>0.00026080669114111443</v>
       </c>
       <c r="E2">
-        <v>-1.8949087682106189E-6</v>
+        <v>-1.8731033982084113e-06</v>
       </c>
       <c r="F2">
-        <v>1.6125286979863651E-4</v>
+        <v>0.00016528187142263368</v>
       </c>
       <c r="G2">
-        <v>1.4019254357231393E-4</v>
+        <v>0.00014379480133129932</v>
       </c>
       <c r="H2">
-        <v>5.2905596644327236E-5</v>
+        <v>5.2606500120361937e-05</v>
       </c>
       <c r="I2">
-        <v>-1.7529261826953199E-5</v>
+        <v>-1.8416785791032823e-05</v>
       </c>
       <c r="J2">
-        <v>-2.2022144852791754E-4</v>
+        <v>-0.00021958150897450593</v>
       </c>
       <c r="K2">
-        <v>6.6123127470460355E-4</v>
+        <v>0.00067192034012660711</v>
       </c>
       <c r="L2">
-        <v>-4.8913121880072967E-5</v>
+        <v>-5.5264151413928235e-05</v>
       </c>
       <c r="M2">
-        <v>6.0159217809408101E-5</v>
+        <v>6.3376609343299421e-05</v>
       </c>
       <c r="N2">
-        <v>7.9045820025245081E-5</v>
+        <v>7.2253227151967227e-05</v>
       </c>
       <c r="O2">
-        <v>1.1942233552537671E-4</v>
+        <v>0.00012306410155555125</v>
       </c>
       <c r="P2">
-        <v>1.1547551740743927E-4</v>
+        <v>0.00011944305151244749</v>
       </c>
       <c r="Q2">
-        <v>-4.2326165195228981E-4</v>
+        <v>-0.0004304664801795211</v>
       </c>
       <c r="R2">
-        <v>6.7479034677417641E-4</v>
+        <v>0.00067577935592695029</v>
       </c>
       <c r="S2">
-        <v>-2.9874274436318573E-4</v>
+        <v>-0.00029915017580784423</v>
       </c>
       <c r="T2">
-        <v>-1.2882799477750343E-4</v>
+        <v>-0.00013079096663129295</v>
       </c>
       <c r="U2">
-        <v>-4.3888650747473957E-5</v>
+        <v>-4.1247832463237971e-05</v>
       </c>
       <c r="V2">
-        <v>1.1905073398588788E-4</v>
+        <v>0.00011798726149560331</v>
       </c>
       <c r="W2">
-        <v>1.2246231362551363E-4</v>
+        <v>0.0001216580083301035</v>
       </c>
       <c r="X2">
-        <v>1.1841634004566988E-4</v>
+        <v>0.00011718669828638859</v>
       </c>
       <c r="Y2">
-        <v>5.3230216531714952E-5</v>
+        <v>4.8178744582271665e-05</v>
       </c>
       <c r="Z2">
-        <v>1.3865831618414337E-4</v>
+        <v>0.00013774607665294658</v>
       </c>
       <c r="AA2">
-        <v>1.0818608546091598E-4</v>
+        <v>0.00010682639065885913</v>
       </c>
       <c r="AB2">
-        <v>6.904116465748897E-6</v>
+        <v>4.9126265871130698e-06</v>
       </c>
       <c r="AC2">
-        <v>2.5353164022284618E-6</v>
+        <v>2.4776307102107787e-06</v>
       </c>
       <c r="AD2">
-        <v>-2.3776572513753403E-5</v>
+        <v>-2.3223249741205097e-05</v>
       </c>
       <c r="AE2">
-        <v>-6.2605724090432444E-6</v>
+        <v>-4.4678625891582738e-06</v>
       </c>
       <c r="AF2">
-        <v>-1.0362830863151266E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.010287050854226872</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3">
-        <v>-0.13305849153237556</v>
+        <v>-0.13252089450971108</v>
       </c>
       <c r="C3">
-        <v>2.6351995467891723E-4</v>
+        <v>0.00026080669114111443</v>
       </c>
       <c r="D3">
-        <v>3.9911821609429216E-3</v>
+        <v>0.0039833749777673788</v>
       </c>
       <c r="E3">
-        <v>-3.2617005872278605E-5</v>
+        <v>-3.2550725639991296e-05</v>
       </c>
       <c r="F3">
-        <v>-3.0743431384759601E-3</v>
+        <v>-0.0030662949033974166</v>
       </c>
       <c r="G3">
-        <v>-2.8461126722139837E-3</v>
+        <v>-0.0028380985746906465</v>
       </c>
       <c r="H3">
-        <v>-1.6699693319072303E-5</v>
+        <v>-1.6462846914606336e-05</v>
       </c>
       <c r="I3">
-        <v>-3.889118890994421E-5</v>
+        <v>-3.9429936100229129e-05</v>
       </c>
       <c r="J3">
-        <v>2.9036669500218798E-3</v>
+        <v>0.0028973481320201666</v>
       </c>
       <c r="K3">
-        <v>-1.0827520633596363E-4</v>
+        <v>-0.0001140924911570999</v>
       </c>
       <c r="L3">
-        <v>6.2770874967373914E-4</v>
+        <v>0.00062055094659239918</v>
       </c>
       <c r="M3">
-        <v>9.6512158729210318E-5</v>
+        <v>9.743625964996061e-05</v>
       </c>
       <c r="N3">
-        <v>-1.3184482315622015E-4</v>
+        <v>-0.00013868008304897435</v>
       </c>
       <c r="O3">
-        <v>-8.1319415389565462E-5</v>
+        <v>-8.2348075255332664e-05</v>
       </c>
       <c r="P3">
-        <v>-1.8703019726721941E-4</v>
+        <v>-0.00018815207593221584</v>
       </c>
       <c r="Q3">
-        <v>-2.0887139217288945E-4</v>
+        <v>-0.00020996914975170578</v>
       </c>
       <c r="R3">
-        <v>3.3549961559651859E-4</v>
+        <v>0.00033289755269206873</v>
       </c>
       <c r="S3">
-        <v>-2.1927914050563421E-4</v>
+        <v>-0.00021995960783803559</v>
       </c>
       <c r="T3">
-        <v>-4.7693563485250515E-4</v>
+        <v>-0.00047823499328440017</v>
       </c>
       <c r="U3">
-        <v>-8.7403088317757407E-5</v>
+        <v>-7.9057641188312079e-05</v>
       </c>
       <c r="V3">
-        <v>-3.9630962419177906E-5</v>
+        <v>-4.1500887747793549e-05</v>
       </c>
       <c r="W3">
-        <v>-5.6088664379352893E-5</v>
+        <v>-5.6406921666155019e-05</v>
       </c>
       <c r="X3">
-        <v>2.3621705846563201E-5</v>
+        <v>2.3742081909097768e-05</v>
       </c>
       <c r="Y3">
-        <v>1.2143799227627705E-6</v>
+        <v>-3.8704070429579351e-06</v>
       </c>
       <c r="Z3">
-        <v>6.9302106205107461E-5</v>
+        <v>6.8724992871471713e-05</v>
       </c>
       <c r="AA3">
-        <v>9.9680704468585457E-5</v>
+        <v>9.8212617936709046e-05</v>
       </c>
       <c r="AB3">
-        <v>-7.81267756554474E-6</v>
+        <v>-8.910078441896202e-06</v>
       </c>
       <c r="AC3">
-        <v>7.9028390590845342E-6</v>
+        <v>7.6894564163970409e-06</v>
       </c>
       <c r="AD3">
-        <v>-3.6344385382469646E-5</v>
+        <v>-3.5578004677468134e-05</v>
       </c>
       <c r="AE3">
-        <v>-1.1806164469294056E-4</v>
+        <v>-0.00011682690919145866</v>
       </c>
       <c r="AF3">
-        <v>-0.12185803817751206</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.1216221215987221</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>29</v>
       </c>
       <c r="B4">
-        <v>2.5587336153346401E-3</v>
+        <v>0.0025533116799562215</v>
       </c>
       <c r="C4">
-        <v>-1.8949087682106189E-6</v>
+        <v>-1.8731033982084113e-06</v>
       </c>
       <c r="D4">
-        <v>-3.2617005872278605E-5</v>
+        <v>-3.2550725639991296e-05</v>
       </c>
       <c r="E4">
-        <v>2.6828608101512658E-7</v>
+        <v>2.6772357017140066e-07</v>
       </c>
       <c r="F4">
-        <v>2.6529668322655101E-5</v>
+        <v>2.6461933695672187e-05</v>
       </c>
       <c r="G4">
-        <v>2.4491446781841578E-5</v>
+        <v>2.4423866699323671e-05</v>
       </c>
       <c r="H4">
-        <v>1.7343125147841508E-7</v>
+        <v>1.7166618849454034e-07</v>
       </c>
       <c r="I4">
-        <v>1.9391287751345271E-7</v>
+        <v>1.9760001215703659e-07</v>
       </c>
       <c r="J4">
-        <v>-2.6012675408419359E-5</v>
+        <v>-2.5962078436814911e-05</v>
       </c>
       <c r="K4">
-        <v>7.5152924264724531E-7</v>
+        <v>7.9479329864851176e-07</v>
       </c>
       <c r="L4">
-        <v>-5.0196387272318454E-6</v>
+        <v>-4.9540706792555056e-06</v>
       </c>
       <c r="M4">
-        <v>-8.7456991016698362E-7</v>
+        <v>-8.7934830508124527e-07</v>
       </c>
       <c r="N4">
-        <v>9.9457475663084313E-7</v>
+        <v>1.0473007521171212e-06</v>
       </c>
       <c r="O4">
-        <v>6.0846141394254764E-7</v>
+        <v>6.1753067167807994e-07</v>
       </c>
       <c r="P4">
-        <v>1.4432278013997931E-6</v>
+        <v>1.4512987421101616e-06</v>
       </c>
       <c r="Q4">
-        <v>1.8094565872085687E-6</v>
+        <v>1.815238254891526e-06</v>
       </c>
       <c r="R4">
-        <v>-3.0130221747405795E-6</v>
+        <v>-2.9924091113209866e-06</v>
       </c>
       <c r="S4">
-        <v>1.6623732069506259E-6</v>
+        <v>1.6700638034189311e-06</v>
       </c>
       <c r="T4">
-        <v>3.984075981260774E-6</v>
+        <v>3.9955451880267139e-06</v>
       </c>
       <c r="U4">
-        <v>6.3141847957079455E-7</v>
+        <v>5.6401835505208724e-07</v>
       </c>
       <c r="V4">
-        <v>3.6666186084683935E-7</v>
+        <v>3.8320730658488898e-07</v>
       </c>
       <c r="W4">
-        <v>5.8161907022155884E-7</v>
+        <v>5.8426398834971437e-07</v>
       </c>
       <c r="X4">
-        <v>3.2856827072145524E-8</v>
+        <v>3.1977520128048144e-08</v>
       </c>
       <c r="Y4">
-        <v>2.6728374349146034E-8</v>
+        <v>6.5086707011464354e-08</v>
       </c>
       <c r="Z4">
-        <v>-3.7698988840557685E-7</v>
+        <v>-3.7202786469926578e-07</v>
       </c>
       <c r="AA4">
-        <v>-6.8591618313773562E-7</v>
+        <v>-6.741521444412655e-07</v>
       </c>
       <c r="AB4">
-        <v>7.4841568163490618E-8</v>
+        <v>8.4422650261327652e-08</v>
       </c>
       <c r="AC4">
-        <v>-8.6962150874775284E-8</v>
+        <v>-8.5298855852961786e-08</v>
       </c>
       <c r="AD4">
-        <v>1.9120497312020849E-7</v>
+        <v>1.8555260430182154e-07</v>
       </c>
       <c r="AE4">
-        <v>8.4897259201063401E-7</v>
+        <v>8.3937923825243809e-07</v>
       </c>
       <c r="AF4">
-        <v>9.899097002269196E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.00098791275842285194</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>30</v>
       </c>
       <c r="B5">
-        <v>1.3694363247794523</v>
+        <v>1.3685141602025486</v>
       </c>
       <c r="C5">
-        <v>1.6125286979863651E-4</v>
+        <v>0.00016528187142263368</v>
       </c>
       <c r="D5">
-        <v>-3.0743431384759601E-3</v>
+        <v>-0.0030662949033974166</v>
       </c>
       <c r="E5">
-        <v>2.6529668322655101E-5</v>
+        <v>2.6461933695672187e-05</v>
       </c>
       <c r="F5">
-        <v>6.6015099205308618E-3</v>
+        <v>0.0065972944510503014</v>
       </c>
       <c r="G5">
-        <v>4.4686807341489318E-3</v>
+        <v>0.0044629899992591517</v>
       </c>
       <c r="H5">
-        <v>3.0361065631737474E-5</v>
+        <v>2.9322935170906291e-05</v>
       </c>
       <c r="I5">
-        <v>-9.1843111118318846E-5</v>
+        <v>-9.1478306190129546e-05</v>
       </c>
       <c r="J5">
-        <v>-6.1390699349622921E-3</v>
+        <v>-0.0061467179430682584</v>
       </c>
       <c r="K5">
-        <v>3.9967890983191867E-5</v>
+        <v>4.740363584776041e-05</v>
       </c>
       <c r="L5">
-        <v>2.3842254359761166E-4</v>
+        <v>0.00026270942905487656</v>
       </c>
       <c r="M5">
-        <v>-1.6210494769831538E-4</v>
+        <v>-0.00015861172431358601</v>
       </c>
       <c r="N5">
-        <v>-1.0757101683266101E-5</v>
+        <v>-1.8455124347368894e-06</v>
       </c>
       <c r="O5">
-        <v>-2.5411319357183416E-5</v>
+        <v>-1.3024006284469841e-05</v>
       </c>
       <c r="P5">
-        <v>1.2613560276452523E-4</v>
+        <v>0.00013804361536214841</v>
       </c>
       <c r="Q5">
-        <v>1.7638354082061833E-4</v>
+        <v>0.00017524345245878035</v>
       </c>
       <c r="R5">
-        <v>5.334614974869048E-4</v>
+        <v>0.00053400536797941749</v>
       </c>
       <c r="S5">
-        <v>-1.0446205190958319E-3</v>
+        <v>-0.0010393606857251846</v>
       </c>
       <c r="T5">
-        <v>-5.1706008620285709E-4</v>
+        <v>-0.00051582780279432142</v>
       </c>
       <c r="U5">
-        <v>2.754369199701838E-6</v>
+        <v>1.6490789835040334e-06</v>
       </c>
       <c r="V5">
-        <v>7.7288522244261734E-5</v>
+        <v>7.9434913196970922e-05</v>
       </c>
       <c r="W5">
-        <v>1.5317646621142156E-4</v>
+        <v>0.00015306238546803491</v>
       </c>
       <c r="X5">
-        <v>1.4883785957289786E-4</v>
+        <v>0.00014803026748788639</v>
       </c>
       <c r="Y5">
-        <v>6.0600137503937987E-5</v>
+        <v>6.1839722320284479e-05</v>
       </c>
       <c r="Z5">
-        <v>1.030180871239017E-4</v>
+        <v>0.00010363882469052732</v>
       </c>
       <c r="AA5">
-        <v>-2.615179518489566E-6</v>
+        <v>-2.8384731853136475e-06</v>
       </c>
       <c r="AB5">
-        <v>2.8694224247772376E-5</v>
+        <v>2.8557322717493588e-05</v>
       </c>
       <c r="AC5">
-        <v>-2.65208927625434E-5</v>
+        <v>-2.6204696560632465e-05</v>
       </c>
       <c r="AD5">
-        <v>1.2217974530180642E-5</v>
+        <v>1.0373384236265354e-05</v>
       </c>
       <c r="AE5">
-        <v>4.8669687654673971E-5</v>
+        <v>4.7905722388302818e-05</v>
       </c>
       <c r="AF5">
-        <v>8.891250148184171E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.088654720080440064</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>31</v>
       </c>
       <c r="B6">
-        <v>1.1027322902605532</v>
+        <v>1.1018741739179907</v>
       </c>
       <c r="C6">
-        <v>1.4019254357231393E-4</v>
+        <v>0.00014379480133129932</v>
       </c>
       <c r="D6">
-        <v>-2.8461126722139837E-3</v>
+        <v>-0.0028380985746906465</v>
       </c>
       <c r="E6">
-        <v>2.4491446781841578E-5</v>
+        <v>2.4423866699323671e-05</v>
       </c>
       <c r="F6">
-        <v>4.4686807341489318E-3</v>
+        <v>0.0044629899992591517</v>
       </c>
       <c r="G6">
-        <v>7.2606191181155584E-3</v>
+        <v>0.0072541302105825108</v>
       </c>
       <c r="H6">
-        <v>-2.8816378452953847E-5</v>
+        <v>-2.9901187180231476e-05</v>
       </c>
       <c r="I6">
-        <v>-7.6316453111400714E-5</v>
+        <v>-7.6394175909675309e-05</v>
       </c>
       <c r="J6">
-        <v>-5.3722389513483695E-3</v>
+        <v>-0.0053754871728811451</v>
       </c>
       <c r="K6">
-        <v>3.3980678954891735E-5</v>
+        <v>3.9048066701328349e-05</v>
       </c>
       <c r="L6">
-        <v>1.0631622524553269E-6</v>
+        <v>2.0221421931344852e-05</v>
       </c>
       <c r="M6">
-        <v>-8.7598100233475529E-5</v>
+        <v>-8.2928563362002355e-05</v>
       </c>
       <c r="N6">
-        <v>6.6364127081302259E-5</v>
+        <v>7.4911270605472913e-05</v>
       </c>
       <c r="O6">
-        <v>2.8065530651967974E-5</v>
+        <v>3.391273410147241e-05</v>
       </c>
       <c r="P6">
-        <v>1.5498686885990869E-4</v>
+        <v>0.00016224229690828349</v>
       </c>
       <c r="Q6">
-        <v>1.7383092497874272E-4</v>
+        <v>0.00017314373404284838</v>
       </c>
       <c r="R6">
-        <v>3.9766183659994004E-4</v>
+        <v>0.00039700539379843199</v>
       </c>
       <c r="S6">
-        <v>-9.321461225941137E-4</v>
+        <v>-0.0009275583334300494</v>
       </c>
       <c r="T6">
-        <v>-5.128743988593509E-4</v>
+        <v>-0.00051119961810912502</v>
       </c>
       <c r="U6">
-        <v>3.5950533332993959E-5</v>
+        <v>3.386821370094089e-05</v>
       </c>
       <c r="V6">
-        <v>1.1735735905567344E-4</v>
+        <v>0.00011865074427218607</v>
       </c>
       <c r="W6">
-        <v>5.5624645884946866E-5</v>
+        <v>5.642536678727994e-05</v>
       </c>
       <c r="X6">
-        <v>-6.1543642715794489E-6</v>
+        <v>-5.7741551319351325e-06</v>
       </c>
       <c r="Y6">
-        <v>-4.5158532275312371E-5</v>
+        <v>-4.2541419175512116e-05</v>
       </c>
       <c r="Z6">
-        <v>-5.2784243551179388E-5</v>
+        <v>-5.2264566186684125e-05</v>
       </c>
       <c r="AA6">
-        <v>-1.5847080904152558E-4</v>
+        <v>-0.00015755310279066438</v>
       </c>
       <c r="AB6">
-        <v>-6.1231019737612719E-5</v>
+        <v>-6.1080630215214898e-05</v>
       </c>
       <c r="AC6">
-        <v>-2.1592680214786318E-5</v>
+        <v>-2.1341645404754459e-05</v>
       </c>
       <c r="AD6">
-        <v>-5.6279052144281305E-5</v>
+        <v>-5.7384389136192621e-05</v>
       </c>
       <c r="AE6">
-        <v>4.852695168872101E-5</v>
+        <v>4.7849793608903401e-05</v>
       </c>
       <c r="AF6">
-        <v>8.2591000956276639E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.082340267770000919</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>32</v>
       </c>
       <c r="B7">
-        <v>3.905795925593878E-2</v>
+        <v>0.039309168603647228</v>
       </c>
       <c r="C7">
-        <v>5.2905596644327236E-5</v>
+        <v>5.2606500120361937e-05</v>
       </c>
       <c r="D7">
-        <v>-1.6699693319072303E-5</v>
+        <v>-1.6462846914606336e-05</v>
       </c>
       <c r="E7">
-        <v>1.7343125147841508E-7</v>
+        <v>1.7166618849454034e-07</v>
       </c>
       <c r="F7">
-        <v>3.0361065631737474E-5</v>
+        <v>2.9322935170906291e-05</v>
       </c>
       <c r="G7">
-        <v>-2.8816378452953847E-5</v>
+        <v>-2.9901187180231476e-05</v>
       </c>
       <c r="H7">
-        <v>1.8053396591577989E-3</v>
+        <v>0.0018046643823627546</v>
       </c>
       <c r="I7">
-        <v>1.0075705447430221E-3</v>
+        <v>0.0010073363942093086</v>
       </c>
       <c r="J7">
-        <v>7.096464307682418E-5</v>
+        <v>7.4765861303976349e-05</v>
       </c>
       <c r="K7">
-        <v>-9.5817491673552506E-5</v>
+        <v>-9.5103633714389681e-05</v>
       </c>
       <c r="L7">
-        <v>-7.6062093547468929E-5</v>
+        <v>-8.1295309240372621e-05</v>
       </c>
       <c r="M7">
-        <v>-5.3617857572944134E-6</v>
+        <v>-1.3546435051658675e-05</v>
       </c>
       <c r="N7">
-        <v>-2.4116853083533811E-5</v>
+        <v>-3.6619191247162397e-05</v>
       </c>
       <c r="O7">
-        <v>-4.6698585106363228E-5</v>
+        <v>-5.3826335131041146e-05</v>
       </c>
       <c r="P7">
-        <v>3.3649144332574543E-4</v>
+        <v>0.00032937712331470036</v>
       </c>
       <c r="Q7">
-        <v>5.6744577319602142E-5</v>
+        <v>5.7323925649828976e-05</v>
       </c>
       <c r="R7">
-        <v>2.7001880979072185E-5</v>
+        <v>2.5648343674877696e-05</v>
       </c>
       <c r="S7">
-        <v>-3.5516595288080091E-5</v>
+        <v>-3.5678958558918146e-05</v>
       </c>
       <c r="T7">
-        <v>3.8815558325247458E-5</v>
+        <v>3.9660197303357147e-05</v>
       </c>
       <c r="U7">
-        <v>-1.5690043718079186E-5</v>
+        <v>-1.4349680073702439e-05</v>
       </c>
       <c r="V7">
-        <v>5.4984855633013877E-5</v>
+        <v>5.3806148629456879e-05</v>
       </c>
       <c r="W7">
-        <v>8.4693385359520821E-5</v>
+        <v>8.5785970736355997e-05</v>
       </c>
       <c r="X7">
-        <v>1.0227449040021161E-4</v>
+        <v>0.00010308475397696358</v>
       </c>
       <c r="Y7">
-        <v>1.2191385129444571E-4</v>
+        <v>0.00012400163406832058</v>
       </c>
       <c r="Z7">
-        <v>1.4436710684840757E-4</v>
+        <v>0.00014488697517877833</v>
       </c>
       <c r="AA7">
-        <v>8.724676520181551E-5</v>
+        <v>8.8669377087120793e-05</v>
       </c>
       <c r="AB7">
-        <v>1.216628739850352E-4</v>
+        <v>0.00012156054460784455</v>
       </c>
       <c r="AC7">
-        <v>-7.5258779324508928E-8</v>
+        <v>-6.7567849008904588e-08</v>
       </c>
       <c r="AD7">
-        <v>5.0381547394161199E-6</v>
+        <v>4.2652856073839215e-06</v>
       </c>
       <c r="AE7">
-        <v>-8.4157082835525834E-6</v>
+        <v>-8.8677485128745882e-06</v>
       </c>
       <c r="AF7">
-        <v>-7.4842086026358917E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.00075024134974785439</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>33</v>
       </c>
       <c r="B8">
-        <v>-1.5066034547928358E-2</v>
+        <v>-0.015025446811905874</v>
       </c>
       <c r="C8">
-        <v>-1.7529261826953199E-5</v>
+        <v>-1.8416785791032823e-05</v>
       </c>
       <c r="D8">
-        <v>-3.889118890994421E-5</v>
+        <v>-3.9429936100229129e-05</v>
       </c>
       <c r="E8">
-        <v>1.9391287751345271E-7</v>
+        <v>1.9760001215703659e-07</v>
       </c>
       <c r="F8">
-        <v>-9.1843111118318846E-5</v>
+        <v>-9.1478306190129546e-05</v>
       </c>
       <c r="G8">
-        <v>-7.6316453111400714E-5</v>
+        <v>-7.6394175909675309e-05</v>
       </c>
       <c r="H8">
-        <v>1.0075705447430221E-3</v>
+        <v>0.0010073363942093086</v>
       </c>
       <c r="I8">
-        <v>1.4538949950025457E-3</v>
+        <v>0.001452570837722555</v>
       </c>
       <c r="J8">
-        <v>1.7104066956493162E-4</v>
+        <v>0.00017323385416625711</v>
       </c>
       <c r="K8">
-        <v>-1.4644758320911014E-4</v>
+        <v>-0.000144062768578621</v>
       </c>
       <c r="L8">
-        <v>-2.7988680859991437E-5</v>
+        <v>-3.2436912576122036e-05</v>
       </c>
       <c r="M8">
-        <v>3.6893921217557126E-5</v>
+        <v>3.8066225333145058e-05</v>
       </c>
       <c r="N8">
-        <v>8.2605719810949547E-5</v>
+        <v>7.2676990231244774e-05</v>
       </c>
       <c r="O8">
-        <v>1.2999567124037076E-4</v>
+        <v>0.00012747658642246615</v>
       </c>
       <c r="P8">
-        <v>5.6161171625847804E-4</v>
+        <v>0.00056089991394867934</v>
       </c>
       <c r="Q8">
-        <v>1.3745747940808854E-5</v>
+        <v>1.1374371667580843e-05</v>
       </c>
       <c r="R8">
-        <v>-5.0477405441336413E-5</v>
+        <v>-5.4935247828751853e-05</v>
       </c>
       <c r="S8">
-        <v>1.1539642106720392E-4</v>
+        <v>0.00011524221577113863</v>
       </c>
       <c r="T8">
-        <v>6.8919768821180149E-5</v>
+        <v>6.9516077722265042e-05</v>
       </c>
       <c r="U8">
-        <v>3.1646010236562169E-6</v>
+        <v>1.1538600167796317e-05</v>
       </c>
       <c r="V8">
-        <v>-3.3708711019775415E-6</v>
+        <v>-6.4435918452581786e-06</v>
       </c>
       <c r="W8">
-        <v>-1.5199253212248224E-4</v>
+        <v>-0.00015164298821924288</v>
       </c>
       <c r="X8">
-        <v>-1.1537836761782016E-4</v>
+        <v>-0.00011493013242398222</v>
       </c>
       <c r="Y8">
-        <v>2.1642693637046503E-5</v>
+        <v>2.1315789771607103e-05</v>
       </c>
       <c r="Z8">
-        <v>-1.4584323727857406E-4</v>
+        <v>-0.00014588290102506723</v>
       </c>
       <c r="AA8">
-        <v>-1.1108130216969212E-4</v>
+        <v>-0.0001101965605927568</v>
       </c>
       <c r="AB8">
-        <v>-1.170967151515451E-4</v>
+        <v>-0.00011801960343317856</v>
       </c>
       <c r="AC8">
-        <v>1.9389961749731991E-5</v>
+        <v>1.941753313047549e-05</v>
       </c>
       <c r="AD8">
-        <v>-8.5274694678563897E-6</v>
+        <v>-7.8372901766114852e-06</v>
       </c>
       <c r="AE8">
-        <v>6.5353898931124832E-6</v>
+        <v>6.5603499794597651e-06</v>
       </c>
       <c r="AF8">
-        <v>2.4179104459880023E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.00025950867414788366</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>34</v>
       </c>
       <c r="B9">
-        <v>-0.50468778583287344</v>
+        <v>-0.50479731541543826</v>
       </c>
       <c r="C9">
-        <v>-2.2022144852791754E-4</v>
+        <v>-0.00021958150897450593</v>
       </c>
       <c r="D9">
-        <v>2.9036669500218798E-3</v>
+        <v>0.0028973481320201666</v>
       </c>
       <c r="E9">
-        <v>-2.6012675408419359E-5</v>
+        <v>-2.5962078436814911e-05</v>
       </c>
       <c r="F9">
-        <v>-6.1390699349622921E-3</v>
+        <v>-0.0061467179430682584</v>
       </c>
       <c r="G9">
-        <v>-5.3722389513483695E-3</v>
+        <v>-0.0053754871728811451</v>
       </c>
       <c r="H9">
-        <v>7.096464307682418E-5</v>
+        <v>7.4765861303976349e-05</v>
       </c>
       <c r="I9">
-        <v>1.7104066956493162E-4</v>
+        <v>0.00017323385416625711</v>
       </c>
       <c r="J9">
-        <v>9.4388770424811905E-3</v>
+        <v>0.0094726972888608402</v>
       </c>
       <c r="K9">
-        <v>5.5569331545706271E-4</v>
+        <v>0.00055446553573004938</v>
       </c>
       <c r="L9">
-        <v>-2.5102359203569794E-3</v>
+        <v>-0.0025537194954028033</v>
       </c>
       <c r="M9">
-        <v>1.6607121125292862E-4</v>
+        <v>0.00016111343245355479</v>
       </c>
       <c r="N9">
-        <v>-7.3395784211771013E-5</v>
+        <v>-7.4953509943312836e-05</v>
       </c>
       <c r="O9">
-        <v>-7.098638285532935E-5</v>
+        <v>-8.069450533138272e-05</v>
       </c>
       <c r="P9">
-        <v>-2.3381371213415658E-4</v>
+        <v>-0.00024359716547673986</v>
       </c>
       <c r="Q9">
-        <v>-3.6123510642958163E-4</v>
+        <v>-0.00035756523214562413</v>
       </c>
       <c r="R9">
-        <v>-7.1843000749185126E-4</v>
+        <v>-0.00071582114080738501</v>
       </c>
       <c r="S9">
-        <v>7.6959633285667885E-4</v>
+        <v>0.00076257837387564906</v>
       </c>
       <c r="T9">
-        <v>4.6056870370207292E-4</v>
+        <v>0.00046231032399435181</v>
       </c>
       <c r="U9">
-        <v>-9.9701994357434716E-5</v>
+        <v>-0.00010241931413974663</v>
       </c>
       <c r="V9">
-        <v>-1.8217420460480294E-4</v>
+        <v>-0.00018834946243690125</v>
       </c>
       <c r="W9">
-        <v>-1.6400049026041308E-4</v>
+        <v>-0.00016381393113066439</v>
       </c>
       <c r="X9">
-        <v>-1.4747596137238556E-4</v>
+        <v>-0.00014575261442900667</v>
       </c>
       <c r="Y9">
-        <v>-2.8842142467410542E-5</v>
+        <v>-2.5493468178346482e-05</v>
       </c>
       <c r="Z9">
-        <v>-1.4158238213639318E-4</v>
+        <v>-0.00014083786234840579</v>
       </c>
       <c r="AA9">
-        <v>3.8227683195932172E-5</v>
+        <v>3.9493979859681061e-05</v>
       </c>
       <c r="AB9">
-        <v>2.333301139561747E-5</v>
+        <v>2.4788358628582974e-05</v>
       </c>
       <c r="AC9">
-        <v>3.1534090340889229E-5</v>
+        <v>3.1386323548112727e-05</v>
       </c>
       <c r="AD9">
-        <v>1.2208290770163513E-4</v>
+        <v>0.00012509085884941304</v>
       </c>
       <c r="AE9">
-        <v>8.8173611989782186E-6</v>
+        <v>8.0769061200705594e-06</v>
       </c>
       <c r="AF9">
-        <v>-8.0972410481051138E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.080769256865265038</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>35</v>
       </c>
       <c r="B10">
-        <v>0.27838996416079476</v>
+        <v>0.27200824663036932</v>
       </c>
       <c r="C10">
-        <v>6.6123127470460355E-4</v>
+        <v>0.00067192034012660711</v>
       </c>
       <c r="D10">
-        <v>-1.0827520633596363E-4</v>
+        <v>-0.0001140924911570999</v>
       </c>
       <c r="E10">
-        <v>7.5152924264724531E-7</v>
+        <v>7.9479329864851176e-07</v>
       </c>
       <c r="F10">
-        <v>3.9967890983191867E-5</v>
+        <v>4.740363584776041e-05</v>
       </c>
       <c r="G10">
-        <v>3.3980678954891735E-5</v>
+        <v>3.9048066701328349e-05</v>
       </c>
       <c r="H10">
-        <v>-9.5817491673552506E-5</v>
+        <v>-9.5103633714389681e-05</v>
       </c>
       <c r="I10">
-        <v>-1.4644758320911014E-4</v>
+        <v>-0.000144062768578621</v>
       </c>
       <c r="J10">
-        <v>5.5569331545706271E-4</v>
+        <v>0.00055446553573004938</v>
       </c>
       <c r="K10">
-        <v>2.1791906095711203E-3</v>
+        <v>0.0022017250654415136</v>
       </c>
       <c r="L10">
-        <v>-9.3390791806195837E-4</v>
+        <v>-0.00093634912879443622</v>
       </c>
       <c r="M10">
-        <v>9.2049353282732467E-5</v>
+        <v>8.9580757145953159e-05</v>
       </c>
       <c r="N10">
-        <v>7.0151635845918021E-4</v>
+        <v>0.00070411770135952664</v>
       </c>
       <c r="O10">
-        <v>1.3125258090180498E-3</v>
+        <v>0.0013278299385835963</v>
       </c>
       <c r="P10">
-        <v>1.3115516340900695E-3</v>
+        <v>0.0013321691137982289</v>
       </c>
       <c r="Q10">
-        <v>-7.9344262078678395E-4</v>
+        <v>-0.00079985212899195111</v>
       </c>
       <c r="R10">
-        <v>1.6357534692175877E-4</v>
+        <v>0.0001707997183665266</v>
       </c>
       <c r="S10">
-        <v>-3.1190163130372849E-4</v>
+        <v>-0.00031785303535177239</v>
       </c>
       <c r="T10">
-        <v>-8.7108686529680239E-5</v>
+        <v>-9.2110215636964703e-05</v>
       </c>
       <c r="U10">
-        <v>3.5376683292267808E-4</v>
+        <v>0.00035782205994734059</v>
       </c>
       <c r="V10">
-        <v>-4.6484309492659213E-5</v>
+        <v>-5.2737730712387482e-05</v>
       </c>
       <c r="W10">
-        <v>-2.0626614274486159E-4</v>
+        <v>-0.00021306693517389192</v>
       </c>
       <c r="X10">
-        <v>-2.9102294568792721E-4</v>
+        <v>-0.00029825124602073073</v>
       </c>
       <c r="Y10">
-        <v>-2.6567098142122941E-4</v>
+        <v>-0.00027577310138109194</v>
       </c>
       <c r="Z10">
-        <v>-2.5171508452830624E-4</v>
+        <v>-0.00025726902001886706</v>
       </c>
       <c r="AA10">
-        <v>-1.951670658954595E-4</v>
+        <v>-0.00020468450235596668</v>
       </c>
       <c r="AB10">
-        <v>-3.5260073014265619E-4</v>
+        <v>-0.00035659743215211309</v>
       </c>
       <c r="AC10">
-        <v>1.0821262241786595E-5</v>
+        <v>1.0842317350978006e-05</v>
       </c>
       <c r="AD10">
-        <v>3.6093097805065867E-5</v>
+        <v>3.7954302363365014e-05</v>
       </c>
       <c r="AE10">
-        <v>3.9237592265942796E-5</v>
+        <v>4.5256783722280461e-05</v>
       </c>
       <c r="AF10">
-        <v>1.5604631246996618E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+        <v>0.0017261773402181477</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>51</v>
       </c>
       <c r="B11">
-        <v>-0.73159263351476467</v>
+        <v>-0.72717450101041925</v>
       </c>
       <c r="C11">
-        <v>-4.8913121880072967E-5</v>
+        <v>-5.5264151413928235e-05</v>
       </c>
       <c r="D11">
-        <v>6.2770874967373914E-4</v>
+        <v>0.00062055094659239918</v>
       </c>
       <c r="E11">
-        <v>-5.0196387272318454E-6</v>
+        <v>-4.9540706792555056e-06</v>
       </c>
       <c r="F11">
-        <v>2.3842254359761166E-4</v>
+        <v>0.00026270942905487656</v>
       </c>
       <c r="G11">
-        <v>1.0631622524553269E-6</v>
+        <v>2.0221421931344852e-05</v>
       </c>
       <c r="H11">
-        <v>-7.6062093547468929E-5</v>
+        <v>-8.1295309240372621e-05</v>
       </c>
       <c r="I11">
-        <v>-2.7988680859991437E-5</v>
+        <v>-3.2436912576122036e-05</v>
       </c>
       <c r="J11">
-        <v>-2.5102359203569794E-3</v>
+        <v>-0.0025537194954028033</v>
       </c>
       <c r="K11">
-        <v>-9.3390791806195837E-4</v>
+        <v>-0.00093634912879443622</v>
       </c>
       <c r="L11">
-        <v>4.1356211281798772E-3</v>
+        <v>0.0041568244180113607</v>
       </c>
       <c r="M11">
-        <v>3.6232436102933037E-6</v>
+        <v>3.5213640171274582e-07</v>
       </c>
       <c r="N11">
-        <v>1.1971662893532989E-4</v>
+        <v>0.00011587667299776277</v>
       </c>
       <c r="O11">
-        <v>1.505653018209651E-4</v>
+        <v>0.00014951204298983519</v>
       </c>
       <c r="P11">
-        <v>2.4873667104816739E-4</v>
+        <v>0.00024925095793545667</v>
       </c>
       <c r="Q11">
-        <v>2.0245654437918447E-4</v>
+        <v>0.00020027401010320133</v>
       </c>
       <c r="R11">
-        <v>-4.2244178030889353E-4</v>
+        <v>-0.0004237939970053858</v>
       </c>
       <c r="S11">
-        <v>8.1219011060027499E-4</v>
+        <v>0.00081028288590552933</v>
       </c>
       <c r="T11">
-        <v>3.3389148418677141E-4</v>
+        <v>0.00032689911605012553</v>
       </c>
       <c r="U11">
-        <v>1.5073419211822446E-4</v>
+        <v>0.00015348961065671815</v>
       </c>
       <c r="V11">
-        <v>9.0337666218841175E-5</v>
+        <v>9.8776575788613041e-05</v>
       </c>
       <c r="W11">
-        <v>6.7893106911379349E-5</v>
+        <v>6.9235447544693969e-05</v>
       </c>
       <c r="X11">
-        <v>9.1786741238915684E-6</v>
+        <v>9.1627549761077315e-06</v>
       </c>
       <c r="Y11">
-        <v>-2.4033414581407526E-5</v>
+        <v>-2.8121862879063649e-05</v>
       </c>
       <c r="Z11">
-        <v>3.194206417965386E-5</v>
+        <v>3.1790154372651237e-05</v>
       </c>
       <c r="AA11">
-        <v>2.1387047368748562E-5</v>
+        <v>2.1090592946311926e-05</v>
       </c>
       <c r="AB11">
-        <v>1.6773148791221059E-4</v>
+        <v>0.00016642399232355033</v>
       </c>
       <c r="AC11">
-        <v>1.338068976918949E-5</v>
+        <v>1.314740851867121e-05</v>
       </c>
       <c r="AD11">
-        <v>-4.2790836759010187E-5</v>
+        <v>-4.5823475039459549e-05</v>
       </c>
       <c r="AE11">
-        <v>-6.2428390317280889E-5</v>
+        <v>-6.054863791288452e-05</v>
       </c>
       <c r="AF11">
-        <v>-1.9576070744094703E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.019370287991933549</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>36</v>
       </c>
       <c r="B12">
-        <v>4.5004152394663557E-2</v>
+        <v>0.049400264258032095</v>
       </c>
       <c r="C12">
-        <v>6.0159217809408101E-5</v>
+        <v>6.3376609343299421e-05</v>
       </c>
       <c r="D12">
-        <v>9.6512158729210318E-5</v>
+        <v>9.743625964996061e-05</v>
       </c>
       <c r="E12">
-        <v>-8.7456991016698362E-7</v>
+        <v>-8.7934830508124527e-07</v>
       </c>
       <c r="F12">
-        <v>-1.6210494769831538E-4</v>
+        <v>-0.00015861172431358601</v>
       </c>
       <c r="G12">
-        <v>-8.7598100233475529E-5</v>
+        <v>-8.2928563362002355e-05</v>
       </c>
       <c r="H12">
-        <v>-5.3617857572944134E-6</v>
+        <v>-1.3546435051658675e-05</v>
       </c>
       <c r="I12">
-        <v>3.6893921217557126E-5</v>
+        <v>3.8066225333145058e-05</v>
       </c>
       <c r="J12">
-        <v>1.6607121125292862E-4</v>
+        <v>0.00016111343245355479</v>
       </c>
       <c r="K12">
-        <v>9.2049353282732467E-5</v>
+        <v>8.9580757145953159e-05</v>
       </c>
       <c r="L12">
-        <v>3.6232436102933037E-6</v>
+        <v>3.5213640171274582e-07</v>
       </c>
       <c r="M12">
-        <v>1.6622718457168252E-3</v>
+        <v>0.0016711040755378222</v>
       </c>
       <c r="N12">
-        <v>8.2511256477257931E-4</v>
+        <v>0.00082409242376665654</v>
       </c>
       <c r="O12">
-        <v>8.475390906643827E-4</v>
+        <v>0.00084523579652855227</v>
       </c>
       <c r="P12">
-        <v>8.6181643411142026E-4</v>
+        <v>0.00086069528110890934</v>
       </c>
       <c r="Q12">
-        <v>-2.4454183319798611E-5</v>
+        <v>1.1512930187278014e-06</v>
       </c>
       <c r="R12">
-        <v>-4.6234290833055967E-5</v>
+        <v>-5.191262028410125e-05</v>
       </c>
       <c r="S12">
-        <v>7.1503245069130675E-5</v>
+        <v>7.419441091697631e-05</v>
       </c>
       <c r="T12">
-        <v>4.7584987379977188E-5</v>
+        <v>4.850505315233633e-05</v>
       </c>
       <c r="U12">
-        <v>5.6004843837205204E-5</v>
+        <v>5.9456746988825892e-05</v>
       </c>
       <c r="V12">
-        <v>7.7953104558420858E-5</v>
+        <v>6.8905589753293501e-05</v>
       </c>
       <c r="W12">
-        <v>-1.4442909588583091E-4</v>
+        <v>-0.00014480504307785944</v>
       </c>
       <c r="X12">
-        <v>-1.0044767566196326E-4</v>
+        <v>-9.7156749001770697e-05</v>
       </c>
       <c r="Y12">
-        <v>-1.2464882319047031E-4</v>
+        <v>-0.00010555819433444882</v>
       </c>
       <c r="Z12">
-        <v>-9.1092954269858745E-5</v>
+        <v>-8.8108133419343001e-05</v>
       </c>
       <c r="AA12">
-        <v>-1.3600591306319029E-4</v>
+        <v>-0.00013608889006057784</v>
       </c>
       <c r="AB12">
-        <v>-3.7767557070671242E-5</v>
+        <v>-4.2360719535237783e-05</v>
       </c>
       <c r="AC12">
-        <v>1.0084306560428356E-5</v>
+        <v>1.0680174898978e-05</v>
       </c>
       <c r="AD12">
-        <v>-6.3177250266289336E-5</v>
+        <v>-6.5824493005430342e-05</v>
       </c>
       <c r="AE12">
-        <v>-1.0207168516141178E-5</v>
+        <v>-1.6012190147301694e-05</v>
       </c>
       <c r="AF12">
-        <v>-3.6488735544846183E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.0037011640693166287</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>37</v>
       </c>
       <c r="B13">
-        <v>6.6195445378885109E-2</v>
+        <v>0.059970413388445637</v>
       </c>
       <c r="C13">
-        <v>7.9045820025245081E-5</v>
+        <v>7.2253227151967227e-05</v>
       </c>
       <c r="D13">
-        <v>-1.3184482315622015E-4</v>
+        <v>-0.00013868008304897435</v>
       </c>
       <c r="E13">
-        <v>9.9457475663084313E-7</v>
+        <v>1.0473007521171212e-06</v>
       </c>
       <c r="F13">
-        <v>-1.0757101683266101E-5</v>
+        <v>-1.8455124347368894e-06</v>
       </c>
       <c r="G13">
-        <v>6.6364127081302259E-5</v>
+        <v>7.4911270605472913e-05</v>
       </c>
       <c r="H13">
-        <v>-2.4116853083533811E-5</v>
+        <v>-3.6619191247162397e-05</v>
       </c>
       <c r="I13">
-        <v>8.2605719810949547E-5</v>
+        <v>7.2676990231244774e-05</v>
       </c>
       <c r="J13">
-        <v>-7.3395784211771013E-5</v>
+        <v>-7.4953509943312836e-05</v>
       </c>
       <c r="K13">
-        <v>7.0151635845918021E-4</v>
+        <v>0.00070411770135952664</v>
       </c>
       <c r="L13">
-        <v>1.1971662893532989E-4</v>
+        <v>0.00011587667299776277</v>
       </c>
       <c r="M13">
-        <v>8.2511256477257931E-4</v>
+        <v>0.00082409242376665654</v>
       </c>
       <c r="N13">
-        <v>1.9377806896897719E-3</v>
+        <v>0.001930946687596287</v>
       </c>
       <c r="O13">
-        <v>1.5878241110124573E-3</v>
+        <v>0.0015890593102673945</v>
       </c>
       <c r="P13">
-        <v>1.6971493001531265E-3</v>
+        <v>0.0016995858073487744</v>
       </c>
       <c r="Q13">
-        <v>-9.2968393790273808E-5</v>
+        <v>-0.00010933891157100732</v>
       </c>
       <c r="R13">
-        <v>-2.4854932899001718E-5</v>
+        <v>-2.8274344098533312e-05</v>
       </c>
       <c r="S13">
-        <v>-2.2702103437804316E-5</v>
+        <v>-2.8897883260571946e-05</v>
       </c>
       <c r="T13">
-        <v>2.1865485366483043E-5</v>
+        <v>2.330254805124523e-05</v>
       </c>
       <c r="U13">
-        <v>4.5167361398785219E-4</v>
+        <v>0.00045966266149689638</v>
       </c>
       <c r="V13">
-        <v>1.5002552897824662E-4</v>
+        <v>0.00015662739175361225</v>
       </c>
       <c r="W13">
-        <v>-2.1996446149501973E-4</v>
+        <v>-0.00022541981049799915</v>
       </c>
       <c r="X13">
-        <v>-2.4244449458122675E-4</v>
+        <v>-0.00024939586751726757</v>
       </c>
       <c r="Y13">
-        <v>-2.9083518978950033E-4</v>
+        <v>-0.00031920227166225854</v>
       </c>
       <c r="Z13">
-        <v>-2.4887505658916865E-4</v>
+        <v>-0.00025524503412832503</v>
       </c>
       <c r="AA13">
-        <v>-2.8005638457713684E-4</v>
+        <v>-0.00028614519125218403</v>
       </c>
       <c r="AB13">
-        <v>-2.0339001972587178E-4</v>
+        <v>-0.00020670251566448032</v>
       </c>
       <c r="AC13">
-        <v>1.4648079613180153E-5</v>
+        <v>1.4337837120798419e-05</v>
       </c>
       <c r="AD13">
-        <v>-1.5044552863043405E-5</v>
+        <v>-9.7963643587656649e-06</v>
       </c>
       <c r="AE13">
-        <v>1.6109562603758331E-5</v>
+        <v>2.2381727130647063e-05</v>
       </c>
       <c r="AF13">
-        <v>2.2789462033859474E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.0025178687532631493</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>38</v>
       </c>
       <c r="B14">
-        <v>7.2682851392894932E-2</v>
+        <v>0.068914556275380304</v>
       </c>
       <c r="C14">
-        <v>1.1942233552537671E-4</v>
+        <v>0.00012306410155555125</v>
       </c>
       <c r="D14">
-        <v>-8.1319415389565462E-5</v>
+        <v>-8.2348075255332664e-05</v>
       </c>
       <c r="E14">
-        <v>6.0846141394254764E-7</v>
+        <v>6.1753067167807994e-07</v>
       </c>
       <c r="F14">
-        <v>-2.5411319357183416E-5</v>
+        <v>-1.3024006284469841e-05</v>
       </c>
       <c r="G14">
-        <v>2.8065530651967974E-5</v>
+        <v>3.391273410147241e-05</v>
       </c>
       <c r="H14">
-        <v>-4.6698585106363228E-5</v>
+        <v>-5.3826335131041146e-05</v>
       </c>
       <c r="I14">
-        <v>1.2999567124037076E-4</v>
+        <v>0.00012747658642246615</v>
       </c>
       <c r="J14">
-        <v>-7.098638285532935E-5</v>
+        <v>-8.069450533138272e-05</v>
       </c>
       <c r="K14">
-        <v>1.3125258090180498E-3</v>
+        <v>0.0013278299385835963</v>
       </c>
       <c r="L14">
-        <v>1.505653018209651E-4</v>
+        <v>0.00014951204298983519</v>
       </c>
       <c r="M14">
-        <v>8.475390906643827E-4</v>
+        <v>0.00084523579652855227</v>
       </c>
       <c r="N14">
-        <v>1.5878241110124573E-3</v>
+        <v>0.0015890593102673945</v>
       </c>
       <c r="O14">
-        <v>3.3253740814743367E-3</v>
+        <v>0.0033296051842277427</v>
       </c>
       <c r="P14">
-        <v>2.6192812688955011E-3</v>
+        <v>0.00262828609101411</v>
       </c>
       <c r="Q14">
-        <v>-5.9622122030124049E-5</v>
+        <v>-5.3956917345100106e-05</v>
       </c>
       <c r="R14">
-        <v>8.2890003315921635E-5</v>
+        <v>8.9402183421727279e-05</v>
       </c>
       <c r="S14">
-        <v>1.4186033712839091E-4</v>
+        <v>0.00012605306390692564</v>
       </c>
       <c r="T14">
-        <v>2.1820419236548286E-5</v>
+        <v>1.5271071988872135e-05</v>
       </c>
       <c r="U14">
-        <v>9.190654310700431E-4</v>
+        <v>0.00091635133455737522</v>
       </c>
       <c r="V14">
-        <v>7.6340792777190511E-5</v>
+        <v>7.7682110722580009e-05</v>
       </c>
       <c r="W14">
-        <v>-2.5105798887131714E-4</v>
+        <v>-0.00025560892682803668</v>
       </c>
       <c r="X14">
-        <v>-3.2623527497734495E-4</v>
+        <v>-0.00032977357493683838</v>
       </c>
       <c r="Y14">
-        <v>-3.361037257944504E-4</v>
+        <v>-0.00033304066341063876</v>
       </c>
       <c r="Z14">
-        <v>-2.1536049324493009E-4</v>
+        <v>-0.00021799358574065312</v>
       </c>
       <c r="AA14">
-        <v>-3.4239409481394325E-4</v>
+        <v>-0.00035005495749521769</v>
       </c>
       <c r="AB14">
-        <v>-2.1777243440040928E-4</v>
+        <v>-0.00022060929938164369</v>
       </c>
       <c r="AC14">
-        <v>3.0603459678323622E-5</v>
+        <v>3.0811572730141105e-05</v>
       </c>
       <c r="AD14">
-        <v>-7.6728373431216371E-5</v>
+        <v>-7.2283144237423463e-05</v>
       </c>
       <c r="AE14">
-        <v>-6.0861654323060739E-5</v>
+        <v>-5.7626272148701219e-05</v>
       </c>
       <c r="AF14">
-        <v>-8.2375056725186857E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.00080772888074353427</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>39</v>
       </c>
       <c r="B15">
-        <v>0.15058340100915391</v>
+        <v>0.14728245983137547</v>
       </c>
       <c r="C15">
-        <v>1.1547551740743927E-4</v>
+        <v>0.00011944305151244749</v>
       </c>
       <c r="D15">
-        <v>-1.8703019726721941E-4</v>
+        <v>-0.00018815207593221584</v>
       </c>
       <c r="E15">
-        <v>1.4432278013997931E-6</v>
+        <v>1.4512987421101616e-06</v>
       </c>
       <c r="F15">
-        <v>1.2613560276452523E-4</v>
+        <v>0.00013804361536214841</v>
       </c>
       <c r="G15">
-        <v>1.5498686885990869E-4</v>
+        <v>0.00016224229690828349</v>
       </c>
       <c r="H15">
-        <v>3.3649144332574543E-4</v>
+        <v>0.00032937712331470036</v>
       </c>
       <c r="I15">
-        <v>5.6161171625847804E-4</v>
+        <v>0.00056089991394867934</v>
       </c>
       <c r="J15">
-        <v>-2.3381371213415658E-4</v>
+        <v>-0.00024359716547673986</v>
       </c>
       <c r="K15">
-        <v>1.3115516340900695E-3</v>
+        <v>0.0013321691137982289</v>
       </c>
       <c r="L15">
-        <v>2.4873667104816739E-4</v>
+        <v>0.00024925095793545667</v>
       </c>
       <c r="M15">
-        <v>8.6181643411142026E-4</v>
+        <v>0.00086069528110890934</v>
       </c>
       <c r="N15">
-        <v>1.6971493001531265E-3</v>
+        <v>0.0016995858073487744</v>
       </c>
       <c r="O15">
-        <v>2.6192812688955011E-3</v>
+        <v>0.00262828609101411</v>
       </c>
       <c r="P15">
-        <v>3.6861282889782644E-3</v>
+        <v>0.0037043000453118712</v>
       </c>
       <c r="Q15">
-        <v>2.4060358673338626E-5</v>
+        <v>3.1845082331902896e-05</v>
       </c>
       <c r="R15">
-        <v>5.7202121184093968E-5</v>
+        <v>6.1248027905150162e-05</v>
       </c>
       <c r="S15">
-        <v>3.7473955108548998E-5</v>
+        <v>2.5580219986078706e-05</v>
       </c>
       <c r="T15">
-        <v>1.348479476101028E-5</v>
+        <v>8.0810875356669264e-06</v>
       </c>
       <c r="U15">
-        <v>1.1281194748449643E-3</v>
+        <v>0.001135681022588332</v>
       </c>
       <c r="V15">
-        <v>2.3381858180763701E-5</v>
+        <v>2.1632373059275148e-05</v>
       </c>
       <c r="W15">
-        <v>-1.8873634597326491E-4</v>
+        <v>-0.00019360938088171676</v>
       </c>
       <c r="X15">
-        <v>-4.0550502924804237E-4</v>
+        <v>-0.000408633699926878</v>
       </c>
       <c r="Y15">
-        <v>-3.4081909917388657E-4</v>
+        <v>-0.00033592062871086231</v>
       </c>
       <c r="Z15">
-        <v>-1.9405216603030507E-4</v>
+        <v>-0.00019773426821799011</v>
       </c>
       <c r="AA15">
-        <v>-3.2387872231870365E-4</v>
+        <v>-0.00033125111374295436</v>
       </c>
       <c r="AB15">
-        <v>-1.5439345875577432E-4</v>
+        <v>-0.00015752425869476182</v>
       </c>
       <c r="AC15">
-        <v>2.8749809877302813E-5</v>
+        <v>2.9230857368788741e-05</v>
       </c>
       <c r="AD15">
-        <v>-6.9070441358058026E-5</v>
+        <v>-6.7643239154849613e-05</v>
       </c>
       <c r="AE15">
-        <v>7.8556709443727314E-6</v>
+        <v>1.0583718424814204e-05</v>
       </c>
       <c r="AF15">
-        <v>1.8947356936218698E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.0019005430719428174</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>40</v>
       </c>
       <c r="B16">
-        <v>0.69699352119333824</v>
+        <v>0.69803088774179789</v>
       </c>
       <c r="C16">
-        <v>-4.2326165195228981E-4</v>
+        <v>-0.0004304664801795211</v>
       </c>
       <c r="D16">
-        <v>-2.0887139217288945E-4</v>
+        <v>-0.00020996914975170578</v>
       </c>
       <c r="E16">
-        <v>1.8094565872085687E-6</v>
+        <v>1.815238254891526e-06</v>
       </c>
       <c r="F16">
-        <v>1.7638354082061833E-4</v>
+        <v>0.00017524345245878035</v>
       </c>
       <c r="G16">
-        <v>1.7383092497874272E-4</v>
+        <v>0.00017314373404284838</v>
       </c>
       <c r="H16">
-        <v>5.6744577319602142E-5</v>
+        <v>5.7323925649828976e-05</v>
       </c>
       <c r="I16">
-        <v>1.3745747940808854E-5</v>
+        <v>1.1374371667580843e-05</v>
       </c>
       <c r="J16">
-        <v>-3.6123510642958163E-4</v>
+        <v>-0.00035756523214562413</v>
       </c>
       <c r="K16">
-        <v>-7.9344262078678395E-4</v>
+        <v>-0.00079985212899195111</v>
       </c>
       <c r="L16">
-        <v>2.0245654437918447E-4</v>
+        <v>0.00020027401010320133</v>
       </c>
       <c r="M16">
-        <v>-2.4454183319798611E-5</v>
+        <v>1.1512930187278014e-06</v>
       </c>
       <c r="N16">
-        <v>-9.2968393790273808E-5</v>
+        <v>-0.00010933891157100732</v>
       </c>
       <c r="O16">
-        <v>-5.9622122030124049E-5</v>
+        <v>-5.3956917345100106e-05</v>
       </c>
       <c r="P16">
-        <v>2.4060358673338626E-5</v>
+        <v>3.1845082331902896e-05</v>
       </c>
       <c r="Q16">
-        <v>2.0263887279008746E-3</v>
+        <v>0.0020259902417982829</v>
       </c>
       <c r="R16">
-        <v>6.5070232064915541E-5</v>
+        <v>5.0357304871505312e-05</v>
       </c>
       <c r="S16">
-        <v>-2.8370685089056883E-6</v>
+        <v>9.1110886142210649e-07</v>
       </c>
       <c r="T16">
-        <v>9.4704023656464191E-6</v>
+        <v>1.2656887202439921e-05</v>
       </c>
       <c r="U16">
-        <v>5.9004889913628268E-5</v>
+        <v>8.6948584701602018e-05</v>
       </c>
       <c r="V16">
-        <v>-2.9070223405364387E-4</v>
+        <v>-0.00029781696480303527</v>
       </c>
       <c r="W16">
-        <v>3.1426355071809928E-4</v>
+        <v>0.00031492359892058109</v>
       </c>
       <c r="X16">
-        <v>3.0083896246165551E-4</v>
+        <v>0.00030144872498486251</v>
       </c>
       <c r="Y16">
-        <v>4.0775648551883732E-4</v>
+        <v>0.00040497829225931344</v>
       </c>
       <c r="Z16">
-        <v>4.3272826800487568E-4</v>
+        <v>0.00043205366228518563</v>
       </c>
       <c r="AA16">
-        <v>2.2044725784620933E-4</v>
+        <v>0.00022140635943298018</v>
       </c>
       <c r="AB16">
-        <v>3.0965431843519556E-4</v>
+        <v>0.00030722955467435512</v>
       </c>
       <c r="AC16">
-        <v>-2.8648510659164898E-6</v>
+        <v>-2.6593947574513934e-06</v>
       </c>
       <c r="AD16">
-        <v>-5.9196877903071657E-5</v>
+        <v>-5.7126805712021767e-05</v>
       </c>
       <c r="AE16">
-        <v>-2.0531197943280403E-5</v>
+        <v>-2.0966339689480106e-05</v>
       </c>
       <c r="AF16">
-        <v>6.096500656888419E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.0061292056521188437</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>52</v>
       </c>
       <c r="B17">
-        <v>-0.18001015393793976</v>
+        <v>-0.18229250873151123</v>
       </c>
       <c r="C17">
-        <v>6.7479034677417641E-4</v>
+        <v>0.00067577935592695029</v>
       </c>
       <c r="D17">
-        <v>3.3549961559651859E-4</v>
+        <v>0.00033289755269206873</v>
       </c>
       <c r="E17">
-        <v>-3.0130221747405795E-6</v>
+        <v>-2.9924091113209866e-06</v>
       </c>
       <c r="F17">
-        <v>5.334614974869048E-4</v>
+        <v>0.00053400536797941749</v>
       </c>
       <c r="G17">
-        <v>3.9766183659994004E-4</v>
+        <v>0.00039700539379843199</v>
       </c>
       <c r="H17">
-        <v>2.7001880979072185E-5</v>
+        <v>2.5648343674877696e-05</v>
       </c>
       <c r="I17">
-        <v>-5.0477405441336413E-5</v>
+        <v>-5.4935247828751853e-05</v>
       </c>
       <c r="J17">
-        <v>-7.1843000749185126E-4</v>
+        <v>-0.00071582114080738501</v>
       </c>
       <c r="K17">
-        <v>1.6357534692175877E-4</v>
+        <v>0.0001707997183665266</v>
       </c>
       <c r="L17">
-        <v>-4.2244178030889353E-4</v>
+        <v>-0.0004237939970053858</v>
       </c>
       <c r="M17">
-        <v>-4.6234290833055967E-5</v>
+        <v>-5.191262028410125e-05</v>
       </c>
       <c r="N17">
-        <v>-2.4854932899001718E-5</v>
+        <v>-2.8274344098533312e-05</v>
       </c>
       <c r="O17">
-        <v>8.2890003315921635E-5</v>
+        <v>8.9402183421727279e-05</v>
       </c>
       <c r="P17">
-        <v>5.7202121184093968E-5</v>
+        <v>6.1248027905150162e-05</v>
       </c>
       <c r="Q17">
-        <v>6.5070232064915541E-5</v>
+        <v>5.0357304871505312e-05</v>
       </c>
       <c r="R17">
-        <v>2.7652518618685278E-3</v>
+        <v>0.0027633311103181148</v>
       </c>
       <c r="S17">
-        <v>-1.7887970744277814E-3</v>
+        <v>-0.0017872572625979332</v>
       </c>
       <c r="T17">
-        <v>-1.5953009365758301E-3</v>
+        <v>-0.0015936248542220799</v>
       </c>
       <c r="U17">
-        <v>-3.4638816861697649E-4</v>
+        <v>-0.00034012933048021101</v>
       </c>
       <c r="V17">
-        <v>3.883545172748969E-4</v>
+        <v>0.00039001561730967913</v>
       </c>
       <c r="W17">
-        <v>1.2121926822444319E-4</v>
+        <v>0.00012330061968069284</v>
       </c>
       <c r="X17">
-        <v>3.4437390712475403E-5</v>
+        <v>3.4910606329982726e-05</v>
       </c>
       <c r="Y17">
-        <v>1.467512952495688E-4</v>
+        <v>0.00013395084720729811</v>
       </c>
       <c r="Z17">
-        <v>1.2784028704198366E-4</v>
+        <v>0.00012927734252676619</v>
       </c>
       <c r="AA17">
-        <v>1.192564933582504E-4</v>
+        <v>0.00012053453456526667</v>
       </c>
       <c r="AB17">
-        <v>1.3048039836500384E-4</v>
+        <v>0.00013212833064750202</v>
       </c>
       <c r="AC17">
-        <v>1.0884319646008893E-8</v>
+        <v>-2.0774248674817054e-07</v>
       </c>
       <c r="AD17">
-        <v>6.0972931589001102E-5</v>
+        <v>6.4294158556674631e-05</v>
       </c>
       <c r="AE17">
-        <v>8.481826988177444E-5</v>
+        <v>8.7029099143565505e-05</v>
       </c>
       <c r="AF17">
-        <v>-9.9367354861983545E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.0098559102980137897</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>53</v>
       </c>
       <c r="B18">
-        <v>0.20230510212742045</v>
+        <v>0.20375411848970454</v>
       </c>
       <c r="C18">
-        <v>-2.9874274436318573E-4</v>
+        <v>-0.00029915017580784423</v>
       </c>
       <c r="D18">
-        <v>-2.1927914050563421E-4</v>
+        <v>-0.00021995960783803559</v>
       </c>
       <c r="E18">
-        <v>1.6623732069506259E-6</v>
+        <v>1.6700638034189311e-06</v>
       </c>
       <c r="F18">
-        <v>-1.0446205190958319E-3</v>
+        <v>-0.0010393606857251846</v>
       </c>
       <c r="G18">
-        <v>-9.321461225941137E-4</v>
+        <v>-0.0009275583334300494</v>
       </c>
       <c r="H18">
-        <v>-3.5516595288080091E-5</v>
+        <v>-3.5678958558918146e-05</v>
       </c>
       <c r="I18">
-        <v>1.1539642106720392E-4</v>
+        <v>0.00011524221577113863</v>
       </c>
       <c r="J18">
-        <v>7.6959633285667885E-4</v>
+        <v>0.00076257837387564906</v>
       </c>
       <c r="K18">
-        <v>-3.1190163130372849E-4</v>
+        <v>-0.00031785303535177239</v>
       </c>
       <c r="L18">
-        <v>8.1219011060027499E-4</v>
+        <v>0.00081028288590552933</v>
       </c>
       <c r="M18">
-        <v>7.1503245069130675E-5</v>
+        <v>7.419441091697631e-05</v>
       </c>
       <c r="N18">
-        <v>-2.2702103437804316E-5</v>
+        <v>-2.8897883260571946e-05</v>
       </c>
       <c r="O18">
-        <v>1.4186033712839091E-4</v>
+        <v>0.00012605306390692564</v>
       </c>
       <c r="P18">
-        <v>3.7473955108548998E-5</v>
+        <v>2.5580219986078706e-05</v>
       </c>
       <c r="Q18">
-        <v>-2.8370685089056883E-6</v>
+        <v>9.1110886142210649e-07</v>
       </c>
       <c r="R18">
-        <v>-1.7887970744277814E-3</v>
+        <v>-0.0017872572625979332</v>
       </c>
       <c r="S18">
-        <v>6.3400322917872131E-3</v>
+        <v>0.0063333484635232449</v>
       </c>
       <c r="T18">
-        <v>1.423299510050689E-3</v>
+        <v>0.0014207593689299636</v>
       </c>
       <c r="U18">
-        <v>1.0268980970879458E-4</v>
+        <v>9.5699028293673807e-05</v>
       </c>
       <c r="V18">
-        <v>-2.4070265918691553E-4</v>
+        <v>-0.00023987475432397974</v>
       </c>
       <c r="W18">
-        <v>-9.0096142385287167E-5</v>
+        <v>-9.0049024326974494e-05</v>
       </c>
       <c r="X18">
-        <v>-2.3687929021631859E-5</v>
+        <v>-2.2709025556448548e-05</v>
       </c>
       <c r="Y18">
-        <v>9.3603901718592852E-5</v>
+        <v>9.9053596375039184e-05</v>
       </c>
       <c r="Z18">
-        <v>-2.7170147437050388E-5</v>
+        <v>-2.7282799368474192e-05</v>
       </c>
       <c r="AA18">
-        <v>-3.1612628740141854E-5</v>
+        <v>-3.0708333423957231e-05</v>
       </c>
       <c r="AB18">
-        <v>8.5678058381575238E-5</v>
+        <v>8.4614004872416056e-05</v>
       </c>
       <c r="AC18">
-        <v>1.5624033055573806E-5</v>
+        <v>1.5477903807434494e-05</v>
       </c>
       <c r="AD18">
-        <v>-1.7872411875424592E-4</v>
+        <v>-0.00017939898187556685</v>
       </c>
       <c r="AE18">
-        <v>-1.6821745419701769E-4</v>
+        <v>-0.00016849461974473984</v>
       </c>
       <c r="AF18">
-        <v>7.0811416908349023E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.0071112984478000213</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>54</v>
       </c>
       <c r="B19">
-        <v>0.20846442851149286</v>
+        <v>0.21017012045503036</v>
       </c>
       <c r="C19">
-        <v>-1.2882799477750343E-4</v>
+        <v>-0.00013079096663129295</v>
       </c>
       <c r="D19">
-        <v>-4.7693563485250515E-4</v>
+        <v>-0.00047823499328440017</v>
       </c>
       <c r="E19">
-        <v>3.984075981260774E-6</v>
+        <v>3.9955451880267139e-06</v>
       </c>
       <c r="F19">
-        <v>-5.1706008620285709E-4</v>
+        <v>-0.00051582780279432142</v>
       </c>
       <c r="G19">
-        <v>-5.128743988593509E-4</v>
+        <v>-0.00051119961810912502</v>
       </c>
       <c r="H19">
-        <v>3.8815558325247458E-5</v>
+        <v>3.9660197303357147e-05</v>
       </c>
       <c r="I19">
-        <v>6.8919768821180149E-5</v>
+        <v>6.9516077722265042e-05</v>
       </c>
       <c r="J19">
-        <v>4.6056870370207292E-4</v>
+        <v>0.00046231032399435181</v>
       </c>
       <c r="K19">
-        <v>-8.7108686529680239E-5</v>
+        <v>-9.2110215636964703e-05</v>
       </c>
       <c r="L19">
-        <v>3.3389148418677141E-4</v>
+        <v>0.00032689911605012553</v>
       </c>
       <c r="M19">
-        <v>4.7584987379977188E-5</v>
+        <v>4.850505315233633e-05</v>
       </c>
       <c r="N19">
-        <v>2.1865485366483043E-5</v>
+        <v>2.330254805124523e-05</v>
       </c>
       <c r="O19">
-        <v>2.1820419236548286E-5</v>
+        <v>1.5271071988872135e-05</v>
       </c>
       <c r="P19">
-        <v>1.348479476101028E-5</v>
+        <v>8.0810875356669264e-06</v>
       </c>
       <c r="Q19">
-        <v>9.4704023656464191E-6</v>
+        <v>1.2656887202439921e-05</v>
       </c>
       <c r="R19">
-        <v>-1.5953009365758301E-3</v>
+        <v>-0.0015936248542220799</v>
       </c>
       <c r="S19">
-        <v>1.423299510050689E-3</v>
+        <v>0.0014207593689299636</v>
       </c>
       <c r="T19">
-        <v>4.794871695148104E-3</v>
+        <v>0.0047914272595773111</v>
       </c>
       <c r="U19">
-        <v>2.0086170280672914E-5</v>
+        <v>1.5689340871257698e-05</v>
       </c>
       <c r="V19">
-        <v>-1.2204080069225373E-4</v>
+        <v>-0.00012087175611377255</v>
       </c>
       <c r="W19">
-        <v>-4.8482046843859386E-5</v>
+        <v>-4.8268541012239097e-05</v>
       </c>
       <c r="X19">
-        <v>-6.6372444596110233E-5</v>
+        <v>-6.5827260097269316e-05</v>
       </c>
       <c r="Y19">
-        <v>-1.5413901220451406E-4</v>
+        <v>-0.0001517202491255424</v>
       </c>
       <c r="Z19">
-        <v>2.2633020274732615E-5</v>
+        <v>2.3578514321611135e-05</v>
       </c>
       <c r="AA19">
-        <v>-1.2648232008996389E-4</v>
+        <v>-0.00012558882733546472</v>
       </c>
       <c r="AB19">
-        <v>-2.6678346156877066E-5</v>
+        <v>-2.6005312702187013e-05</v>
       </c>
       <c r="AC19">
-        <v>5.5367129802432136E-6</v>
+        <v>5.4575238601470191e-06</v>
       </c>
       <c r="AD19">
-        <v>7.5151238037992826E-5</v>
+        <v>7.3655770240833515e-05</v>
       </c>
       <c r="AE19">
-        <v>-5.1538663644032368E-5</v>
+        <v>-5.18315454336735e-05</v>
       </c>
       <c r="AF19">
-        <v>1.4227122448520785E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.014272363652518577</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>55</v>
       </c>
       <c r="B20">
-        <v>0.10975265556717631</v>
+        <v>0.11224456369542851</v>
       </c>
       <c r="C20">
-        <v>-4.3888650747473957E-5</v>
+        <v>-4.1247832463237971e-05</v>
       </c>
       <c r="D20">
-        <v>-8.7403088317757407E-5</v>
+        <v>-7.9057641188312079e-05</v>
       </c>
       <c r="E20">
-        <v>6.3141847957079455E-7</v>
+        <v>5.6401835505208724e-07</v>
       </c>
       <c r="F20">
-        <v>2.754369199701838E-6</v>
+        <v>1.6490789835040334e-06</v>
       </c>
       <c r="G20">
-        <v>3.5950533332993959E-5</v>
+        <v>3.386821370094089e-05</v>
       </c>
       <c r="H20">
-        <v>-1.5690043718079186E-5</v>
+        <v>-1.4349680073702439e-05</v>
       </c>
       <c r="I20">
-        <v>3.1646010236562169E-6</v>
+        <v>1.1538600167796317e-05</v>
       </c>
       <c r="J20">
-        <v>-9.9701994357434716E-5</v>
+        <v>-0.00010241931413974663</v>
       </c>
       <c r="K20">
-        <v>3.5376683292267808E-4</v>
+        <v>0.00035782205994734059</v>
       </c>
       <c r="L20">
-        <v>1.5073419211822446E-4</v>
+        <v>0.00015348961065671815</v>
       </c>
       <c r="M20">
-        <v>5.6004843837205204E-5</v>
+        <v>5.9456746988825892e-05</v>
       </c>
       <c r="N20">
-        <v>4.5167361398785219E-4</v>
+        <v>0.00045966266149689638</v>
       </c>
       <c r="O20">
-        <v>9.190654310700431E-4</v>
+        <v>0.00091635133455737522</v>
       </c>
       <c r="P20">
-        <v>1.1281194748449643E-3</v>
+        <v>0.001135681022588332</v>
       </c>
       <c r="Q20">
-        <v>5.9004889913628268E-5</v>
+        <v>8.6948584701602018e-05</v>
       </c>
       <c r="R20">
-        <v>-3.4638816861697649E-4</v>
+        <v>-0.00034012933048021101</v>
       </c>
       <c r="S20">
-        <v>1.0268980970879458E-4</v>
+        <v>9.5699028293673807e-05</v>
       </c>
       <c r="T20">
-        <v>2.0086170280672914E-5</v>
+        <v>1.5689340871257698e-05</v>
       </c>
       <c r="U20">
-        <v>1.4338082258748598E-3</v>
+        <v>0.0014338211205016736</v>
       </c>
       <c r="V20">
-        <v>-3.7669489887032356E-4</v>
+        <v>-0.00037894872615133561</v>
       </c>
       <c r="W20">
-        <v>8.6277608255261318E-5</v>
+        <v>8.4941478565882288e-05</v>
       </c>
       <c r="X20">
-        <v>4.6019033076032806E-5</v>
+        <v>4.7126878472075881e-05</v>
       </c>
       <c r="Y20">
-        <v>4.3922389092400556E-5</v>
+        <v>7.4877008986713766e-05</v>
       </c>
       <c r="Z20">
-        <v>1.1918264766500042E-5</v>
+        <v>1.019056184778616e-05</v>
       </c>
       <c r="AA20">
-        <v>2.0337663410299181E-5</v>
+        <v>1.7606702362682643e-05</v>
       </c>
       <c r="AB20">
-        <v>-1.0155547831822251E-5</v>
+        <v>-1.0781277873877463e-05</v>
       </c>
       <c r="AC20">
-        <v>1.9886218302450158E-5</v>
+        <v>2.07578784322191e-05</v>
       </c>
       <c r="AD20">
-        <v>-3.1775308139086621E-5</v>
+        <v>-3.6830218089368353e-05</v>
       </c>
       <c r="AE20">
-        <v>6.0271614670592616E-6</v>
+        <v>2.6466396971980191e-06</v>
       </c>
       <c r="AF20">
-        <v>1.0161438826846517E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.00072251865082669994</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
         <v>56</v>
       </c>
       <c r="B21">
-        <v>-9.5214537267864593E-2</v>
+        <v>-0.097735522386162732</v>
       </c>
       <c r="C21">
-        <v>1.1905073398588788E-4</v>
+        <v>0.00011798726149560331</v>
       </c>
       <c r="D21">
-        <v>-3.9630962419177906E-5</v>
+        <v>-4.1500887747793549e-05</v>
       </c>
       <c r="E21">
-        <v>3.6666186084683935E-7</v>
+        <v>3.8320730658488898e-07</v>
       </c>
       <c r="F21">
-        <v>7.7288522244261734E-5</v>
+        <v>7.9434913196970922e-05</v>
       </c>
       <c r="G21">
-        <v>1.1735735905567344E-4</v>
+        <v>0.00011865074427218607</v>
       </c>
       <c r="H21">
-        <v>5.4984855633013877E-5</v>
+        <v>5.3806148629456879e-05</v>
       </c>
       <c r="I21">
-        <v>-3.3708711019775415E-6</v>
+        <v>-6.4435918452581786e-06</v>
       </c>
       <c r="J21">
-        <v>-1.8217420460480294E-4</v>
+        <v>-0.00018834946243690125</v>
       </c>
       <c r="K21">
-        <v>-4.6484309492659213E-5</v>
+        <v>-5.2737730712387482e-05</v>
       </c>
       <c r="L21">
-        <v>9.0337666218841175E-5</v>
+        <v>9.8776575788613041e-05</v>
       </c>
       <c r="M21">
-        <v>7.7953104558420858E-5</v>
+        <v>6.8905589753293501e-05</v>
       </c>
       <c r="N21">
-        <v>1.5002552897824662E-4</v>
+        <v>0.00015662739175361225</v>
       </c>
       <c r="O21">
-        <v>7.6340792777190511E-5</v>
+        <v>7.7682110722580009e-05</v>
       </c>
       <c r="P21">
-        <v>2.3381858180763701E-5</v>
+        <v>2.1632373059275148e-05</v>
       </c>
       <c r="Q21">
-        <v>-2.9070223405364387E-4</v>
+        <v>-0.00029781696480303527</v>
       </c>
       <c r="R21">
-        <v>3.883545172748969E-4</v>
+        <v>0.00039001561730967913</v>
       </c>
       <c r="S21">
-        <v>-2.4070265918691553E-4</v>
+        <v>-0.00023987475432397974</v>
       </c>
       <c r="T21">
-        <v>-1.2204080069225373E-4</v>
+        <v>-0.00012087175611377255</v>
       </c>
       <c r="U21">
-        <v>-3.7669489887032356E-4</v>
+        <v>-0.00037894872615133561</v>
       </c>
       <c r="V21">
-        <v>4.2159126883528023E-3</v>
+        <v>0.0042177081276283694</v>
       </c>
       <c r="W21">
-        <v>6.6728005251545132E-5</v>
+        <v>6.8948990521042783e-05</v>
       </c>
       <c r="X21">
-        <v>1.5637276049661658E-4</v>
+        <v>0.0001577460642710839</v>
       </c>
       <c r="Y21">
-        <v>1.6367861033354371E-5</v>
+        <v>5.3152765317789606e-06</v>
       </c>
       <c r="Z21">
-        <v>1.2900647662039927E-4</v>
+        <v>0.0001313451766555546</v>
       </c>
       <c r="AA21">
-        <v>4.6779451483714639E-5</v>
+        <v>4.840379574826084e-05</v>
       </c>
       <c r="AB21">
-        <v>6.1309649792859797E-5</v>
+        <v>6.5308869836180249e-05</v>
       </c>
       <c r="AC21">
-        <v>1.2533754994691592E-6</v>
+        <v>8.7929737120875221e-07</v>
       </c>
       <c r="AD21">
-        <v>1.0683123865898217E-5</v>
+        <v>1.3224633977957989e-05</v>
       </c>
       <c r="AE21">
-        <v>-8.60921585123263E-5</v>
+        <v>-8.3977859161524015e-05</v>
       </c>
       <c r="AF21">
-        <v>8.5672300024444877E-4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.0009223747283513958</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
         <v>41</v>
       </c>
       <c r="B22">
-        <v>0.23991662873098082</v>
+        <v>0.23937423757847007</v>
       </c>
       <c r="C22">
-        <v>1.2246231362551363E-4</v>
+        <v>0.0001216580083301035</v>
       </c>
       <c r="D22">
-        <v>-5.6088664379352893E-5</v>
+        <v>-5.6406921666155019e-05</v>
       </c>
       <c r="E22">
-        <v>5.8161907022155884E-7</v>
+        <v>5.8426398834971437e-07</v>
       </c>
       <c r="F22">
-        <v>1.5317646621142156E-4</v>
+        <v>0.00015306238546803491</v>
       </c>
       <c r="G22">
-        <v>5.5624645884946866E-5</v>
+        <v>5.642536678727994e-05</v>
       </c>
       <c r="H22">
-        <v>8.4693385359520821E-5</v>
+        <v>8.5785970736355997e-05</v>
       </c>
       <c r="I22">
-        <v>-1.5199253212248224E-4</v>
+        <v>-0.00015164298821924288</v>
       </c>
       <c r="J22">
-        <v>-1.6400049026041308E-4</v>
+        <v>-0.00016381393113066439</v>
       </c>
       <c r="K22">
-        <v>-2.0626614274486159E-4</v>
+        <v>-0.00021306693517389192</v>
       </c>
       <c r="L22">
-        <v>6.7893106911379349E-5</v>
+        <v>6.9235447544693969e-05</v>
       </c>
       <c r="M22">
-        <v>-1.4442909588583091E-4</v>
+        <v>-0.00014480504307785944</v>
       </c>
       <c r="N22">
-        <v>-2.1996446149501973E-4</v>
+        <v>-0.00022541981049799915</v>
       </c>
       <c r="O22">
-        <v>-2.5105798887131714E-4</v>
+        <v>-0.00025560892682803668</v>
       </c>
       <c r="P22">
-        <v>-1.8873634597326491E-4</v>
+        <v>-0.00019360938088171676</v>
       </c>
       <c r="Q22">
-        <v>3.1426355071809928E-4</v>
+        <v>0.00031492359892058109</v>
       </c>
       <c r="R22">
-        <v>1.2121926822444319E-4</v>
+        <v>0.00012330061968069284</v>
       </c>
       <c r="S22">
-        <v>-9.0096142385287167E-5</v>
+        <v>-9.0049024326974494e-05</v>
       </c>
       <c r="T22">
-        <v>-4.8482046843859386E-5</v>
+        <v>-4.8268541012239097e-05</v>
       </c>
       <c r="U22">
-        <v>8.6277608255261318E-5</v>
+        <v>8.4941478565882288e-05</v>
       </c>
       <c r="V22">
-        <v>6.6728005251545132E-5</v>
+        <v>6.8948990521042783e-05</v>
       </c>
       <c r="W22">
-        <v>6.565999906691578E-3</v>
+        <v>0.0065749415329474752</v>
       </c>
       <c r="X22">
-        <v>5.5886845572016754E-3</v>
+        <v>0.005597489205782246</v>
       </c>
       <c r="Y22">
-        <v>5.5836897298863347E-3</v>
+        <v>0.0055913246969478874</v>
       </c>
       <c r="Z22">
-        <v>5.6096126105041749E-3</v>
+        <v>0.0056182184006463437</v>
       </c>
       <c r="AA22">
-        <v>5.6020299962277319E-3</v>
+        <v>0.0056105441696781954</v>
       </c>
       <c r="AB22">
-        <v>5.5751490951724235E-3</v>
+        <v>0.0055840314006913505</v>
       </c>
       <c r="AC22">
-        <v>2.2049455490788755E-6</v>
+        <v>2.2032915992962865e-06</v>
       </c>
       <c r="AD22">
-        <v>1.8804419656084275E-5</v>
+        <v>1.9595381813651731e-05</v>
       </c>
       <c r="AE22">
-        <v>4.5988420942344845E-5</v>
+        <v>4.6454748864826947e-05</v>
       </c>
       <c r="AF22">
-        <v>-4.2507347105164121E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.0042436321338876516</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
         <v>42</v>
       </c>
       <c r="B23">
-        <v>0.25624357551963872</v>
+        <v>0.25577669884025778</v>
       </c>
       <c r="C23">
-        <v>1.1841634004566988E-4</v>
+        <v>0.00011718669828638859</v>
       </c>
       <c r="D23">
-        <v>2.3621705846563201E-5</v>
+        <v>2.3742081909097768e-05</v>
       </c>
       <c r="E23">
-        <v>3.2856827072145524E-8</v>
+        <v>3.1977520128048144e-08</v>
       </c>
       <c r="F23">
-        <v>1.4883785957289786E-4</v>
+        <v>0.00014803026748788639</v>
       </c>
       <c r="G23">
-        <v>-6.1543642715794489E-6</v>
+        <v>-5.7741551319351325e-06</v>
       </c>
       <c r="H23">
-        <v>1.0227449040021161E-4</v>
+        <v>0.00010308475397696358</v>
       </c>
       <c r="I23">
-        <v>-1.1537836761782016E-4</v>
+        <v>-0.00011493013242398222</v>
       </c>
       <c r="J23">
-        <v>-1.4747596137238556E-4</v>
+        <v>-0.00014575261442900667</v>
       </c>
       <c r="K23">
-        <v>-2.9102294568792721E-4</v>
+        <v>-0.00029825124602073073</v>
       </c>
       <c r="L23">
-        <v>9.1786741238915684E-6</v>
+        <v>9.1627549761077315e-06</v>
       </c>
       <c r="M23">
-        <v>-1.0044767566196326E-4</v>
+        <v>-9.7156749001770697e-05</v>
       </c>
       <c r="N23">
-        <v>-2.4244449458122675E-4</v>
+        <v>-0.00024939586751726757</v>
       </c>
       <c r="O23">
-        <v>-3.2623527497734495E-4</v>
+        <v>-0.00032977357493683838</v>
       </c>
       <c r="P23">
-        <v>-4.0550502924804237E-4</v>
+        <v>-0.000408633699926878</v>
       </c>
       <c r="Q23">
-        <v>3.0083896246165551E-4</v>
+        <v>0.00030144872498486251</v>
       </c>
       <c r="R23">
-        <v>3.4437390712475403E-5</v>
+        <v>3.4910606329982726e-05</v>
       </c>
       <c r="S23">
-        <v>-2.3687929021631859E-5</v>
+        <v>-2.2709025556448548e-05</v>
       </c>
       <c r="T23">
-        <v>-6.6372444596110233E-5</v>
+        <v>-6.5827260097269316e-05</v>
       </c>
       <c r="U23">
-        <v>4.6019033076032806E-5</v>
+        <v>4.7126878472075881e-05</v>
       </c>
       <c r="V23">
-        <v>1.5637276049661658E-4</v>
+        <v>0.0001577460642710839</v>
       </c>
       <c r="W23">
-        <v>5.5886845572016754E-3</v>
+        <v>0.005597489205782246</v>
       </c>
       <c r="X23">
-        <v>6.5739828603584996E-3</v>
+        <v>0.0065818549399272982</v>
       </c>
       <c r="Y23">
-        <v>5.603033708659738E-3</v>
+        <v>0.0056099711448272466</v>
       </c>
       <c r="Z23">
-        <v>5.5975466463629043E-3</v>
+        <v>0.0056061862046577144</v>
       </c>
       <c r="AA23">
-        <v>5.6063691318284118E-3</v>
+        <v>0.0056149553515647014</v>
       </c>
       <c r="AB23">
-        <v>5.5571625800598769E-3</v>
+        <v>0.0055657098779065229</v>
       </c>
       <c r="AC23">
-        <v>2.8547976749440013E-6</v>
+        <v>2.8613173346996912e-06</v>
       </c>
       <c r="AD23">
-        <v>3.6772286860930646E-5</v>
+        <v>3.7511827945030732e-05</v>
       </c>
       <c r="AE23">
-        <v>1.5565115333169384E-5</v>
+        <v>1.5883862409894756e-05</v>
       </c>
       <c r="AF23">
-        <v>-6.9392962608397397E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.0069472892503008865</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
         <v>43</v>
       </c>
       <c r="B24">
-        <v>0.14521188020378961</v>
+        <v>0.14475684371156555</v>
       </c>
       <c r="C24">
-        <v>5.3230216531714952E-5</v>
+        <v>4.8178744582271665e-05</v>
       </c>
       <c r="D24">
-        <v>1.2143799227627705E-6</v>
+        <v>-3.8704070429579351e-06</v>
       </c>
       <c r="E24">
-        <v>2.6728374349146034E-8</v>
+        <v>6.5086707011464354e-08</v>
       </c>
       <c r="F24">
-        <v>6.0600137503937987E-5</v>
+        <v>6.1839722320284479e-05</v>
       </c>
       <c r="G24">
-        <v>-4.5158532275312371E-5</v>
+        <v>-4.2541419175512116e-05</v>
       </c>
       <c r="H24">
-        <v>1.2191385129444571E-4</v>
+        <v>0.00012400163406832058</v>
       </c>
       <c r="I24">
-        <v>2.1642693637046503E-5</v>
+        <v>2.1315789771607103e-05</v>
       </c>
       <c r="J24">
-        <v>-2.8842142467410542E-5</v>
+        <v>-2.5493468178346482e-05</v>
       </c>
       <c r="K24">
-        <v>-2.6567098142122941E-4</v>
+        <v>-0.00027577310138109194</v>
       </c>
       <c r="L24">
-        <v>-2.4033414581407526E-5</v>
+        <v>-2.8121862879063649e-05</v>
       </c>
       <c r="M24">
-        <v>-1.2464882319047031E-4</v>
+        <v>-0.00010555819433444882</v>
       </c>
       <c r="N24">
-        <v>-2.9083518978950033E-4</v>
+        <v>-0.00031920227166225854</v>
       </c>
       <c r="O24">
-        <v>-3.361037257944504E-4</v>
+        <v>-0.00033304066341063876</v>
       </c>
       <c r="P24">
-        <v>-3.4081909917388657E-4</v>
+        <v>-0.00033592062871086231</v>
       </c>
       <c r="Q24">
-        <v>4.0775648551883732E-4</v>
+        <v>0.00040497829225931344</v>
       </c>
       <c r="R24">
-        <v>1.467512952495688E-4</v>
+        <v>0.00013395084720729811</v>
       </c>
       <c r="S24">
-        <v>9.3603901718592852E-5</v>
+        <v>9.9053596375039184e-05</v>
       </c>
       <c r="T24">
-        <v>-1.5413901220451406E-4</v>
+        <v>-0.0001517202491255424</v>
       </c>
       <c r="U24">
-        <v>4.3922389092400556E-5</v>
+        <v>7.4877008986713766e-05</v>
       </c>
       <c r="V24">
-        <v>1.6367861033354371E-5</v>
+        <v>5.3152765317789606e-06</v>
       </c>
       <c r="W24">
-        <v>5.5836897298863347E-3</v>
+        <v>0.0055913246969478874</v>
       </c>
       <c r="X24">
-        <v>5.603033708659738E-3</v>
+        <v>0.0056099711448272466</v>
       </c>
       <c r="Y24">
-        <v>7.1160749970941902E-3</v>
+        <v>0.0071158738882606274</v>
       </c>
       <c r="Z24">
-        <v>5.5979776750722339E-3</v>
+        <v>0.0056044562289165895</v>
       </c>
       <c r="AA24">
-        <v>5.6023363320036202E-3</v>
+        <v>0.0056089329248003982</v>
       </c>
       <c r="AB24">
-        <v>5.5501722043315629E-3</v>
+        <v>0.0055545735966008427</v>
       </c>
       <c r="AC24">
-        <v>1.076773712683325E-5</v>
+        <v>1.0812600760194125e-05</v>
       </c>
       <c r="AD24">
-        <v>-6.970219717220439E-5</v>
+        <v>-6.7301146346862659e-05</v>
       </c>
       <c r="AE24">
-        <v>-4.0481782723951606E-5</v>
+        <v>-3.8056245425237062e-05</v>
       </c>
       <c r="AF24">
-        <v>-5.7599498240735805E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.0056085842255697779</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
       <c r="B25">
-        <v>0.11376422781623149</v>
+        <v>0.11331726483593248</v>
       </c>
       <c r="C25">
-        <v>1.3865831618414337E-4</v>
+        <v>0.00013774607665294658</v>
       </c>
       <c r="D25">
-        <v>6.9302106205107461E-5</v>
+        <v>6.8724992871471713e-05</v>
       </c>
       <c r="E25">
-        <v>-3.7698988840557685E-7</v>
+        <v>-3.7202786469926578e-07</v>
       </c>
       <c r="F25">
-        <v>1.030180871239017E-4</v>
+        <v>0.00010363882469052732</v>
       </c>
       <c r="G25">
-        <v>-5.2784243551179388E-5</v>
+        <v>-5.2264566186684125e-05</v>
       </c>
       <c r="H25">
-        <v>1.4436710684840757E-4</v>
+        <v>0.00014488697517877833</v>
       </c>
       <c r="I25">
-        <v>-1.4584323727857406E-4</v>
+        <v>-0.00014588290102506723</v>
       </c>
       <c r="J25">
-        <v>-1.4158238213639318E-4</v>
+        <v>-0.00014083786234840579</v>
       </c>
       <c r="K25">
-        <v>-2.5171508452830624E-4</v>
+        <v>-0.00025726902001886706</v>
       </c>
       <c r="L25">
-        <v>3.194206417965386E-5</v>
+        <v>3.1790154372651237e-05</v>
       </c>
       <c r="M25">
-        <v>-9.1092954269858745E-5</v>
+        <v>-8.8108133419343001e-05</v>
       </c>
       <c r="N25">
-        <v>-2.4887505658916865E-4</v>
+        <v>-0.00025524503412832503</v>
       </c>
       <c r="O25">
-        <v>-2.1536049324493009E-4</v>
+        <v>-0.00021799358574065312</v>
       </c>
       <c r="P25">
-        <v>-1.9405216603030507E-4</v>
+        <v>-0.00019773426821799011</v>
       </c>
       <c r="Q25">
-        <v>4.3272826800487568E-4</v>
+        <v>0.00043205366228518563</v>
       </c>
       <c r="R25">
-        <v>1.2784028704198366E-4</v>
+        <v>0.00012927734252676619</v>
       </c>
       <c r="S25">
-        <v>-2.7170147437050388E-5</v>
+        <v>-2.7282799368474192e-05</v>
       </c>
       <c r="T25">
-        <v>2.2633020274732615E-5</v>
+        <v>2.3578514321611135e-05</v>
       </c>
       <c r="U25">
-        <v>1.1918264766500042E-5</v>
+        <v>1.019056184778616e-05</v>
       </c>
       <c r="V25">
-        <v>1.2900647662039927E-4</v>
+        <v>0.0001313451766555546</v>
       </c>
       <c r="W25">
-        <v>5.6096126105041749E-3</v>
+        <v>0.0056182184006463437</v>
       </c>
       <c r="X25">
-        <v>5.5975466463629043E-3</v>
+        <v>0.0056061862046577144</v>
       </c>
       <c r="Y25">
-        <v>5.5979776750722339E-3</v>
+        <v>0.0056044562289165895</v>
       </c>
       <c r="Z25">
-        <v>6.469535202487945E-3</v>
+        <v>0.0064779728425862432</v>
       </c>
       <c r="AA25">
-        <v>5.6007274304517964E-3</v>
+        <v>0.0056090680234447418</v>
       </c>
       <c r="AB25">
-        <v>5.5867791216551044E-3</v>
+        <v>0.0055954437261854714</v>
       </c>
       <c r="AC25">
-        <v>1.4202039484412414E-6</v>
+        <v>1.394613114075054e-06</v>
       </c>
       <c r="AD25">
-        <v>-1.2177033538397688E-6</v>
+        <v>-3.4759947519598031e-07</v>
       </c>
       <c r="AE25">
-        <v>1.2426743780448099E-5</v>
+        <v>1.2955226785943798e-05</v>
       </c>
       <c r="AF25">
-        <v>-8.27618962564141E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.0082617951493176578</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
         <v>45</v>
       </c>
       <c r="B26">
-        <v>0.20219026314534</v>
+        <v>0.20163011245796764</v>
       </c>
       <c r="C26">
-        <v>1.0818608546091598E-4</v>
+        <v>0.00010682639065885913</v>
       </c>
       <c r="D26">
-        <v>9.9680704468585457E-5</v>
+        <v>9.8212617936709046e-05</v>
       </c>
       <c r="E26">
-        <v>-6.8591618313773562E-7</v>
+        <v>-6.741521444412655e-07</v>
       </c>
       <c r="F26">
-        <v>-2.615179518489566E-6</v>
+        <v>-2.8384731853136475e-06</v>
       </c>
       <c r="G26">
-        <v>-1.5847080904152558E-4</v>
+        <v>-0.00015755310279066438</v>
       </c>
       <c r="H26">
-        <v>8.724676520181551E-5</v>
+        <v>8.8669377087120793e-05</v>
       </c>
       <c r="I26">
-        <v>-1.1108130216969212E-4</v>
+        <v>-0.0001101965605927568</v>
       </c>
       <c r="J26">
-        <v>3.8227683195932172E-5</v>
+        <v>3.9493979859681061e-05</v>
       </c>
       <c r="K26">
-        <v>-1.951670658954595E-4</v>
+        <v>-0.00020468450235596668</v>
       </c>
       <c r="L26">
-        <v>2.1387047368748562E-5</v>
+        <v>2.1090592946311926e-05</v>
       </c>
       <c r="M26">
-        <v>-1.3600591306319029E-4</v>
+        <v>-0.00013608889006057784</v>
       </c>
       <c r="N26">
-        <v>-2.8005638457713684E-4</v>
+        <v>-0.00028614519125218403</v>
       </c>
       <c r="O26">
-        <v>-3.4239409481394325E-4</v>
+        <v>-0.00035005495749521769</v>
       </c>
       <c r="P26">
-        <v>-3.2387872231870365E-4</v>
+        <v>-0.00033125111374295436</v>
       </c>
       <c r="Q26">
-        <v>2.2044725784620933E-4</v>
+        <v>0.00022140635943298018</v>
       </c>
       <c r="R26">
-        <v>1.192564933582504E-4</v>
+        <v>0.00012053453456526667</v>
       </c>
       <c r="S26">
-        <v>-3.1612628740141854E-5</v>
+        <v>-3.0708333423957231e-05</v>
       </c>
       <c r="T26">
-        <v>-1.2648232008996389E-4</v>
+        <v>-0.00012558882733546472</v>
       </c>
       <c r="U26">
-        <v>2.0337663410299181E-5</v>
+        <v>1.7606702362682643e-05</v>
       </c>
       <c r="V26">
-        <v>4.6779451483714639E-5</v>
+        <v>4.840379574826084e-05</v>
       </c>
       <c r="W26">
-        <v>5.6020299962277319E-3</v>
+        <v>0.0056105441696781954</v>
       </c>
       <c r="X26">
-        <v>5.6063691318284118E-3</v>
+        <v>0.0056149553515647014</v>
       </c>
       <c r="Y26">
-        <v>5.6023363320036202E-3</v>
+        <v>0.0056089329248003982</v>
       </c>
       <c r="Z26">
-        <v>5.6007274304517964E-3</v>
+        <v>0.0056090680234447418</v>
       </c>
       <c r="AA26">
-        <v>6.2919386641834708E-3</v>
+        <v>0.0063001709699822203</v>
       </c>
       <c r="AB26">
-        <v>5.5752842344851351E-3</v>
+        <v>0.0055838764450321212</v>
       </c>
       <c r="AC26">
-        <v>-1.1625259043383916E-6</v>
+        <v>-1.2834038213058294e-06</v>
       </c>
       <c r="AD26">
-        <v>-1.7669484237886222E-5</v>
+        <v>-1.6928933898208588e-05</v>
       </c>
       <c r="AE26">
-        <v>-4.7732134044238582E-5</v>
+        <v>-4.6927308750788601e-05</v>
       </c>
       <c r="AF26">
-        <v>-8.8774891191270508E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.0088279038811361274</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="s">
         <v>46</v>
       </c>
       <c r="B27">
-        <v>9.0700948916997357E-2</v>
+        <v>0.090118593809311698</v>
       </c>
       <c r="C27">
-        <v>6.904116465748897E-6</v>
+        <v>4.9126265871130698e-06</v>
       </c>
       <c r="D27">
-        <v>-7.81267756554474E-6</v>
+        <v>-8.910078441896202e-06</v>
       </c>
       <c r="E27">
-        <v>7.4841568163490618E-8</v>
+        <v>8.4422650261327652e-08</v>
       </c>
       <c r="F27">
-        <v>2.8694224247772376E-5</v>
+        <v>2.8557322717493588e-05</v>
       </c>
       <c r="G27">
-        <v>-6.1231019737612719E-5</v>
+        <v>-6.1080630215214898e-05</v>
       </c>
       <c r="H27">
-        <v>1.216628739850352E-4</v>
+        <v>0.00012156054460784455</v>
       </c>
       <c r="I27">
-        <v>-1.170967151515451E-4</v>
+        <v>-0.00011801960343317856</v>
       </c>
       <c r="J27">
-        <v>2.333301139561747E-5</v>
+        <v>2.4788358628582974e-05</v>
       </c>
       <c r="K27">
-        <v>-3.5260073014265619E-4</v>
+        <v>-0.00035659743215211309</v>
       </c>
       <c r="L27">
-        <v>1.6773148791221059E-4</v>
+        <v>0.00016642399232355033</v>
       </c>
       <c r="M27">
-        <v>-3.7767557070671242E-5</v>
+        <v>-4.2360719535237783e-05</v>
       </c>
       <c r="N27">
-        <v>-2.0339001972587178E-4</v>
+        <v>-0.00020670251566448032</v>
       </c>
       <c r="O27">
-        <v>-2.1777243440040928E-4</v>
+        <v>-0.00022060929938164369</v>
       </c>
       <c r="P27">
-        <v>-1.5439345875577432E-4</v>
+        <v>-0.00015752425869476182</v>
       </c>
       <c r="Q27">
-        <v>3.0965431843519556E-4</v>
+        <v>0.00030722955467435512</v>
       </c>
       <c r="R27">
-        <v>1.3048039836500384E-4</v>
+        <v>0.00013212833064750202</v>
       </c>
       <c r="S27">
-        <v>8.5678058381575238E-5</v>
+        <v>8.4614004872416056e-05</v>
       </c>
       <c r="T27">
-        <v>-2.6678346156877066E-5</v>
+        <v>-2.6005312702187013e-05</v>
       </c>
       <c r="U27">
-        <v>-1.0155547831822251E-5</v>
+        <v>-1.0781277873877463e-05</v>
       </c>
       <c r="V27">
-        <v>6.1309649792859797E-5</v>
+        <v>6.5308869836180249e-05</v>
       </c>
       <c r="W27">
-        <v>5.5751490951724235E-3</v>
+        <v>0.0055840314006913505</v>
       </c>
       <c r="X27">
-        <v>5.5571625800598769E-3</v>
+        <v>0.0055657098779065229</v>
       </c>
       <c r="Y27">
-        <v>5.5501722043315629E-3</v>
+        <v>0.0055545735966008427</v>
       </c>
       <c r="Z27">
-        <v>5.5867791216551044E-3</v>
+        <v>0.0055954437261854714</v>
       </c>
       <c r="AA27">
-        <v>5.5752842344851351E-3</v>
+        <v>0.0055838764450321212</v>
       </c>
       <c r="AB27">
-        <v>6.4263435122981277E-3</v>
+        <v>0.0064351836762464448</v>
       </c>
       <c r="AC27">
-        <v>-1.033716147270756E-6</v>
+        <v>-1.1292520019287871e-06</v>
       </c>
       <c r="AD27">
-        <v>-1.1612915465998835E-5</v>
+        <v>-1.0185041513356566e-05</v>
       </c>
       <c r="AE27">
-        <v>-6.1415532766426889E-6</v>
+        <v>-5.3503943841536929e-06</v>
       </c>
       <c r="AF27">
-        <v>-5.1189027836808718E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.0050884515272725667</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
         <v>47</v>
       </c>
       <c r="B28">
-        <v>-1.2784743266723547E-2</v>
+        <v>-0.012785075279735304</v>
       </c>
       <c r="C28">
-        <v>2.5353164022284618E-6</v>
+        <v>2.4776307102107787e-06</v>
       </c>
       <c r="D28">
-        <v>7.9028390590845342E-6</v>
+        <v>7.6894564163970409e-06</v>
       </c>
       <c r="E28">
-        <v>-8.6962150874775284E-8</v>
+        <v>-8.5298855852961786e-08</v>
       </c>
       <c r="F28">
-        <v>-2.65208927625434E-5</v>
+        <v>-2.6204696560632465e-05</v>
       </c>
       <c r="G28">
-        <v>-2.1592680214786318E-5</v>
+        <v>-2.1341645404754459e-05</v>
       </c>
       <c r="H28">
-        <v>-7.5258779324508928E-8</v>
+        <v>-6.7567849008904588e-08</v>
       </c>
       <c r="I28">
-        <v>1.9389961749731991E-5</v>
+        <v>1.941753313047549e-05</v>
       </c>
       <c r="J28">
-        <v>3.1534090340889229E-5</v>
+        <v>3.1386323548112727e-05</v>
       </c>
       <c r="K28">
-        <v>1.0821262241786595E-5</v>
+        <v>1.0842317350978006e-05</v>
       </c>
       <c r="L28">
-        <v>1.338068976918949E-5</v>
+        <v>1.314740851867121e-05</v>
       </c>
       <c r="M28">
-        <v>1.0084306560428356E-5</v>
+        <v>1.0680174898978e-05</v>
       </c>
       <c r="N28">
-        <v>1.4648079613180153E-5</v>
+        <v>1.4337837120798419e-05</v>
       </c>
       <c r="O28">
-        <v>3.0603459678323622E-5</v>
+        <v>3.0811572730141105e-05</v>
       </c>
       <c r="P28">
-        <v>2.8749809877302813E-5</v>
+        <v>2.9230857368788741e-05</v>
       </c>
       <c r="Q28">
-        <v>-2.8648510659164898E-6</v>
+        <v>-2.6593947574513934e-06</v>
       </c>
       <c r="R28">
-        <v>1.0884319646008893E-8</v>
+        <v>-2.0774248674817054e-07</v>
       </c>
       <c r="S28">
-        <v>1.5624033055573806E-5</v>
+        <v>1.5477903807434494e-05</v>
       </c>
       <c r="T28">
-        <v>5.5367129802432136E-6</v>
+        <v>5.4575238601470191e-06</v>
       </c>
       <c r="U28">
-        <v>1.9886218302450158E-5</v>
+        <v>2.07578784322191e-05</v>
       </c>
       <c r="V28">
-        <v>1.2533754994691592E-6</v>
+        <v>8.7929737120875221e-07</v>
       </c>
       <c r="W28">
-        <v>2.2049455490788755E-6</v>
+        <v>2.2032915992962865e-06</v>
       </c>
       <c r="X28">
-        <v>2.8547976749440013E-6</v>
+        <v>2.8613173346996912e-06</v>
       </c>
       <c r="Y28">
-        <v>1.076773712683325E-5</v>
+        <v>1.0812600760194125e-05</v>
       </c>
       <c r="Z28">
-        <v>1.4202039484412414E-6</v>
+        <v>1.394613114075054e-06</v>
       </c>
       <c r="AA28">
-        <v>-1.1625259043383916E-6</v>
+        <v>-1.2834038213058294e-06</v>
       </c>
       <c r="AB28">
-        <v>-1.033716147270756E-6</v>
+        <v>-1.1292520019287871e-06</v>
       </c>
       <c r="AC28">
-        <v>1.1325146511577549E-5</v>
+        <v>1.1331696986853658e-05</v>
       </c>
       <c r="AD28">
-        <v>-5.1944754159041913E-5</v>
+        <v>-5.1906003842919947e-05</v>
       </c>
       <c r="AE28">
-        <v>-6.1322572801623265E-5</v>
+        <v>-6.1234078315309807e-05</v>
       </c>
       <c r="AF28">
-        <v>-4.0443249410909276E-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+        <v>-0.00039845771258858933</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="s">
         <v>57</v>
       </c>
       <c r="B29">
-        <v>-0.10375050595729865</v>
+        <v>-0.1031359646339098</v>
       </c>
       <c r="C29">
-        <v>-2.3776572513753403E-5</v>
+        <v>-2.3223249741205097e-05</v>
       </c>
       <c r="D29">
-        <v>-3.6344385382469646E-5</v>
+        <v>-3.5578004677468134e-05</v>
       </c>
       <c r="E29">
-        <v>1.9120497312020849E-7</v>
+        <v>1.8555260430182154e-07</v>
       </c>
       <c r="F29">
-        <v>1.2217974530180642E-5</v>
+        <v>1.0373384236265354e-05</v>
       </c>
       <c r="G29">
-        <v>-5.6279052144281305E-5</v>
+        <v>-5.7384389136192621e-05</v>
       </c>
       <c r="H29">
-        <v>5.0381547394161199E-6</v>
+        <v>4.2652856073839215e-06</v>
       </c>
       <c r="I29">
-        <v>-8.5274694678563897E-6</v>
+        <v>-7.8372901766114852e-06</v>
       </c>
       <c r="J29">
-        <v>1.2208290770163513E-4</v>
+        <v>0.00012509085884941304</v>
       </c>
       <c r="K29">
-        <v>3.6093097805065867E-5</v>
+        <v>3.7954302363365014e-05</v>
       </c>
       <c r="L29">
-        <v>-4.2790836759010187E-5</v>
+        <v>-4.5823475039459549e-05</v>
       </c>
       <c r="M29">
-        <v>-6.3177250266289336E-5</v>
+        <v>-6.5824493005430342e-05</v>
       </c>
       <c r="N29">
-        <v>-1.5044552863043405E-5</v>
+        <v>-9.7963643587656649e-06</v>
       </c>
       <c r="O29">
-        <v>-7.6728373431216371E-5</v>
+        <v>-7.2283144237423463e-05</v>
       </c>
       <c r="P29">
-        <v>-6.9070441358058026E-5</v>
+        <v>-6.7643239154849613e-05</v>
       </c>
       <c r="Q29">
-        <v>-5.9196877903071657E-5</v>
+        <v>-5.7126805712021767e-05</v>
       </c>
       <c r="R29">
-        <v>6.0972931589001102E-5</v>
+        <v>6.4294158556674631e-05</v>
       </c>
       <c r="S29">
-        <v>-1.7872411875424592E-4</v>
+        <v>-0.00017939898187556685</v>
       </c>
       <c r="T29">
-        <v>7.5151238037992826E-5</v>
+        <v>7.3655770240833515e-05</v>
       </c>
       <c r="U29">
-        <v>-3.1775308139086621E-5</v>
+        <v>-3.6830218089368353e-05</v>
       </c>
       <c r="V29">
-        <v>1.0683123865898217E-5</v>
+        <v>1.3224633977957989e-05</v>
       </c>
       <c r="W29">
-        <v>1.8804419656084275E-5</v>
+        <v>1.9595381813651731e-05</v>
       </c>
       <c r="X29">
-        <v>3.6772286860930646E-5</v>
+        <v>3.7511827945030732e-05</v>
       </c>
       <c r="Y29">
-        <v>-6.970219717220439E-5</v>
+        <v>-6.7301146346862659e-05</v>
       </c>
       <c r="Z29">
-        <v>-1.2177033538397688E-6</v>
+        <v>-3.4759947519598031e-07</v>
       </c>
       <c r="AA29">
-        <v>-1.7669484237886222E-5</v>
+        <v>-1.6928933898208588e-05</v>
       </c>
       <c r="AB29">
-        <v>-1.1612915465998835E-5</v>
+        <v>-1.0185041513356566e-05</v>
       </c>
       <c r="AC29">
-        <v>-5.1944754159041913E-5</v>
+        <v>-5.1906003842919947e-05</v>
       </c>
       <c r="AD29">
-        <v>1.9972247089062828E-3</v>
+        <v>0.0019955742881395994</v>
       </c>
       <c r="AE29">
-        <v>5.2015278159011269E-4</v>
+        <v>0.00051939025008444946</v>
       </c>
       <c r="AF29">
-        <v>2.2454379278869395E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.0022170965788758943</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="s">
         <v>58</v>
       </c>
       <c r="B30">
-        <v>-0.14415804782230582</v>
+        <v>-0.14393642498623999</v>
       </c>
       <c r="C30">
-        <v>-6.2605724090432444E-6</v>
+        <v>-4.4678625891582738e-06</v>
       </c>
       <c r="D30">
-        <v>-1.1806164469294056E-4</v>
+        <v>-0.00011682690919145866</v>
       </c>
       <c r="E30">
-        <v>8.4897259201063401E-7</v>
+        <v>8.3937923825243809e-07</v>
       </c>
       <c r="F30">
-        <v>4.8669687654673971E-5</v>
+        <v>4.7905722388302818e-05</v>
       </c>
       <c r="G30">
-        <v>4.852695168872101E-5</v>
+        <v>4.7849793608903401e-05</v>
       </c>
       <c r="H30">
-        <v>-8.4157082835525834E-6</v>
+        <v>-8.8677485128745882e-06</v>
       </c>
       <c r="I30">
-        <v>6.5353898931124832E-6</v>
+        <v>6.5603499794597651e-06</v>
       </c>
       <c r="J30">
-        <v>8.8173611989782186E-6</v>
+        <v>8.0769061200705594e-06</v>
       </c>
       <c r="K30">
-        <v>3.9237592265942796E-5</v>
+        <v>4.5256783722280461e-05</v>
       </c>
       <c r="L30">
-        <v>-6.2428390317280889E-5</v>
+        <v>-6.054863791288452e-05</v>
       </c>
       <c r="M30">
-        <v>-1.0207168516141178E-5</v>
+        <v>-1.6012190147301694e-05</v>
       </c>
       <c r="N30">
-        <v>1.6109562603758331E-5</v>
+        <v>2.2381727130647063e-05</v>
       </c>
       <c r="O30">
-        <v>-6.0861654323060739E-5</v>
+        <v>-5.7626272148701219e-05</v>
       </c>
       <c r="P30">
-        <v>7.8556709443727314E-6</v>
+        <v>1.0583718424814204e-05</v>
       </c>
       <c r="Q30">
-        <v>-2.0531197943280403E-5</v>
+        <v>-2.0966339689480106e-05</v>
       </c>
       <c r="R30">
-        <v>8.481826988177444E-5</v>
+        <v>8.7029099143565505e-05</v>
       </c>
       <c r="S30">
-        <v>-1.6821745419701769E-4</v>
+        <v>-0.00016849461974473984</v>
       </c>
       <c r="T30">
-        <v>-5.1538663644032368E-5</v>
+        <v>-5.18315454336735e-05</v>
       </c>
       <c r="U30">
-        <v>6.0271614670592616E-6</v>
+        <v>2.6466396971980191e-06</v>
       </c>
       <c r="V30">
-        <v>-8.60921585123263E-5</v>
+        <v>-8.3977859161524015e-05</v>
       </c>
       <c r="W30">
-        <v>4.5988420942344845E-5</v>
+        <v>4.6454748864826947e-05</v>
       </c>
       <c r="X30">
-        <v>1.5565115333169384E-5</v>
+        <v>1.5883862409894756e-05</v>
       </c>
       <c r="Y30">
-        <v>-4.0481782723951606E-5</v>
+        <v>-3.8056245425237062e-05</v>
       </c>
       <c r="Z30">
-        <v>1.2426743780448099E-5</v>
+        <v>1.2955226785943798e-05</v>
       </c>
       <c r="AA30">
-        <v>-4.7732134044238582E-5</v>
+        <v>-4.6927308750788601e-05</v>
       </c>
       <c r="AB30">
-        <v>-6.1415532766426889E-6</v>
+        <v>-5.3503943841536929e-06</v>
       </c>
       <c r="AC30">
-        <v>-6.1322572801623265E-5</v>
+        <v>-6.1234078315309807e-05</v>
       </c>
       <c r="AD30">
-        <v>5.2015278159011269E-4</v>
+        <v>0.00051939025008444946</v>
       </c>
       <c r="AE30">
-        <v>1.8985645626088787E-3</v>
+        <v>0.0018976268139986984</v>
       </c>
       <c r="AF30">
-        <v>4.8771004306105443E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0.004831323220829401</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="s">
         <v>49</v>
       </c>
       <c r="B31">
-        <v>-3.4766705973745746</v>
+        <v>-3.4851017522342072</v>
       </c>
       <c r="C31">
-        <v>-1.0362830863151266E-2</v>
+        <v>-0.010287050854226872</v>
       </c>
       <c r="D31">
-        <v>-0.12185803817751206</v>
+        <v>-0.1216221215987221</v>
       </c>
       <c r="E31">
-        <v>9.899097002269196E-4</v>
+        <v>0.00098791275842285194</v>
       </c>
       <c r="F31">
-        <v>8.891250148184171E-2</v>
+        <v>0.088654720080440064</v>
       </c>
       <c r="G31">
-        <v>8.2591000956276639E-2</v>
+        <v>0.082340267770000919</v>
       </c>
       <c r="H31">
-        <v>-7.4842086026358917E-4</v>
+        <v>-0.00075024134974785439</v>
       </c>
       <c r="I31">
-        <v>2.4179104459880023E-4</v>
+        <v>0.00025950867414788366</v>
       </c>
       <c r="J31">
-        <v>-8.0972410481051138E-2</v>
+        <v>-0.080769256865265038</v>
       </c>
       <c r="K31">
-        <v>1.5604631246996618E-3</v>
+        <v>0.0017261773402181477</v>
       </c>
       <c r="L31">
-        <v>-1.9576070744094703E-2</v>
+        <v>-0.019370287991933549</v>
       </c>
       <c r="M31">
-        <v>-3.6488735544846183E-3</v>
+        <v>-0.0037011640693166287</v>
       </c>
       <c r="N31">
-        <v>2.2789462033859474E-3</v>
+        <v>0.0025178687532631493</v>
       </c>
       <c r="O31">
-        <v>-8.2375056725186857E-4</v>
+        <v>-0.00080772888074353427</v>
       </c>
       <c r="P31">
-        <v>1.8947356936218698E-3</v>
+        <v>0.0019005430719428174</v>
       </c>
       <c r="Q31">
-        <v>6.096500656888419E-3</v>
+        <v>0.0061292056521188437</v>
       </c>
       <c r="R31">
-        <v>-9.9367354861983545E-3</v>
+        <v>-0.0098559102980137897</v>
       </c>
       <c r="S31">
-        <v>7.0811416908349023E-3</v>
+        <v>0.0071112984478000213</v>
       </c>
       <c r="T31">
-        <v>1.4227122448520785E-2</v>
+        <v>0.014272363652518577</v>
       </c>
       <c r="U31">
-        <v>1.0161438826846517E-3</v>
+        <v>0.00072251865082669994</v>
       </c>
       <c r="V31">
-        <v>8.5672300024444877E-4</v>
+        <v>0.0009223747283513958</v>
       </c>
       <c r="W31">
-        <v>-4.2507347105164121E-3</v>
+        <v>-0.0042436321338876516</v>
       </c>
       <c r="X31">
-        <v>-6.9392962608397397E-3</v>
+        <v>-0.0069472892503008865</v>
       </c>
       <c r="Y31">
-        <v>-5.7599498240735805E-3</v>
+        <v>-0.0056085842255697779</v>
       </c>
       <c r="Z31">
-        <v>-8.27618962564141E-3</v>
+        <v>-0.0082617951493176578</v>
       </c>
       <c r="AA31">
-        <v>-8.8774891191270508E-3</v>
+        <v>-0.0088279038811361274</v>
       </c>
       <c r="AB31">
-        <v>-5.1189027836808718E-3</v>
+        <v>-0.0050884515272725667</v>
       </c>
       <c r="AC31">
-        <v>-4.0443249410909276E-4</v>
+        <v>-0.00039845771258858933</v>
       </c>
       <c r="AD31">
-        <v>2.2454379278869395E-3</v>
+        <v>0.0022170965788758943</v>
       </c>
       <c r="AE31">
-        <v>4.8771004306105443E-3</v>
+        <v>0.004831323220829401</v>
       </c>
       <c r="AF31">
-        <v>3.757441185828533</v>
+        <v>3.7503475456077062</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>